--- a/artfynd/A 19766-2025 artfynd.xlsx
+++ b/artfynd/A 19766-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125451751</v>
+        <v>125452794</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
+        <v>98269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533503</v>
+        <v>533476</v>
       </c>
       <c r="R2" t="n">
-        <v>6885498</v>
+        <v>6885492</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125452441</v>
+        <v>125450058</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>98290</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +793,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533485</v>
+        <v>533564</v>
       </c>
       <c r="R3" t="n">
-        <v>6885472</v>
+        <v>6885654</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125456035</v>
+        <v>125449226</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533444</v>
+        <v>533571</v>
       </c>
       <c r="R4" t="n">
-        <v>6884916</v>
+        <v>6885716</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125457380</v>
+        <v>125453495</v>
       </c>
       <c r="B5" t="n">
-        <v>91299</v>
+        <v>57635</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,43 +1005,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533577</v>
+        <v>533487</v>
       </c>
       <c r="R5" t="n">
-        <v>6885438</v>
+        <v>6885398</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,6 +1070,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125456406</v>
+        <v>125450555</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>78947</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,39 +1117,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533520</v>
+        <v>533508</v>
       </c>
       <c r="R6" t="n">
-        <v>6885018</v>
+        <v>6885633</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125456893</v>
+        <v>125456788</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>98269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,40 +1215,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>130</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1253,10 +1247,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533561</v>
+        <v>533556</v>
       </c>
       <c r="R7" t="n">
-        <v>6885192</v>
+        <v>6885155</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,10 +1309,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125451793</v>
+        <v>125455042</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>57635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,42 +1321,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>200</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533474</v>
+        <v>533556</v>
       </c>
       <c r="R8" t="n">
-        <v>6885517</v>
+        <v>6885155</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,6 +1390,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,10 +1421,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125452859</v>
+        <v>125451409</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1437,34 +1437,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533466</v>
+        <v>533498</v>
       </c>
       <c r="R9" t="n">
-        <v>6885506</v>
+        <v>6885552</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,6 +1502,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall. Både äldre spår och färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1523,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125452794</v>
+        <v>125454035</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,30 +1545,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1567,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533476</v>
+        <v>533438</v>
       </c>
       <c r="R10" t="n">
-        <v>6885492</v>
+        <v>6885340</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125448798</v>
+        <v>125451627</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>80028</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,42 +1652,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533560</v>
+        <v>533471</v>
       </c>
       <c r="R11" t="n">
-        <v>6885711</v>
+        <v>6885526</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1742,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125451578</v>
+        <v>125449196</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>57635</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,30 +1754,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1779,10 +1791,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533480</v>
+        <v>533558</v>
       </c>
       <c r="R12" t="n">
-        <v>6885534</v>
+        <v>6885696</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1853,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125449144</v>
+        <v>125448834</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>58001</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,20 +1865,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1877,7 +1889,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1886,10 +1898,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533538</v>
+        <v>533571</v>
       </c>
       <c r="R13" t="n">
-        <v>6885703</v>
+        <v>6885716</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,11 +1934,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1953,10 +1960,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125456251</v>
+        <v>125450898</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>80028</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1969,34 +1976,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533497</v>
+        <v>533518</v>
       </c>
       <c r="R14" t="n">
-        <v>6884966</v>
+        <v>6885534</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,10 +2067,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125453918</v>
+        <v>125452859</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>78947</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2071,21 +2083,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2095,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>533477</v>
+        <v>533466</v>
       </c>
       <c r="R15" t="n">
-        <v>6885329</v>
+        <v>6885506</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2157,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125451683</v>
+        <v>125449383</v>
       </c>
       <c r="B16" t="n">
-        <v>79920</v>
+        <v>78947</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2169,25 +2181,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2197,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533471</v>
+        <v>533564</v>
       </c>
       <c r="R16" t="n">
-        <v>6885526</v>
+        <v>6885654</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2259,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125450188</v>
+        <v>125457466</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>91166</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2275,39 +2287,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>533539</v>
+        <v>533602</v>
       </c>
       <c r="R17" t="n">
-        <v>6885634</v>
+        <v>6885362</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2340,11 +2347,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2371,10 +2373,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125455421</v>
+        <v>125454495</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2404,26 +2406,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>533497</v>
+        <v>533467</v>
       </c>
       <c r="R18" t="n">
-        <v>6885148</v>
+        <v>6885270</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2456,6 +2454,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2482,10 +2485,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125449337</v>
+        <v>125452374</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2522,10 +2525,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>533564</v>
+        <v>533550</v>
       </c>
       <c r="R19" t="n">
-        <v>6885654</v>
+        <v>6885458</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,10 +2587,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125455217</v>
+        <v>125451692</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2596,38 +2599,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>533571</v>
+        <v>533471</v>
       </c>
       <c r="R20" t="n">
-        <v>6885153</v>
+        <v>6885526</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2686,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125451627</v>
+        <v>125449144</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2702,34 +2709,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>533471</v>
+        <v>533538</v>
       </c>
       <c r="R21" t="n">
-        <v>6885526</v>
+        <v>6885703</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2762,6 +2774,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2788,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125453207</v>
+        <v>125453918</v>
       </c>
       <c r="B22" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2828,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533421</v>
+        <v>533477</v>
       </c>
       <c r="R22" t="n">
-        <v>6885458</v>
+        <v>6885329</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125456355</v>
+        <v>125451213</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>98290</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2902,42 +2919,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533513</v>
+        <v>533490</v>
       </c>
       <c r="R23" t="n">
-        <v>6885005</v>
+        <v>6885584</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2996,10 +3013,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125450718</v>
+        <v>125449764</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>57635</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3008,30 +3025,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3040,10 +3058,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533537</v>
+        <v>533559</v>
       </c>
       <c r="R24" t="n">
-        <v>6885571</v>
+        <v>6885649</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3076,6 +3094,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3102,10 +3125,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125450671</v>
+        <v>125449821</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3137,7 +3160,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3146,10 +3169,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533493</v>
+        <v>533559</v>
       </c>
       <c r="R25" t="n">
-        <v>6885612</v>
+        <v>6885649</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3208,10 +3231,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125455687</v>
+        <v>125457312</v>
       </c>
       <c r="B26" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3248,10 +3271,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533469</v>
+        <v>533577</v>
       </c>
       <c r="R26" t="n">
-        <v>6885049</v>
+        <v>6885438</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3310,10 +3333,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125455042</v>
+        <v>125455421</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3343,10 +3366,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3355,10 +3382,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533556</v>
+        <v>533497</v>
       </c>
       <c r="R27" t="n">
-        <v>6885155</v>
+        <v>6885148</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3391,11 +3418,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3422,10 +3444,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125448393</v>
+        <v>125448352</v>
       </c>
       <c r="B28" t="n">
-        <v>96979</v>
+        <v>91166</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3434,25 +3456,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3524,10 +3546,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125456654</v>
+        <v>125452337</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3540,27 +3562,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3569,10 +3595,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533587</v>
+        <v>533485</v>
       </c>
       <c r="R29" t="n">
-        <v>6885384</v>
+        <v>6885472</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3605,11 +3631,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3636,10 +3657,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125456823</v>
+        <v>125452107</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>57793</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3652,39 +3673,48 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533580</v>
+        <v>533485</v>
       </c>
       <c r="R30" t="n">
-        <v>6885391</v>
+        <v>6885472</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3717,11 +3747,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3748,10 +3773,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125457466</v>
+        <v>125448326</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
+        <v>78947</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3764,34 +3789,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533602</v>
+        <v>533568</v>
       </c>
       <c r="R31" t="n">
-        <v>6885362</v>
+        <v>6885736</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3850,10 +3875,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125452374</v>
+        <v>125449337</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3890,10 +3915,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533550</v>
+        <v>533564</v>
       </c>
       <c r="R32" t="n">
-        <v>6885458</v>
+        <v>6885654</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3952,10 +3977,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125449765</v>
+        <v>125451683</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>80057</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3964,25 +3989,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3992,10 +4017,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533527</v>
+        <v>533471</v>
       </c>
       <c r="R33" t="n">
-        <v>6885657</v>
+        <v>6885526</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4054,10 +4079,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125449226</v>
+        <v>125454471</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>80028</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4070,21 +4095,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4094,10 +4119,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533571</v>
+        <v>533467</v>
       </c>
       <c r="R34" t="n">
-        <v>6885716</v>
+        <v>6885270</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4156,10 +4181,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125449821</v>
+        <v>125450637</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4168,42 +4193,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533559</v>
+        <v>533545</v>
       </c>
       <c r="R35" t="n">
-        <v>6885649</v>
+        <v>6885577</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4262,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125452660</v>
+        <v>125452738</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4278,43 +4299,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533535</v>
+        <v>533500</v>
       </c>
       <c r="R36" t="n">
-        <v>6885468</v>
+        <v>6885440</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4373,10 +4385,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125450387</v>
+        <v>125458140</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4409,14 +4421,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533528</v>
+        <v>533574</v>
       </c>
       <c r="R37" t="n">
-        <v>6885627</v>
+        <v>6885198</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4475,10 +4487,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125451954</v>
+        <v>125456035</v>
       </c>
       <c r="B38" t="n">
-        <v>56714</v>
+        <v>91166</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4491,39 +4503,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533479</v>
+        <v>533444</v>
       </c>
       <c r="R38" t="n">
-        <v>6885506</v>
+        <v>6884916</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4582,10 +4589,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125450747</v>
+        <v>125456406</v>
       </c>
       <c r="B39" t="n">
-        <v>98122</v>
+        <v>57632</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4594,42 +4601,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533545</v>
+        <v>533520</v>
       </c>
       <c r="R39" t="n">
-        <v>6885577</v>
+        <v>6885018</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4688,10 +4696,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125455201</v>
+        <v>125451578</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4723,19 +4731,19 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533571</v>
+        <v>533480</v>
       </c>
       <c r="R40" t="n">
-        <v>6885153</v>
+        <v>6885534</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4794,10 +4802,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125450555</v>
+        <v>125450747</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>98290</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4806,38 +4814,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533508</v>
+        <v>533545</v>
       </c>
       <c r="R41" t="n">
-        <v>6885633</v>
+        <v>6885577</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4896,10 +4908,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125449383</v>
+        <v>125456823</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4912,34 +4924,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533564</v>
+        <v>533580</v>
       </c>
       <c r="R42" t="n">
-        <v>6885654</v>
+        <v>6885391</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4972,6 +4989,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4998,10 +5020,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125453817</v>
+        <v>125456968</v>
       </c>
       <c r="B43" t="n">
-        <v>79891</v>
+        <v>91166</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5014,34 +5036,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533455</v>
+        <v>533562</v>
       </c>
       <c r="R43" t="n">
-        <v>6885379</v>
+        <v>6885408</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5100,10 +5122,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125456732</v>
+        <v>125457210</v>
       </c>
       <c r="B44" t="n">
-        <v>57529</v>
+        <v>57635</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5116,16 +5138,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5145,10 +5167,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533566</v>
+        <v>533578</v>
       </c>
       <c r="R44" t="n">
-        <v>6885119</v>
+        <v>6885205</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5181,6 +5203,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5207,10 +5234,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125459043</v>
+        <v>125456893</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5240,22 +5267,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533634</v>
+        <v>533561</v>
       </c>
       <c r="R45" t="n">
-        <v>6885654</v>
+        <v>6885192</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5288,11 +5324,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5319,10 +5350,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125458100</v>
+        <v>125457445</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5354,7 +5385,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>37</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5363,10 +5394,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533578</v>
+        <v>533577</v>
       </c>
       <c r="R46" t="n">
-        <v>6885205</v>
+        <v>6885438</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5425,10 +5456,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125450452</v>
+        <v>125454123</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>97147</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5437,42 +5468,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>533508</v>
+        <v>533490</v>
       </c>
       <c r="R47" t="n">
-        <v>6885633</v>
+        <v>6885291</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5531,10 +5558,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125456232</v>
+        <v>125448879</v>
       </c>
       <c r="B48" t="n">
-        <v>57513</v>
+        <v>98269</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5543,43 +5570,42 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533493</v>
+        <v>533558</v>
       </c>
       <c r="R48" t="n">
-        <v>6884951</v>
+        <v>6885696</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5612,11 +5638,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.  Mest äldre spår men öven något färskt</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5643,10 +5664,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125453495</v>
+        <v>125451954</v>
       </c>
       <c r="B49" t="n">
-        <v>57513</v>
+        <v>56828</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5659,16 +5680,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5679,7 +5700,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5688,10 +5709,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>533487</v>
+        <v>533479</v>
       </c>
       <c r="R49" t="n">
-        <v>6885398</v>
+        <v>6885506</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5724,11 +5745,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5755,10 +5771,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125449396</v>
+        <v>125448393</v>
       </c>
       <c r="B50" t="n">
-        <v>79891</v>
+        <v>97147</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5767,25 +5783,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5795,10 +5811,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>533550</v>
+        <v>533568</v>
       </c>
       <c r="R50" t="n">
-        <v>6885685</v>
+        <v>6885736</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5857,10 +5873,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125450152</v>
+        <v>125455217</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5893,14 +5909,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>533539</v>
+        <v>533571</v>
       </c>
       <c r="R51" t="n">
-        <v>6885645</v>
+        <v>6885153</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5959,10 +5975,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125457133</v>
+        <v>125450505</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>80028</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5975,34 +5991,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>533574</v>
+        <v>533526</v>
       </c>
       <c r="R52" t="n">
-        <v>6885404</v>
+        <v>6885605</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6061,10 +6082,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125450637</v>
+        <v>125459043</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6077,34 +6098,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533545</v>
+        <v>533634</v>
       </c>
       <c r="R53" t="n">
-        <v>6885577</v>
+        <v>6885654</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6137,6 +6163,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6163,10 +6194,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125457312</v>
+        <v>125449549</v>
       </c>
       <c r="B54" t="n">
-        <v>91012</v>
+        <v>80028</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6179,34 +6210,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>533577</v>
+        <v>533559</v>
       </c>
       <c r="R54" t="n">
-        <v>6885438</v>
+        <v>6885649</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6265,10 +6296,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125451247</v>
+        <v>125456221</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6301,14 +6332,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>533498</v>
+        <v>533478</v>
       </c>
       <c r="R55" t="n">
-        <v>6885552</v>
+        <v>6884944</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6367,10 +6398,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125452337</v>
+        <v>125457380</v>
       </c>
       <c r="B56" t="n">
-        <v>78810</v>
+        <v>91459</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6383,43 +6414,43 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>533485</v>
+        <v>533577</v>
       </c>
       <c r="R56" t="n">
-        <v>6885472</v>
+        <v>6885438</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6478,10 +6509,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125451409</v>
+        <v>125458930</v>
       </c>
       <c r="B57" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6494,39 +6525,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>533498</v>
+        <v>533634</v>
       </c>
       <c r="R57" t="n">
-        <v>6885552</v>
+        <v>6885654</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6559,11 +6585,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall. Både äldre spår och färska</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6590,10 +6611,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125450058</v>
+        <v>125452441</v>
       </c>
       <c r="B58" t="n">
-        <v>98122</v>
+        <v>91184</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6602,42 +6623,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>533564</v>
+        <v>533485</v>
       </c>
       <c r="R58" t="n">
-        <v>6885654</v>
+        <v>6885472</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6696,10 +6713,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125449549</v>
+        <v>125455687</v>
       </c>
       <c r="B59" t="n">
-        <v>79891</v>
+        <v>91166</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6712,34 +6729,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>533559</v>
+        <v>533469</v>
       </c>
       <c r="R59" t="n">
-        <v>6885649</v>
+        <v>6885049</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6798,10 +6815,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125449273</v>
+        <v>125453277</v>
       </c>
       <c r="B60" t="n">
-        <v>98101</v>
+        <v>57793</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6810,30 +6827,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>37</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6842,10 +6860,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>533550</v>
+        <v>533421</v>
       </c>
       <c r="R60" t="n">
-        <v>6885685</v>
+        <v>6885458</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6904,10 +6922,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125453277</v>
+        <v>125455827</v>
       </c>
       <c r="B61" t="n">
-        <v>57666</v>
+        <v>91166</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6920,39 +6938,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>533421</v>
+        <v>533479</v>
       </c>
       <c r="R61" t="n">
-        <v>6885458</v>
+        <v>6884999</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7011,10 +7024,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125450898</v>
+        <v>125456538</v>
       </c>
       <c r="B62" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7027,39 +7040,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>533518</v>
+        <v>533543</v>
       </c>
       <c r="R62" t="n">
-        <v>6885534</v>
+        <v>6885069</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7092,6 +7105,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7118,10 +7136,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125456968</v>
+        <v>125458714</v>
       </c>
       <c r="B63" t="n">
-        <v>91012</v>
+        <v>57635</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7134,34 +7152,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>533562</v>
+        <v>533683</v>
       </c>
       <c r="R63" t="n">
-        <v>6885408</v>
+        <v>6885420</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7194,6 +7217,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7220,10 +7248,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125456371</v>
+        <v>125449396</v>
       </c>
       <c r="B64" t="n">
-        <v>78810</v>
+        <v>80028</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7236,34 +7264,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>533602</v>
+        <v>533550</v>
       </c>
       <c r="R64" t="n">
-        <v>6885362</v>
+        <v>6885685</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7322,10 +7350,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125456221</v>
+        <v>125449273</v>
       </c>
       <c r="B65" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7334,38 +7362,42 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>533478</v>
+        <v>533550</v>
       </c>
       <c r="R65" t="n">
-        <v>6884944</v>
+        <v>6885685</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7424,10 +7456,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125458714</v>
+        <v>125453207</v>
       </c>
       <c r="B66" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7440,39 +7472,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>533683</v>
+        <v>533421</v>
       </c>
       <c r="R66" t="n">
-        <v>6885420</v>
+        <v>6885458</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7505,11 +7532,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7536,10 +7558,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125450235</v>
+        <v>125451793</v>
       </c>
       <c r="B67" t="n">
-        <v>57513</v>
+        <v>98269</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7548,31 +7570,30 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>200</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7581,10 +7602,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>533551</v>
+        <v>533474</v>
       </c>
       <c r="R67" t="n">
-        <v>6885632</v>
+        <v>6885517</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7617,11 +7638,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7648,10 +7664,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125457445</v>
+        <v>125450452</v>
       </c>
       <c r="B68" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7683,19 +7699,19 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533577</v>
+        <v>533508</v>
       </c>
       <c r="R68" t="n">
-        <v>6885438</v>
+        <v>6885633</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7754,10 +7770,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125448879</v>
+        <v>125452660</v>
       </c>
       <c r="B69" t="n">
-        <v>98101</v>
+        <v>57635</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7766,30 +7782,35 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -7798,10 +7819,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533558</v>
+        <v>533535</v>
       </c>
       <c r="R69" t="n">
-        <v>6885696</v>
+        <v>6885468</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7860,10 +7881,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125458930</v>
+        <v>125456654</v>
       </c>
       <c r="B70" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7876,34 +7897,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533634</v>
+        <v>533587</v>
       </c>
       <c r="R70" t="n">
-        <v>6885654</v>
+        <v>6885384</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7936,6 +7962,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7962,10 +7993,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125456250</v>
+        <v>125450235</v>
       </c>
       <c r="B71" t="n">
-        <v>91030</v>
+        <v>57635</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7978,43 +8009,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>533602</v>
+        <v>533551</v>
       </c>
       <c r="R71" t="n">
-        <v>6885362</v>
+        <v>6885632</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8047,6 +8074,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8073,10 +8105,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125452107</v>
+        <v>125450818</v>
       </c>
       <c r="B72" t="n">
-        <v>57666</v>
+        <v>98269</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8085,40 +8117,30 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8127,10 +8149,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>533485</v>
+        <v>533494</v>
       </c>
       <c r="R72" t="n">
-        <v>6885472</v>
+        <v>6885624</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8189,10 +8211,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125451213</v>
+        <v>125456355</v>
       </c>
       <c r="B73" t="n">
-        <v>98122</v>
+        <v>98269</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8201,42 +8223,42 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>533490</v>
+        <v>533513</v>
       </c>
       <c r="R73" t="n">
-        <v>6885584</v>
+        <v>6885005</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8295,10 +8317,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125449764</v>
+        <v>125451751</v>
       </c>
       <c r="B74" t="n">
-        <v>57513</v>
+        <v>97147</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8307,43 +8329,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>533559</v>
+        <v>533503</v>
       </c>
       <c r="R74" t="n">
-        <v>6885649</v>
+        <v>6885498</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8376,11 +8393,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8407,10 +8419,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125456538</v>
+        <v>125451445</v>
       </c>
       <c r="B75" t="n">
-        <v>57513</v>
+        <v>80057</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8419,43 +8431,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>533543</v>
+        <v>533474</v>
       </c>
       <c r="R75" t="n">
-        <v>6885069</v>
+        <v>6885569</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8488,11 +8495,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8519,10 +8521,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125454495</v>
+        <v>125453817</v>
       </c>
       <c r="B76" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8535,39 +8537,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>533467</v>
+        <v>533455</v>
       </c>
       <c r="R76" t="n">
-        <v>6885270</v>
+        <v>6885379</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8600,11 +8597,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8631,10 +8623,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125452738</v>
+        <v>125457133</v>
       </c>
       <c r="B77" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8667,14 +8659,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>533500</v>
+        <v>533574</v>
       </c>
       <c r="R77" t="n">
-        <v>6885440</v>
+        <v>6885404</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8733,10 +8725,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125459017</v>
+        <v>125456371</v>
       </c>
       <c r="B78" t="n">
-        <v>91673</v>
+        <v>78947</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8745,38 +8737,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>898</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>533634</v>
+        <v>533602</v>
       </c>
       <c r="R78" t="n">
-        <v>6885654</v>
+        <v>6885362</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8835,10 +8827,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125458140</v>
+        <v>125456250</v>
       </c>
       <c r="B79" t="n">
-        <v>78810</v>
+        <v>91184</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8851,34 +8843,43 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>533574</v>
+        <v>533602</v>
       </c>
       <c r="R79" t="n">
-        <v>6885198</v>
+        <v>6885362</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8937,10 +8938,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125452693</v>
+        <v>125450387</v>
       </c>
       <c r="B80" t="n">
-        <v>56112</v>
+        <v>78947</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8953,39 +8954,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>533485</v>
+        <v>533528</v>
       </c>
       <c r="R80" t="n">
-        <v>6885472</v>
+        <v>6885627</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9044,10 +9040,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125449196</v>
+        <v>125459017</v>
       </c>
       <c r="B81" t="n">
-        <v>57513</v>
+        <v>91833</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9056,47 +9052,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>533558</v>
+        <v>533634</v>
       </c>
       <c r="R81" t="n">
-        <v>6885696</v>
+        <v>6885654</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9155,10 +9142,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125455827</v>
+        <v>125456732</v>
       </c>
       <c r="B82" t="n">
-        <v>91012</v>
+        <v>57632</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9171,34 +9158,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533479</v>
+        <v>533566</v>
       </c>
       <c r="R82" t="n">
-        <v>6884999</v>
+        <v>6885119</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9257,10 +9249,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125450818</v>
+        <v>125456232</v>
       </c>
       <c r="B83" t="n">
-        <v>98101</v>
+        <v>57635</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9269,42 +9261,43 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>150</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>533494</v>
+        <v>533493</v>
       </c>
       <c r="R83" t="n">
-        <v>6885624</v>
+        <v>6884951</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9337,6 +9330,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Mest äldre spår men öven något färskt</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9363,10 +9361,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125454471</v>
+        <v>125455201</v>
       </c>
       <c r="B84" t="n">
-        <v>79891</v>
+        <v>98269</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9375,38 +9373,42 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>533467</v>
+        <v>533571</v>
       </c>
       <c r="R84" t="n">
-        <v>6885270</v>
+        <v>6885153</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9465,10 +9467,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125454035</v>
+        <v>125450671</v>
       </c>
       <c r="B85" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9477,31 +9479,30 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9510,10 +9511,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>533438</v>
+        <v>533493</v>
       </c>
       <c r="R85" t="n">
-        <v>6885340</v>
+        <v>6885612</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9572,10 +9573,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125457210</v>
+        <v>125452693</v>
       </c>
       <c r="B86" t="n">
-        <v>57513</v>
+        <v>56226</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9588,39 +9589,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>533578</v>
+        <v>533485</v>
       </c>
       <c r="R86" t="n">
-        <v>6885205</v>
+        <v>6885472</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9653,11 +9654,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9684,10 +9680,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125451445</v>
+        <v>125449765</v>
       </c>
       <c r="B87" t="n">
-        <v>79920</v>
+        <v>78947</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9696,25 +9692,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9724,10 +9720,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>533474</v>
+        <v>533527</v>
       </c>
       <c r="R87" t="n">
-        <v>6885569</v>
+        <v>6885657</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9786,10 +9782,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125450505</v>
+        <v>125450152</v>
       </c>
       <c r="B88" t="n">
-        <v>79891</v>
+        <v>78947</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9802,39 +9798,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>533526</v>
+        <v>533539</v>
       </c>
       <c r="R88" t="n">
-        <v>6885605</v>
+        <v>6885645</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9893,10 +9884,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125456788</v>
+        <v>125451247</v>
       </c>
       <c r="B89" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9905,42 +9896,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>533556</v>
+        <v>533498</v>
       </c>
       <c r="R89" t="n">
-        <v>6885155</v>
+        <v>6885552</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9999,10 +9986,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125448352</v>
+        <v>125450188</v>
       </c>
       <c r="B90" t="n">
-        <v>91012</v>
+        <v>57635</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10015,34 +10002,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>533568</v>
+        <v>533539</v>
       </c>
       <c r="R90" t="n">
-        <v>6885736</v>
+        <v>6885634</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10075,6 +10067,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10101,10 +10098,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125454123</v>
+        <v>125458100</v>
       </c>
       <c r="B91" t="n">
-        <v>96979</v>
+        <v>98269</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10113,38 +10110,42 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>533490</v>
+        <v>533578</v>
       </c>
       <c r="R91" t="n">
-        <v>6885291</v>
+        <v>6885205</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10203,10 +10204,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125448326</v>
+        <v>125450718</v>
       </c>
       <c r="B92" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10215,38 +10216,42 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>533568</v>
+        <v>533537</v>
       </c>
       <c r="R92" t="n">
-        <v>6885736</v>
+        <v>6885571</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10305,10 +10310,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125448667</v>
+        <v>125449118</v>
       </c>
       <c r="B93" t="n">
-        <v>79891</v>
+        <v>98269</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10317,38 +10322,42 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>533560</v>
+        <v>533549</v>
       </c>
       <c r="R93" t="n">
-        <v>6885711</v>
+        <v>6885695</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10378,9 +10387,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10407,10 +10426,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125449555</v>
+        <v>125448798</v>
       </c>
       <c r="B94" t="n">
-        <v>79891</v>
+        <v>98269</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10419,38 +10438,42 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>533527</v>
+        <v>533560</v>
       </c>
       <c r="R94" t="n">
-        <v>6885657</v>
+        <v>6885711</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10509,10 +10532,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125448834</v>
+        <v>125456251</v>
       </c>
       <c r="B95" t="n">
-        <v>57883</v>
+        <v>91166</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10521,43 +10544,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>533571</v>
+        <v>533497</v>
       </c>
       <c r="R95" t="n">
-        <v>6885716</v>
+        <v>6884966</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10616,10 +10634,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125449118</v>
+        <v>125448667</v>
       </c>
       <c r="B96" t="n">
-        <v>98101</v>
+        <v>80028</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10628,42 +10646,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>533549</v>
+        <v>533560</v>
       </c>
       <c r="R96" t="n">
-        <v>6885695</v>
+        <v>6885711</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10693,19 +10707,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>12:08</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10732,10 +10736,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125451692</v>
+        <v>125449555</v>
       </c>
       <c r="B97" t="n">
-        <v>98101</v>
+        <v>80028</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10744,42 +10748,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>533471</v>
+        <v>533527</v>
       </c>
       <c r="R97" t="n">
-        <v>6885526</v>
+        <v>6885657</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10841,7 +10841,7 @@
         <v>125455828</v>
       </c>
       <c r="B98" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>

--- a/artfynd/A 19766-2025 artfynd.xlsx
+++ b/artfynd/A 19766-2025 artfynd.xlsx
@@ -2805,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125453918</v>
+        <v>125449821</v>
       </c>
       <c r="B22" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2817,38 +2817,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533477</v>
+        <v>533559</v>
       </c>
       <c r="R22" t="n">
-        <v>6885329</v>
+        <v>6885649</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,10 +2911,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125451213</v>
+        <v>125455421</v>
       </c>
       <c r="B23" t="n">
-        <v>98290</v>
+        <v>57635</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2919,42 +2923,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533490</v>
+        <v>533497</v>
       </c>
       <c r="R23" t="n">
-        <v>6885584</v>
+        <v>6885148</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3013,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125449764</v>
+        <v>125451213</v>
       </c>
       <c r="B24" t="n">
-        <v>57635</v>
+        <v>98290</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3025,31 +3034,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3058,10 +3066,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533559</v>
+        <v>533490</v>
       </c>
       <c r="R24" t="n">
-        <v>6885649</v>
+        <v>6885584</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3094,11 +3102,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3125,10 +3128,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125449821</v>
+        <v>125449764</v>
       </c>
       <c r="B25" t="n">
-        <v>98269</v>
+        <v>57635</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3137,30 +3140,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3205,6 +3209,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3231,7 +3240,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125457312</v>
+        <v>125448352</v>
       </c>
       <c r="B26" t="n">
         <v>91166</v>
@@ -3267,14 +3276,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533577</v>
+        <v>533568</v>
       </c>
       <c r="R26" t="n">
-        <v>6885438</v>
+        <v>6885736</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3333,10 +3342,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125455421</v>
+        <v>125453918</v>
       </c>
       <c r="B27" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3349,43 +3358,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533497</v>
+        <v>533477</v>
       </c>
       <c r="R27" t="n">
-        <v>6885148</v>
+        <v>6885329</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3444,7 +3444,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125448352</v>
+        <v>125457312</v>
       </c>
       <c r="B28" t="n">
         <v>91166</v>
@@ -3480,14 +3480,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533568</v>
+        <v>533577</v>
       </c>
       <c r="R28" t="n">
-        <v>6885736</v>
+        <v>6885438</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125452107</v>
+        <v>125448326</v>
       </c>
       <c r="B30" t="n">
-        <v>57793</v>
+        <v>78947</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3673,48 +3673,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533485</v>
+        <v>533568</v>
       </c>
       <c r="R30" t="n">
-        <v>6885472</v>
+        <v>6885736</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3773,10 +3759,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125448326</v>
+        <v>125452107</v>
       </c>
       <c r="B31" t="n">
-        <v>78947</v>
+        <v>57793</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3789,34 +3775,48 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533568</v>
+        <v>533485</v>
       </c>
       <c r="R31" t="n">
-        <v>6885736</v>
+        <v>6885472</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4696,10 +4696,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125451578</v>
+        <v>125456823</v>
       </c>
       <c r="B40" t="n">
-        <v>98269</v>
+        <v>57635</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4708,42 +4708,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>18</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533480</v>
+        <v>533580</v>
       </c>
       <c r="R40" t="n">
-        <v>6885534</v>
+        <v>6885391</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4776,6 +4777,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4908,10 +4914,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125456823</v>
+        <v>125451578</v>
       </c>
       <c r="B42" t="n">
-        <v>57635</v>
+        <v>98269</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4920,43 +4926,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533580</v>
+        <v>533480</v>
       </c>
       <c r="R42" t="n">
-        <v>6885391</v>
+        <v>6885534</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4989,11 +4994,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5122,10 +5122,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125457210</v>
+        <v>125451954</v>
       </c>
       <c r="B44" t="n">
-        <v>57635</v>
+        <v>56828</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5138,16 +5138,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5158,19 +5158,19 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533578</v>
+        <v>533479</v>
       </c>
       <c r="R44" t="n">
-        <v>6885205</v>
+        <v>6885506</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5203,11 +5203,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5234,7 +5229,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125456893</v>
+        <v>125457210</v>
       </c>
       <c r="B45" t="n">
         <v>57635</v>
@@ -5267,19 +5262,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5288,10 +5274,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533561</v>
+        <v>533578</v>
       </c>
       <c r="R45" t="n">
-        <v>6885192</v>
+        <v>6885205</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5324,6 +5310,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5350,10 +5341,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125457445</v>
+        <v>125456893</v>
       </c>
       <c r="B46" t="n">
-        <v>98269</v>
+        <v>57635</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5362,30 +5353,40 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5394,10 +5395,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533577</v>
+        <v>533561</v>
       </c>
       <c r="R46" t="n">
-        <v>6885438</v>
+        <v>6885192</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5456,10 +5457,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125454123</v>
+        <v>125457445</v>
       </c>
       <c r="B47" t="n">
-        <v>97147</v>
+        <v>98269</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5468,38 +5469,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>533490</v>
+        <v>533577</v>
       </c>
       <c r="R47" t="n">
-        <v>6885291</v>
+        <v>6885438</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5558,10 +5563,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125448879</v>
+        <v>125454123</v>
       </c>
       <c r="B48" t="n">
-        <v>98269</v>
+        <v>97147</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5570,42 +5575,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533558</v>
+        <v>533490</v>
       </c>
       <c r="R48" t="n">
-        <v>6885696</v>
+        <v>6885291</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5664,10 +5665,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125451954</v>
+        <v>125448879</v>
       </c>
       <c r="B49" t="n">
-        <v>56828</v>
+        <v>98269</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5676,31 +5677,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5709,10 +5709,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>533479</v>
+        <v>533558</v>
       </c>
       <c r="R49" t="n">
-        <v>6885506</v>
+        <v>6885696</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -10310,10 +10310,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125449118</v>
+        <v>125448667</v>
       </c>
       <c r="B93" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10322,42 +10322,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>533549</v>
+        <v>533560</v>
       </c>
       <c r="R93" t="n">
-        <v>6885695</v>
+        <v>6885711</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10387,19 +10383,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>12:08</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10426,10 +10412,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125448798</v>
+        <v>125449555</v>
       </c>
       <c r="B94" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10438,42 +10424,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>533560</v>
+        <v>533527</v>
       </c>
       <c r="R94" t="n">
-        <v>6885711</v>
+        <v>6885657</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10532,10 +10514,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125456251</v>
+        <v>125449118</v>
       </c>
       <c r="B95" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10544,38 +10526,42 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>533497</v>
+        <v>533549</v>
       </c>
       <c r="R95" t="n">
-        <v>6884966</v>
+        <v>6885695</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10605,9 +10591,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10634,10 +10630,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125448667</v>
+        <v>125448798</v>
       </c>
       <c r="B96" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10646,28 +10642,32 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
@@ -10736,10 +10736,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125449555</v>
+        <v>125456251</v>
       </c>
       <c r="B97" t="n">
-        <v>80028</v>
+        <v>91166</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10752,34 +10752,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>533527</v>
+        <v>533497</v>
       </c>
       <c r="R97" t="n">
-        <v>6885657</v>
+        <v>6884966</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>

--- a/artfynd/A 19766-2025 artfynd.xlsx
+++ b/artfynd/A 19766-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125452794</v>
+        <v>125457466</v>
       </c>
       <c r="B2" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533476</v>
+        <v>533602</v>
       </c>
       <c r="R2" t="n">
-        <v>6885492</v>
+        <v>6885362</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125450058</v>
+        <v>125452738</v>
       </c>
       <c r="B3" t="n">
-        <v>98290</v>
+        <v>78947</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,42 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533564</v>
+        <v>533500</v>
       </c>
       <c r="R3" t="n">
-        <v>6885654</v>
+        <v>6885440</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125449226</v>
+        <v>125449555</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533571</v>
+        <v>533527</v>
       </c>
       <c r="R4" t="n">
-        <v>6885716</v>
+        <v>6885657</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125453495</v>
+        <v>125457445</v>
       </c>
       <c r="B5" t="n">
-        <v>57635</v>
+        <v>98269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,43 +993,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>37</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533487</v>
+        <v>533577</v>
       </c>
       <c r="R5" t="n">
-        <v>6885398</v>
+        <v>6885438</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,11 +1061,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125450555</v>
+        <v>125450718</v>
       </c>
       <c r="B6" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,38 +1099,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533508</v>
+        <v>533537</v>
       </c>
       <c r="R6" t="n">
-        <v>6885633</v>
+        <v>6885571</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125456788</v>
+        <v>125451213</v>
       </c>
       <c r="B7" t="n">
-        <v>98269</v>
+        <v>98290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,42 +1205,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533556</v>
+        <v>533490</v>
       </c>
       <c r="R7" t="n">
-        <v>6885155</v>
+        <v>6885584</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,10 +1299,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125455042</v>
+        <v>125450671</v>
       </c>
       <c r="B8" t="n">
-        <v>57635</v>
+        <v>98269</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,43 +1311,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533556</v>
+        <v>533493</v>
       </c>
       <c r="R8" t="n">
-        <v>6885155</v>
+        <v>6885612</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,11 +1379,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,10 +1405,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125451409</v>
+        <v>125449383</v>
       </c>
       <c r="B9" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1437,39 +1421,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533498</v>
+        <v>533564</v>
       </c>
       <c r="R9" t="n">
-        <v>6885552</v>
+        <v>6885654</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,11 +1481,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall. Både äldre spår och färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125454035</v>
+        <v>125454471</v>
       </c>
       <c r="B10" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,39 +1523,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533438</v>
+        <v>533467</v>
       </c>
       <c r="R10" t="n">
-        <v>6885340</v>
+        <v>6885270</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1640,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125451627</v>
+        <v>125456250</v>
       </c>
       <c r="B11" t="n">
-        <v>80028</v>
+        <v>91184</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1656,34 +1625,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533471</v>
+        <v>533602</v>
       </c>
       <c r="R11" t="n">
-        <v>6885526</v>
+        <v>6885362</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125449196</v>
+        <v>125456251</v>
       </c>
       <c r="B12" t="n">
-        <v>57635</v>
+        <v>91166</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1758,43 +1736,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533558</v>
+        <v>533497</v>
       </c>
       <c r="R12" t="n">
-        <v>6885696</v>
+        <v>6884966</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1853,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125448834</v>
+        <v>125452337</v>
       </c>
       <c r="B13" t="n">
-        <v>58001</v>
+        <v>78947</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1865,31 +1834,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1898,10 +1871,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533571</v>
+        <v>533485</v>
       </c>
       <c r="R13" t="n">
-        <v>6885716</v>
+        <v>6885472</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1960,7 +1933,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125450898</v>
+        <v>125453918</v>
       </c>
       <c r="B14" t="n">
         <v>80028</v>
@@ -1994,21 +1967,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533518</v>
+        <v>533477</v>
       </c>
       <c r="R14" t="n">
-        <v>6885534</v>
+        <v>6885329</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,7 +2035,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125452859</v>
+        <v>125450387</v>
       </c>
       <c r="B15" t="n">
         <v>78947</v>
@@ -2107,10 +2075,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>533466</v>
+        <v>533528</v>
       </c>
       <c r="R15" t="n">
-        <v>6885506</v>
+        <v>6885627</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2169,10 +2137,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125449383</v>
+        <v>125459017</v>
       </c>
       <c r="B16" t="n">
-        <v>78947</v>
+        <v>91833</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2181,25 +2149,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>898</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,7 +2177,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533564</v>
+        <v>533634</v>
       </c>
       <c r="R16" t="n">
         <v>6885654</v>
@@ -2271,10 +2239,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125457466</v>
+        <v>125449226</v>
       </c>
       <c r="B17" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2287,34 +2255,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>533602</v>
+        <v>533571</v>
       </c>
       <c r="R17" t="n">
-        <v>6885362</v>
+        <v>6885716</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2373,10 +2341,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125454495</v>
+        <v>125448393</v>
       </c>
       <c r="B18" t="n">
-        <v>57635</v>
+        <v>97147</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2385,43 +2353,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>533467</v>
+        <v>533568</v>
       </c>
       <c r="R18" t="n">
-        <v>6885270</v>
+        <v>6885736</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,11 +2417,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2485,10 +2443,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125452374</v>
+        <v>125459043</v>
       </c>
       <c r="B19" t="n">
-        <v>91166</v>
+        <v>57635</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2501,34 +2459,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>533550</v>
+        <v>533634</v>
       </c>
       <c r="R19" t="n">
-        <v>6885458</v>
+        <v>6885654</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2561,6 +2524,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2587,10 +2555,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125451692</v>
+        <v>125449764</v>
       </c>
       <c r="B20" t="n">
-        <v>98269</v>
+        <v>57635</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,30 +2567,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>22</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2631,10 +2600,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>533471</v>
+        <v>533559</v>
       </c>
       <c r="R20" t="n">
-        <v>6885526</v>
+        <v>6885649</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2667,6 +2636,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2693,7 +2667,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125449144</v>
+        <v>125458714</v>
       </c>
       <c r="B21" t="n">
         <v>57635</v>
@@ -2734,14 +2708,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>533538</v>
+        <v>533683</v>
       </c>
       <c r="R21" t="n">
-        <v>6885703</v>
+        <v>6885420</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2752,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,10 +2779,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125449821</v>
+        <v>125457133</v>
       </c>
       <c r="B22" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2817,42 +2791,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533559</v>
+        <v>533574</v>
       </c>
       <c r="R22" t="n">
-        <v>6885649</v>
+        <v>6885404</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2911,10 +2881,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125455421</v>
+        <v>125452374</v>
       </c>
       <c r="B23" t="n">
-        <v>57635</v>
+        <v>91166</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2927,43 +2897,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533497</v>
+        <v>533550</v>
       </c>
       <c r="R23" t="n">
-        <v>6885148</v>
+        <v>6885458</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3022,10 +2983,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125451213</v>
+        <v>125450235</v>
       </c>
       <c r="B24" t="n">
-        <v>98290</v>
+        <v>57635</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3034,30 +2995,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3066,10 +3028,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533490</v>
+        <v>533551</v>
       </c>
       <c r="R24" t="n">
-        <v>6885584</v>
+        <v>6885632</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3102,6 +3064,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3128,10 +3095,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125449764</v>
+        <v>125453277</v>
       </c>
       <c r="B25" t="n">
-        <v>57635</v>
+        <v>57793</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3144,27 +3111,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3173,10 +3140,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533559</v>
+        <v>533421</v>
       </c>
       <c r="R25" t="n">
-        <v>6885649</v>
+        <v>6885458</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3209,11 +3176,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3240,10 +3202,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125448352</v>
+        <v>125449821</v>
       </c>
       <c r="B26" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3252,38 +3214,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533568</v>
+        <v>533559</v>
       </c>
       <c r="R26" t="n">
-        <v>6885736</v>
+        <v>6885649</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3342,10 +3308,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125453918</v>
+        <v>125455201</v>
       </c>
       <c r="B27" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3354,38 +3320,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533477</v>
+        <v>533571</v>
       </c>
       <c r="R27" t="n">
-        <v>6885329</v>
+        <v>6885153</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3444,10 +3414,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125457312</v>
+        <v>125452660</v>
       </c>
       <c r="B28" t="n">
-        <v>91166</v>
+        <v>57635</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3460,34 +3430,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533577</v>
+        <v>533535</v>
       </c>
       <c r="R28" t="n">
-        <v>6885438</v>
+        <v>6885468</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3546,10 +3525,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125452337</v>
+        <v>125451683</v>
       </c>
       <c r="B29" t="n">
-        <v>78947</v>
+        <v>80057</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3558,47 +3537,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533485</v>
+        <v>533471</v>
       </c>
       <c r="R29" t="n">
-        <v>6885472</v>
+        <v>6885526</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3657,10 +3627,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125448326</v>
+        <v>125451627</v>
       </c>
       <c r="B30" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3673,21 +3643,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3697,10 +3667,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533568</v>
+        <v>533471</v>
       </c>
       <c r="R30" t="n">
-        <v>6885736</v>
+        <v>6885526</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3759,10 +3729,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125452107</v>
+        <v>125451793</v>
       </c>
       <c r="B31" t="n">
-        <v>57793</v>
+        <v>98269</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3771,40 +3741,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3813,10 +3773,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533485</v>
+        <v>533474</v>
       </c>
       <c r="R31" t="n">
-        <v>6885472</v>
+        <v>6885517</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3875,10 +3835,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125449337</v>
+        <v>125450452</v>
       </c>
       <c r="B32" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3887,38 +3847,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533564</v>
+        <v>533508</v>
       </c>
       <c r="R32" t="n">
-        <v>6885654</v>
+        <v>6885633</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3977,10 +3941,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125451683</v>
+        <v>125456968</v>
       </c>
       <c r="B33" t="n">
-        <v>80057</v>
+        <v>91166</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3989,38 +3953,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533471</v>
+        <v>533562</v>
       </c>
       <c r="R33" t="n">
-        <v>6885526</v>
+        <v>6885408</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4079,10 +4043,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125454471</v>
+        <v>125452441</v>
       </c>
       <c r="B34" t="n">
-        <v>80028</v>
+        <v>91184</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4095,21 +4059,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4119,10 +4083,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533467</v>
+        <v>533485</v>
       </c>
       <c r="R34" t="n">
-        <v>6885270</v>
+        <v>6885472</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4181,7 +4145,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125450637</v>
+        <v>125450555</v>
       </c>
       <c r="B35" t="n">
         <v>78947</v>
@@ -4221,10 +4185,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533545</v>
+        <v>533508</v>
       </c>
       <c r="R35" t="n">
-        <v>6885577</v>
+        <v>6885633</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4283,10 +4247,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125452738</v>
+        <v>125456893</v>
       </c>
       <c r="B36" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4299,34 +4263,48 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533500</v>
+        <v>533561</v>
       </c>
       <c r="R36" t="n">
-        <v>6885440</v>
+        <v>6885192</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4385,10 +4363,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125458140</v>
+        <v>125449337</v>
       </c>
       <c r="B37" t="n">
-        <v>78947</v>
+        <v>91166</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4401,34 +4379,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533574</v>
+        <v>533564</v>
       </c>
       <c r="R37" t="n">
-        <v>6885198</v>
+        <v>6885654</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4487,10 +4465,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125456035</v>
+        <v>125456355</v>
       </c>
       <c r="B38" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4499,38 +4477,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533444</v>
+        <v>533513</v>
       </c>
       <c r="R38" t="n">
-        <v>6884916</v>
+        <v>6885005</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4589,10 +4571,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125456406</v>
+        <v>125450898</v>
       </c>
       <c r="B39" t="n">
-        <v>57632</v>
+        <v>80028</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4605,39 +4587,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533520</v>
+        <v>533518</v>
       </c>
       <c r="R39" t="n">
-        <v>6885018</v>
+        <v>6885534</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4696,10 +4678,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125456823</v>
+        <v>125457380</v>
       </c>
       <c r="B40" t="n">
-        <v>57635</v>
+        <v>91459</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4712,27 +4694,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4741,10 +4727,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533580</v>
+        <v>533577</v>
       </c>
       <c r="R40" t="n">
-        <v>6885391</v>
+        <v>6885438</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4777,11 +4763,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4808,10 +4789,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125450747</v>
+        <v>125455042</v>
       </c>
       <c r="B41" t="n">
-        <v>98290</v>
+        <v>57635</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4820,42 +4801,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533545</v>
+        <v>533556</v>
       </c>
       <c r="R41" t="n">
-        <v>6885577</v>
+        <v>6885155</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4888,6 +4870,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4914,10 +4901,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125451578</v>
+        <v>125456823</v>
       </c>
       <c r="B42" t="n">
-        <v>98269</v>
+        <v>57635</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4926,42 +4913,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>18</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533480</v>
+        <v>533580</v>
       </c>
       <c r="R42" t="n">
-        <v>6885534</v>
+        <v>6885391</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4994,6 +4982,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5020,10 +5013,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125456968</v>
+        <v>125448879</v>
       </c>
       <c r="B43" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5032,38 +5025,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533562</v>
+        <v>533558</v>
       </c>
       <c r="R43" t="n">
-        <v>6885408</v>
+        <v>6885696</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5122,10 +5119,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125451954</v>
+        <v>125456732</v>
       </c>
       <c r="B44" t="n">
-        <v>56828</v>
+        <v>57632</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5138,16 +5135,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5158,19 +5155,19 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533479</v>
+        <v>533566</v>
       </c>
       <c r="R44" t="n">
-        <v>6885506</v>
+        <v>6885119</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5229,7 +5226,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125457210</v>
+        <v>125456538</v>
       </c>
       <c r="B45" t="n">
         <v>57635</v>
@@ -5265,7 +5262,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5274,10 +5271,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533578</v>
+        <v>533543</v>
       </c>
       <c r="R45" t="n">
-        <v>6885205</v>
+        <v>6885069</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5341,10 +5338,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125456893</v>
+        <v>125455827</v>
       </c>
       <c r="B46" t="n">
-        <v>57635</v>
+        <v>91166</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5357,48 +5354,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533561</v>
+        <v>533479</v>
       </c>
       <c r="R46" t="n">
-        <v>6885192</v>
+        <v>6884999</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5457,10 +5440,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125457445</v>
+        <v>125451247</v>
       </c>
       <c r="B47" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5469,42 +5452,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>533577</v>
+        <v>533498</v>
       </c>
       <c r="R47" t="n">
-        <v>6885438</v>
+        <v>6885552</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5563,10 +5542,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125454123</v>
+        <v>125450818</v>
       </c>
       <c r="B48" t="n">
-        <v>97147</v>
+        <v>98269</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5575,38 +5554,42 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533490</v>
+        <v>533494</v>
       </c>
       <c r="R48" t="n">
-        <v>6885291</v>
+        <v>6885624</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5665,10 +5648,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125448879</v>
+        <v>125452693</v>
       </c>
       <c r="B49" t="n">
-        <v>98269</v>
+        <v>56226</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5677,30 +5660,31 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5709,10 +5693,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>533558</v>
+        <v>533485</v>
       </c>
       <c r="R49" t="n">
-        <v>6885696</v>
+        <v>6885472</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5771,7 +5755,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125448393</v>
+        <v>125454123</v>
       </c>
       <c r="B50" t="n">
         <v>97147</v>
@@ -5811,10 +5795,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>533568</v>
+        <v>533490</v>
       </c>
       <c r="R50" t="n">
-        <v>6885736</v>
+        <v>6885291</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5873,7 +5857,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125455217</v>
+        <v>125456371</v>
       </c>
       <c r="B51" t="n">
         <v>78947</v>
@@ -5913,10 +5897,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>533571</v>
+        <v>533602</v>
       </c>
       <c r="R51" t="n">
-        <v>6885153</v>
+        <v>6885362</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5975,10 +5959,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125450505</v>
+        <v>125457312</v>
       </c>
       <c r="B52" t="n">
-        <v>80028</v>
+        <v>91166</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5991,39 +5975,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>533526</v>
+        <v>533577</v>
       </c>
       <c r="R52" t="n">
-        <v>6885605</v>
+        <v>6885438</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6082,10 +6061,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125459043</v>
+        <v>125448834</v>
       </c>
       <c r="B53" t="n">
-        <v>57635</v>
+        <v>58001</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6094,20 +6073,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6118,7 +6097,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6127,10 +6106,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533634</v>
+        <v>533571</v>
       </c>
       <c r="R53" t="n">
-        <v>6885654</v>
+        <v>6885716</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6163,11 +6142,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6194,10 +6168,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125449549</v>
+        <v>125448798</v>
       </c>
       <c r="B54" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6206,38 +6180,42 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>533559</v>
+        <v>533560</v>
       </c>
       <c r="R54" t="n">
-        <v>6885649</v>
+        <v>6885711</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6296,7 +6274,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125456221</v>
+        <v>125454035</v>
       </c>
       <c r="B55" t="n">
         <v>78947</v>
@@ -6330,16 +6308,21 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>533478</v>
+        <v>533438</v>
       </c>
       <c r="R55" t="n">
-        <v>6884944</v>
+        <v>6885340</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6398,10 +6381,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125457380</v>
+        <v>125451409</v>
       </c>
       <c r="B56" t="n">
-        <v>91459</v>
+        <v>57635</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6414,43 +6397,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>533577</v>
+        <v>533498</v>
       </c>
       <c r="R56" t="n">
-        <v>6885438</v>
+        <v>6885552</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6483,6 +6462,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall. Både äldre spår och färska</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6509,10 +6493,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125458930</v>
+        <v>125449196</v>
       </c>
       <c r="B57" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6525,34 +6509,43 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>533634</v>
+        <v>533558</v>
       </c>
       <c r="R57" t="n">
-        <v>6885654</v>
+        <v>6885696</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6611,10 +6604,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125452441</v>
+        <v>125456406</v>
       </c>
       <c r="B58" t="n">
-        <v>91184</v>
+        <v>57632</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6627,34 +6620,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>533485</v>
+        <v>533520</v>
       </c>
       <c r="R58" t="n">
-        <v>6885472</v>
+        <v>6885018</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6713,10 +6711,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125455687</v>
+        <v>125456654</v>
       </c>
       <c r="B59" t="n">
-        <v>91166</v>
+        <v>57635</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6729,34 +6727,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>533469</v>
+        <v>533587</v>
       </c>
       <c r="R59" t="n">
-        <v>6885049</v>
+        <v>6885384</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6789,6 +6792,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6815,10 +6823,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125453277</v>
+        <v>125456232</v>
       </c>
       <c r="B60" t="n">
-        <v>57793</v>
+        <v>57635</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6831,39 +6839,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>533421</v>
+        <v>533493</v>
       </c>
       <c r="R60" t="n">
-        <v>6885458</v>
+        <v>6884951</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6896,6 +6904,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Mest äldre spår men öven något färskt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6922,10 +6935,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125455827</v>
+        <v>125454495</v>
       </c>
       <c r="B61" t="n">
-        <v>91166</v>
+        <v>57635</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6938,34 +6951,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>533479</v>
+        <v>533467</v>
       </c>
       <c r="R61" t="n">
-        <v>6884999</v>
+        <v>6885270</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6998,6 +7016,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7024,10 +7047,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125456538</v>
+        <v>125449118</v>
       </c>
       <c r="B62" t="n">
-        <v>57635</v>
+        <v>98269</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7036,43 +7059,42 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>533543</v>
+        <v>533549</v>
       </c>
       <c r="R62" t="n">
-        <v>6885069</v>
+        <v>6885695</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7102,14 +7124,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7136,10 +7163,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125458714</v>
+        <v>125452794</v>
       </c>
       <c r="B63" t="n">
-        <v>57635</v>
+        <v>98269</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7148,43 +7175,42 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>533683</v>
+        <v>533476</v>
       </c>
       <c r="R63" t="n">
-        <v>6885420</v>
+        <v>6885492</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7217,11 +7243,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7248,10 +7269,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125449396</v>
+        <v>125449273</v>
       </c>
       <c r="B64" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7260,28 +7281,32 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
@@ -7350,10 +7375,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125449273</v>
+        <v>125452859</v>
       </c>
       <c r="B65" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7362,42 +7387,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>533550</v>
+        <v>533466</v>
       </c>
       <c r="R65" t="n">
-        <v>6885685</v>
+        <v>6885506</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7456,7 +7477,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125453207</v>
+        <v>125450505</v>
       </c>
       <c r="B66" t="n">
         <v>80028</v>
@@ -7490,16 +7511,21 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>533421</v>
+        <v>533526</v>
       </c>
       <c r="R66" t="n">
-        <v>6885458</v>
+        <v>6885605</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7558,10 +7584,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125451793</v>
+        <v>125449549</v>
       </c>
       <c r="B67" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7570,42 +7596,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>533474</v>
+        <v>533559</v>
       </c>
       <c r="R67" t="n">
-        <v>6885517</v>
+        <v>6885649</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7664,10 +7686,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125450452</v>
+        <v>125451445</v>
       </c>
       <c r="B68" t="n">
-        <v>98269</v>
+        <v>80057</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7676,42 +7698,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533508</v>
+        <v>533474</v>
       </c>
       <c r="R68" t="n">
-        <v>6885633</v>
+        <v>6885569</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7770,10 +7788,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125452660</v>
+        <v>125451954</v>
       </c>
       <c r="B69" t="n">
-        <v>57635</v>
+        <v>56828</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7786,16 +7804,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7803,14 +7821,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -7819,10 +7833,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533535</v>
+        <v>533479</v>
       </c>
       <c r="R69" t="n">
-        <v>6885468</v>
+        <v>6885506</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7881,10 +7895,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125456654</v>
+        <v>125450747</v>
       </c>
       <c r="B70" t="n">
-        <v>57635</v>
+        <v>98290</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7893,31 +7907,30 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -7926,10 +7939,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533587</v>
+        <v>533545</v>
       </c>
       <c r="R70" t="n">
-        <v>6885384</v>
+        <v>6885577</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7962,11 +7975,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7993,10 +8001,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125450235</v>
+        <v>125448326</v>
       </c>
       <c r="B71" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8009,39 +8017,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>533551</v>
+        <v>533568</v>
       </c>
       <c r="R71" t="n">
-        <v>6885632</v>
+        <v>6885736</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8074,11 +8077,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8105,10 +8103,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125450818</v>
+        <v>125448352</v>
       </c>
       <c r="B72" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8117,42 +8115,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>533494</v>
+        <v>533568</v>
       </c>
       <c r="R72" t="n">
-        <v>6885624</v>
+        <v>6885736</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8211,10 +8205,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125456355</v>
+        <v>125452107</v>
       </c>
       <c r="B73" t="n">
-        <v>98269</v>
+        <v>57793</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8223,42 +8217,52 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>533513</v>
+        <v>533485</v>
       </c>
       <c r="R73" t="n">
-        <v>6885005</v>
+        <v>6885472</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8317,10 +8321,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125451751</v>
+        <v>125451578</v>
       </c>
       <c r="B74" t="n">
-        <v>97147</v>
+        <v>98269</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8329,38 +8333,42 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>533503</v>
+        <v>533480</v>
       </c>
       <c r="R74" t="n">
-        <v>6885498</v>
+        <v>6885534</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8419,10 +8427,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125451445</v>
+        <v>125450152</v>
       </c>
       <c r="B75" t="n">
-        <v>80057</v>
+        <v>78947</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8431,25 +8439,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8459,10 +8467,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>533474</v>
+        <v>533539</v>
       </c>
       <c r="R75" t="n">
-        <v>6885569</v>
+        <v>6885645</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8521,10 +8529,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125453817</v>
+        <v>125456035</v>
       </c>
       <c r="B76" t="n">
-        <v>80028</v>
+        <v>91166</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8537,34 +8545,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>533455</v>
+        <v>533444</v>
       </c>
       <c r="R76" t="n">
-        <v>6885379</v>
+        <v>6884916</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8623,10 +8631,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125457133</v>
+        <v>125450188</v>
       </c>
       <c r="B77" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8639,34 +8647,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>533574</v>
+        <v>533539</v>
       </c>
       <c r="R77" t="n">
-        <v>6885404</v>
+        <v>6885634</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8699,6 +8712,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8725,10 +8743,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125456371</v>
+        <v>125456788</v>
       </c>
       <c r="B78" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8737,38 +8755,42 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>533602</v>
+        <v>533556</v>
       </c>
       <c r="R78" t="n">
-        <v>6885362</v>
+        <v>6885155</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8827,10 +8849,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125456250</v>
+        <v>125451692</v>
       </c>
       <c r="B79" t="n">
-        <v>91184</v>
+        <v>98269</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8839,47 +8861,42 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>533602</v>
+        <v>533471</v>
       </c>
       <c r="R79" t="n">
-        <v>6885362</v>
+        <v>6885526</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8938,10 +8955,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125450387</v>
+        <v>125451751</v>
       </c>
       <c r="B80" t="n">
-        <v>78947</v>
+        <v>97147</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8950,25 +8967,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8978,10 +8995,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>533528</v>
+        <v>533503</v>
       </c>
       <c r="R80" t="n">
-        <v>6885627</v>
+        <v>6885498</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9040,10 +9057,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125459017</v>
+        <v>125449765</v>
       </c>
       <c r="B81" t="n">
-        <v>91833</v>
+        <v>78947</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9052,25 +9069,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>898</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9080,10 +9097,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>533634</v>
+        <v>533527</v>
       </c>
       <c r="R81" t="n">
-        <v>6885654</v>
+        <v>6885657</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9142,10 +9159,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125456732</v>
+        <v>125448667</v>
       </c>
       <c r="B82" t="n">
-        <v>57632</v>
+        <v>80028</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9158,39 +9175,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533566</v>
+        <v>533560</v>
       </c>
       <c r="R82" t="n">
-        <v>6885119</v>
+        <v>6885711</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9249,7 +9261,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125456232</v>
+        <v>125449144</v>
       </c>
       <c r="B83" t="n">
         <v>57635</v>
@@ -9285,19 +9297,19 @@
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>533493</v>
+        <v>533538</v>
       </c>
       <c r="R83" t="n">
-        <v>6884951</v>
+        <v>6885703</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9334,7 +9346,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack på tall.  Mest äldre spår men öven något färskt</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9361,10 +9373,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125455201</v>
+        <v>125458930</v>
       </c>
       <c r="B84" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9373,42 +9385,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>533571</v>
+        <v>533634</v>
       </c>
       <c r="R84" t="n">
-        <v>6885153</v>
+        <v>6885654</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9467,10 +9475,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125450671</v>
+        <v>125458140</v>
       </c>
       <c r="B85" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9479,42 +9487,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>533493</v>
+        <v>533574</v>
       </c>
       <c r="R85" t="n">
-        <v>6885612</v>
+        <v>6885198</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9573,10 +9577,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125452693</v>
+        <v>125456221</v>
       </c>
       <c r="B86" t="n">
-        <v>56226</v>
+        <v>78947</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9589,39 +9593,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>533485</v>
+        <v>533478</v>
       </c>
       <c r="R86" t="n">
-        <v>6885472</v>
+        <v>6884944</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9680,10 +9679,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125449765</v>
+        <v>125453495</v>
       </c>
       <c r="B87" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9696,34 +9695,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>533527</v>
+        <v>533487</v>
       </c>
       <c r="R87" t="n">
-        <v>6885657</v>
+        <v>6885398</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9756,6 +9760,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9782,10 +9791,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125450152</v>
+        <v>125458100</v>
       </c>
       <c r="B88" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9794,38 +9803,42 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>533539</v>
+        <v>533578</v>
       </c>
       <c r="R88" t="n">
-        <v>6885645</v>
+        <v>6885205</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9884,10 +9897,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125451247</v>
+        <v>125450058</v>
       </c>
       <c r="B89" t="n">
-        <v>78947</v>
+        <v>98290</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9896,38 +9909,42 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>533498</v>
+        <v>533564</v>
       </c>
       <c r="R89" t="n">
-        <v>6885552</v>
+        <v>6885654</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9986,10 +10003,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125450188</v>
+        <v>125455217</v>
       </c>
       <c r="B90" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10002,39 +10019,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>533539</v>
+        <v>533571</v>
       </c>
       <c r="R90" t="n">
-        <v>6885634</v>
+        <v>6885153</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10067,11 +10079,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10098,10 +10105,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125458100</v>
+        <v>125449396</v>
       </c>
       <c r="B91" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10110,42 +10117,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>533578</v>
+        <v>533550</v>
       </c>
       <c r="R91" t="n">
-        <v>6885205</v>
+        <v>6885685</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10204,10 +10207,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125450718</v>
+        <v>125455687</v>
       </c>
       <c r="B92" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10216,42 +10219,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>533537</v>
+        <v>533469</v>
       </c>
       <c r="R92" t="n">
-        <v>6885571</v>
+        <v>6885049</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10310,10 +10309,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125448667</v>
+        <v>125450637</v>
       </c>
       <c r="B93" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10326,21 +10325,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10350,10 +10349,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>533560</v>
+        <v>533545</v>
       </c>
       <c r="R93" t="n">
-        <v>6885711</v>
+        <v>6885577</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10412,7 +10411,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125449555</v>
+        <v>125453817</v>
       </c>
       <c r="B94" t="n">
         <v>80028</v>
@@ -10452,10 +10451,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>533527</v>
+        <v>533455</v>
       </c>
       <c r="R94" t="n">
-        <v>6885657</v>
+        <v>6885379</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10514,10 +10513,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125449118</v>
+        <v>125453207</v>
       </c>
       <c r="B95" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10526,42 +10525,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>533549</v>
+        <v>533421</v>
       </c>
       <c r="R95" t="n">
-        <v>6885695</v>
+        <v>6885458</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10591,19 +10586,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>12:08</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10630,10 +10615,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125448798</v>
+        <v>125457210</v>
       </c>
       <c r="B96" t="n">
-        <v>98269</v>
+        <v>57635</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10642,42 +10627,43 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>90</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>533560</v>
+        <v>533578</v>
       </c>
       <c r="R96" t="n">
-        <v>6885711</v>
+        <v>6885205</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10710,6 +10696,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10736,10 +10727,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125456251</v>
+        <v>125455421</v>
       </c>
       <c r="B97" t="n">
-        <v>91166</v>
+        <v>57635</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10752,24 +10743,33 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
@@ -10779,7 +10779,7 @@
         <v>533497</v>
       </c>
       <c r="R97" t="n">
-        <v>6884966</v>
+        <v>6885148</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>

--- a/artfynd/A 19766-2025 artfynd.xlsx
+++ b/artfynd/A 19766-2025 artfynd.xlsx
@@ -1193,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125451213</v>
+        <v>125449383</v>
       </c>
       <c r="B7" t="n">
-        <v>98290</v>
+        <v>78947</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,42 +1205,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533490</v>
+        <v>533564</v>
       </c>
       <c r="R7" t="n">
-        <v>6885584</v>
+        <v>6885654</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125450671</v>
+        <v>125454471</v>
       </c>
       <c r="B8" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1311,42 +1307,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533493</v>
+        <v>533467</v>
       </c>
       <c r="R8" t="n">
-        <v>6885612</v>
+        <v>6885270</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125449383</v>
+        <v>125456250</v>
       </c>
       <c r="B9" t="n">
-        <v>78947</v>
+        <v>91184</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,34 +1413,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533564</v>
+        <v>533602</v>
       </c>
       <c r="R9" t="n">
-        <v>6885654</v>
+        <v>6885362</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,10 +1508,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125454471</v>
+        <v>125456251</v>
       </c>
       <c r="B10" t="n">
-        <v>80028</v>
+        <v>91166</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1523,34 +1524,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533467</v>
+        <v>533497</v>
       </c>
       <c r="R10" t="n">
-        <v>6885270</v>
+        <v>6884966</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,10 +1610,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125456250</v>
+        <v>125452337</v>
       </c>
       <c r="B11" t="n">
-        <v>91184</v>
+        <v>78947</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1625,43 +1626,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533602</v>
+        <v>533485</v>
       </c>
       <c r="R11" t="n">
-        <v>6885362</v>
+        <v>6885472</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,10 +1721,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125456251</v>
+        <v>125453918</v>
       </c>
       <c r="B12" t="n">
-        <v>91166</v>
+        <v>80028</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,34 +1737,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533497</v>
+        <v>533477</v>
       </c>
       <c r="R12" t="n">
-        <v>6884966</v>
+        <v>6885329</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,7 +1823,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125452337</v>
+        <v>125450387</v>
       </c>
       <c r="B13" t="n">
         <v>78947</v>
@@ -1855,26 +1856,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533485</v>
+        <v>533528</v>
       </c>
       <c r="R13" t="n">
-        <v>6885472</v>
+        <v>6885627</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1933,10 +1925,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125453918</v>
+        <v>125459017</v>
       </c>
       <c r="B14" t="n">
-        <v>80028</v>
+        <v>91833</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1945,25 +1937,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1973,10 +1965,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533477</v>
+        <v>533634</v>
       </c>
       <c r="R14" t="n">
-        <v>6885329</v>
+        <v>6885654</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2035,10 +2027,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125450387</v>
+        <v>125451213</v>
       </c>
       <c r="B15" t="n">
-        <v>78947</v>
+        <v>98290</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2047,38 +2039,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>533528</v>
+        <v>533490</v>
       </c>
       <c r="R15" t="n">
-        <v>6885627</v>
+        <v>6885584</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125459017</v>
+        <v>125450671</v>
       </c>
       <c r="B16" t="n">
-        <v>91833</v>
+        <v>98269</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2153,34 +2149,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533634</v>
+        <v>533493</v>
       </c>
       <c r="R16" t="n">
-        <v>6885654</v>
+        <v>6885612</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2779,10 +2779,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125457133</v>
+        <v>125455201</v>
       </c>
       <c r="B22" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2791,38 +2791,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533574</v>
+        <v>533571</v>
       </c>
       <c r="R22" t="n">
-        <v>6885404</v>
+        <v>6885153</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,10 +2885,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125452374</v>
+        <v>125457133</v>
       </c>
       <c r="B23" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2897,34 +2901,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533550</v>
+        <v>533574</v>
       </c>
       <c r="R23" t="n">
-        <v>6885458</v>
+        <v>6885404</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2983,10 +2987,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125450235</v>
+        <v>125452374</v>
       </c>
       <c r="B24" t="n">
-        <v>57635</v>
+        <v>91166</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2999,39 +3003,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533551</v>
+        <v>533550</v>
       </c>
       <c r="R24" t="n">
-        <v>6885632</v>
+        <v>6885458</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3064,11 +3063,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3095,10 +3089,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125453277</v>
+        <v>125450235</v>
       </c>
       <c r="B25" t="n">
-        <v>57793</v>
+        <v>57635</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3111,27 +3105,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3140,10 +3134,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533421</v>
+        <v>533551</v>
       </c>
       <c r="R25" t="n">
-        <v>6885458</v>
+        <v>6885632</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3176,6 +3170,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3202,10 +3201,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125449821</v>
+        <v>125453277</v>
       </c>
       <c r="B26" t="n">
-        <v>98269</v>
+        <v>57793</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3214,30 +3213,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533559</v>
+        <v>533421</v>
       </c>
       <c r="R26" t="n">
-        <v>6885649</v>
+        <v>6885458</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3308,7 +3308,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125455201</v>
+        <v>125449821</v>
       </c>
       <c r="B27" t="n">
         <v>98269</v>
@@ -3343,19 +3343,19 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533571</v>
+        <v>533559</v>
       </c>
       <c r="R27" t="n">
-        <v>6885153</v>
+        <v>6885649</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3941,10 +3941,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125456968</v>
+        <v>125456355</v>
       </c>
       <c r="B33" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3953,38 +3953,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533562</v>
+        <v>533513</v>
       </c>
       <c r="R33" t="n">
-        <v>6885408</v>
+        <v>6885005</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4043,10 +4047,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125452441</v>
+        <v>125449337</v>
       </c>
       <c r="B34" t="n">
-        <v>91184</v>
+        <v>91166</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4059,21 +4063,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4083,10 +4087,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533485</v>
+        <v>533564</v>
       </c>
       <c r="R34" t="n">
-        <v>6885472</v>
+        <v>6885654</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4145,10 +4149,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125450555</v>
+        <v>125456968</v>
       </c>
       <c r="B35" t="n">
-        <v>78947</v>
+        <v>91166</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4161,34 +4165,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533508</v>
+        <v>533562</v>
       </c>
       <c r="R35" t="n">
-        <v>6885633</v>
+        <v>6885408</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4247,10 +4251,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125456893</v>
+        <v>125452441</v>
       </c>
       <c r="B36" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4263,48 +4267,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533561</v>
+        <v>533485</v>
       </c>
       <c r="R36" t="n">
-        <v>6885192</v>
+        <v>6885472</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4363,10 +4353,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125449337</v>
+        <v>125450555</v>
       </c>
       <c r="B37" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4379,21 +4369,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4403,10 +4393,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533564</v>
+        <v>533508</v>
       </c>
       <c r="R37" t="n">
-        <v>6885654</v>
+        <v>6885633</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4465,10 +4455,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125456355</v>
+        <v>125456893</v>
       </c>
       <c r="B38" t="n">
-        <v>98269</v>
+        <v>57635</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4477,30 +4467,40 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533513</v>
+        <v>533561</v>
       </c>
       <c r="R38" t="n">
-        <v>6885005</v>
+        <v>6885192</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4571,10 +4571,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125450898</v>
+        <v>125448879</v>
       </c>
       <c r="B39" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4583,31 +4583,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4616,10 +4615,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533518</v>
+        <v>533558</v>
       </c>
       <c r="R39" t="n">
-        <v>6885534</v>
+        <v>6885696</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,10 +4677,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125457380</v>
+        <v>125450898</v>
       </c>
       <c r="B40" t="n">
-        <v>91459</v>
+        <v>80028</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4694,43 +4693,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533577</v>
+        <v>533518</v>
       </c>
       <c r="R40" t="n">
-        <v>6885438</v>
+        <v>6885534</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4789,10 +4784,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125455042</v>
+        <v>125457380</v>
       </c>
       <c r="B41" t="n">
-        <v>57635</v>
+        <v>91459</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4805,27 +4800,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4834,10 +4833,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533556</v>
+        <v>533577</v>
       </c>
       <c r="R41" t="n">
-        <v>6885155</v>
+        <v>6885438</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4870,11 +4869,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4901,7 +4895,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125456823</v>
+        <v>125455042</v>
       </c>
       <c r="B42" t="n">
         <v>57635</v>
@@ -4946,10 +4940,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533580</v>
+        <v>533556</v>
       </c>
       <c r="R42" t="n">
-        <v>6885391</v>
+        <v>6885155</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4986,7 +4980,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5013,10 +5007,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125448879</v>
+        <v>125456823</v>
       </c>
       <c r="B43" t="n">
-        <v>98269</v>
+        <v>57635</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5025,42 +5019,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533558</v>
+        <v>533580</v>
       </c>
       <c r="R43" t="n">
-        <v>6885696</v>
+        <v>6885391</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5093,6 +5088,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5226,10 +5226,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125456538</v>
+        <v>125455827</v>
       </c>
       <c r="B45" t="n">
-        <v>57635</v>
+        <v>91166</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5242,39 +5242,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533543</v>
+        <v>533479</v>
       </c>
       <c r="R45" t="n">
-        <v>6885069</v>
+        <v>6884999</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5307,11 +5302,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5338,10 +5328,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125455827</v>
+        <v>125451247</v>
       </c>
       <c r="B46" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5354,34 +5344,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533479</v>
+        <v>533498</v>
       </c>
       <c r="R46" t="n">
-        <v>6884999</v>
+        <v>6885552</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5440,10 +5430,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125451247</v>
+        <v>125456538</v>
       </c>
       <c r="B47" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5456,34 +5446,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>533498</v>
+        <v>533543</v>
       </c>
       <c r="R47" t="n">
-        <v>6885552</v>
+        <v>6885069</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5516,6 +5511,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5648,10 +5648,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125452693</v>
+        <v>125456371</v>
       </c>
       <c r="B49" t="n">
-        <v>56226</v>
+        <v>78947</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5664,39 +5664,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>533485</v>
+        <v>533602</v>
       </c>
       <c r="R49" t="n">
-        <v>6885472</v>
+        <v>6885362</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5755,10 +5750,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125454123</v>
+        <v>125457312</v>
       </c>
       <c r="B50" t="n">
-        <v>97147</v>
+        <v>91166</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5767,38 +5762,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>533490</v>
+        <v>533577</v>
       </c>
       <c r="R50" t="n">
-        <v>6885291</v>
+        <v>6885438</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5857,10 +5852,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125456371</v>
+        <v>125452693</v>
       </c>
       <c r="B51" t="n">
-        <v>78947</v>
+        <v>56226</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5873,34 +5868,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>533602</v>
+        <v>533485</v>
       </c>
       <c r="R51" t="n">
-        <v>6885362</v>
+        <v>6885472</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5959,10 +5959,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125457312</v>
+        <v>125454123</v>
       </c>
       <c r="B52" t="n">
-        <v>91166</v>
+        <v>97147</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5971,38 +5971,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>533577</v>
+        <v>533490</v>
       </c>
       <c r="R52" t="n">
-        <v>6885438</v>
+        <v>6885291</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7269,10 +7269,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125449273</v>
+        <v>125449549</v>
       </c>
       <c r="B64" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7281,42 +7281,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>533550</v>
+        <v>533559</v>
       </c>
       <c r="R64" t="n">
-        <v>6885685</v>
+        <v>6885649</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7375,10 +7371,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125452859</v>
+        <v>125449273</v>
       </c>
       <c r="B65" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7387,38 +7383,42 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>533466</v>
+        <v>533550</v>
       </c>
       <c r="R65" t="n">
-        <v>6885506</v>
+        <v>6885685</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7477,10 +7477,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125450505</v>
+        <v>125452859</v>
       </c>
       <c r="B66" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7493,39 +7493,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>533526</v>
+        <v>533466</v>
       </c>
       <c r="R66" t="n">
-        <v>6885605</v>
+        <v>6885506</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7584,7 +7579,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125449549</v>
+        <v>125450505</v>
       </c>
       <c r="B67" t="n">
         <v>80028</v>
@@ -7618,16 +7613,21 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>533559</v>
+        <v>533526</v>
       </c>
       <c r="R67" t="n">
-        <v>6885649</v>
+        <v>6885605</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8743,10 +8743,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125456788</v>
+        <v>125449765</v>
       </c>
       <c r="B78" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8755,42 +8755,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>533556</v>
+        <v>533527</v>
       </c>
       <c r="R78" t="n">
-        <v>6885155</v>
+        <v>6885657</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8849,10 +8845,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125451692</v>
+        <v>125448667</v>
       </c>
       <c r="B79" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8861,42 +8857,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>533471</v>
+        <v>533560</v>
       </c>
       <c r="R79" t="n">
-        <v>6885526</v>
+        <v>6885711</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8955,10 +8947,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125451751</v>
+        <v>125449144</v>
       </c>
       <c r="B80" t="n">
-        <v>97147</v>
+        <v>57635</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8967,38 +8959,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>533503</v>
+        <v>533538</v>
       </c>
       <c r="R80" t="n">
-        <v>6885498</v>
+        <v>6885703</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9031,6 +9028,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9057,10 +9059,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125449765</v>
+        <v>125458930</v>
       </c>
       <c r="B81" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9073,21 +9075,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9097,10 +9099,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>533527</v>
+        <v>533634</v>
       </c>
       <c r="R81" t="n">
-        <v>6885657</v>
+        <v>6885654</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9159,10 +9161,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125448667</v>
+        <v>125458140</v>
       </c>
       <c r="B82" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9175,34 +9177,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533560</v>
+        <v>533574</v>
       </c>
       <c r="R82" t="n">
-        <v>6885711</v>
+        <v>6885198</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9261,10 +9263,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125449144</v>
+        <v>125456221</v>
       </c>
       <c r="B83" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9277,39 +9279,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>533538</v>
+        <v>533478</v>
       </c>
       <c r="R83" t="n">
-        <v>6885703</v>
+        <v>6884944</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9342,11 +9339,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9373,10 +9365,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125458930</v>
+        <v>125453495</v>
       </c>
       <c r="B84" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9389,34 +9381,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>533634</v>
+        <v>533487</v>
       </c>
       <c r="R84" t="n">
-        <v>6885654</v>
+        <v>6885398</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9449,6 +9446,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9475,10 +9477,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125458140</v>
+        <v>125451751</v>
       </c>
       <c r="B85" t="n">
-        <v>78947</v>
+        <v>97147</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9487,38 +9489,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>533574</v>
+        <v>533503</v>
       </c>
       <c r="R85" t="n">
-        <v>6885198</v>
+        <v>6885498</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9577,10 +9579,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125456221</v>
+        <v>125456788</v>
       </c>
       <c r="B86" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9589,38 +9591,42 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>533478</v>
+        <v>533556</v>
       </c>
       <c r="R86" t="n">
-        <v>6884944</v>
+        <v>6885155</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9679,10 +9685,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125453495</v>
+        <v>125451692</v>
       </c>
       <c r="B87" t="n">
-        <v>57635</v>
+        <v>98269</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9691,31 +9697,30 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>22</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -9724,10 +9729,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>533487</v>
+        <v>533471</v>
       </c>
       <c r="R87" t="n">
-        <v>6885398</v>
+        <v>6885526</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9760,11 +9765,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 19766-2025 artfynd.xlsx
+++ b/artfynd/A 19766-2025 artfynd.xlsx
@@ -1193,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125449383</v>
+        <v>125451213</v>
       </c>
       <c r="B7" t="n">
-        <v>78947</v>
+        <v>98290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,38 +1205,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533564</v>
+        <v>533490</v>
       </c>
       <c r="R7" t="n">
-        <v>6885654</v>
+        <v>6885584</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,10 +1299,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125454471</v>
+        <v>125450671</v>
       </c>
       <c r="B8" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1307,38 +1311,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533467</v>
+        <v>533493</v>
       </c>
       <c r="R8" t="n">
-        <v>6885270</v>
+        <v>6885612</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,10 +1405,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125456250</v>
+        <v>125449383</v>
       </c>
       <c r="B9" t="n">
-        <v>91184</v>
+        <v>78947</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1413,43 +1421,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533602</v>
+        <v>533564</v>
       </c>
       <c r="R9" t="n">
-        <v>6885362</v>
+        <v>6885654</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1508,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125456251</v>
+        <v>125454471</v>
       </c>
       <c r="B10" t="n">
-        <v>91166</v>
+        <v>80028</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1524,34 +1523,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533497</v>
+        <v>533467</v>
       </c>
       <c r="R10" t="n">
-        <v>6884966</v>
+        <v>6885270</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1610,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125452337</v>
+        <v>125456250</v>
       </c>
       <c r="B11" t="n">
-        <v>78947</v>
+        <v>91184</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1626,43 +1625,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533485</v>
+        <v>533602</v>
       </c>
       <c r="R11" t="n">
-        <v>6885472</v>
+        <v>6885362</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1721,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125453918</v>
+        <v>125456251</v>
       </c>
       <c r="B12" t="n">
-        <v>80028</v>
+        <v>91166</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1737,34 +1736,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533477</v>
+        <v>533497</v>
       </c>
       <c r="R12" t="n">
-        <v>6885329</v>
+        <v>6884966</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,7 +1822,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125450387</v>
+        <v>125452337</v>
       </c>
       <c r="B13" t="n">
         <v>78947</v>
@@ -1856,17 +1855,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533528</v>
+        <v>533485</v>
       </c>
       <c r="R13" t="n">
-        <v>6885627</v>
+        <v>6885472</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,10 +1933,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125459017</v>
+        <v>125453918</v>
       </c>
       <c r="B14" t="n">
-        <v>91833</v>
+        <v>80028</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1937,25 +1945,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>898</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1965,10 +1973,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533634</v>
+        <v>533477</v>
       </c>
       <c r="R14" t="n">
-        <v>6885654</v>
+        <v>6885329</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2027,10 +2035,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125451213</v>
+        <v>125450387</v>
       </c>
       <c r="B15" t="n">
-        <v>98290</v>
+        <v>78947</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2039,42 +2047,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>533490</v>
+        <v>533528</v>
       </c>
       <c r="R15" t="n">
-        <v>6885584</v>
+        <v>6885627</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,10 +2137,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125450671</v>
+        <v>125459017</v>
       </c>
       <c r="B16" t="n">
-        <v>98269</v>
+        <v>91833</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2149,38 +2153,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>898</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533493</v>
+        <v>533634</v>
       </c>
       <c r="R16" t="n">
-        <v>6885612</v>
+        <v>6885654</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2779,7 +2779,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125455201</v>
+        <v>125449821</v>
       </c>
       <c r="B22" t="n">
         <v>98269</v>
@@ -2814,19 +2814,19 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533571</v>
+        <v>533559</v>
       </c>
       <c r="R22" t="n">
-        <v>6885153</v>
+        <v>6885649</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3089,10 +3089,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125450235</v>
+        <v>125453277</v>
       </c>
       <c r="B25" t="n">
-        <v>57635</v>
+        <v>57793</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3105,27 +3105,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3134,10 +3134,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533551</v>
+        <v>533421</v>
       </c>
       <c r="R25" t="n">
-        <v>6885632</v>
+        <v>6885458</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3170,11 +3170,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3201,10 +3196,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125453277</v>
+        <v>125450235</v>
       </c>
       <c r="B26" t="n">
-        <v>57793</v>
+        <v>57635</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3217,27 +3212,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3246,10 +3241,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533421</v>
+        <v>533551</v>
       </c>
       <c r="R26" t="n">
-        <v>6885458</v>
+        <v>6885632</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3282,6 +3277,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3308,7 +3308,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125449821</v>
+        <v>125455201</v>
       </c>
       <c r="B27" t="n">
         <v>98269</v>
@@ -3343,19 +3343,19 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533559</v>
+        <v>533571</v>
       </c>
       <c r="R27" t="n">
-        <v>6885649</v>
+        <v>6885153</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4571,10 +4571,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125448879</v>
+        <v>125450898</v>
       </c>
       <c r="B39" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4583,30 +4583,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4615,10 +4616,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533558</v>
+        <v>533518</v>
       </c>
       <c r="R39" t="n">
-        <v>6885696</v>
+        <v>6885534</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4677,10 +4678,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125450898</v>
+        <v>125457380</v>
       </c>
       <c r="B40" t="n">
-        <v>80028</v>
+        <v>91459</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4693,39 +4694,43 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533518</v>
+        <v>533577</v>
       </c>
       <c r="R40" t="n">
-        <v>6885534</v>
+        <v>6885438</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4784,10 +4789,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125457380</v>
+        <v>125455042</v>
       </c>
       <c r="B41" t="n">
-        <v>91459</v>
+        <v>57635</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4800,31 +4805,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4833,10 +4834,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533577</v>
+        <v>533556</v>
       </c>
       <c r="R41" t="n">
-        <v>6885438</v>
+        <v>6885155</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4869,6 +4870,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4895,7 +4901,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125455042</v>
+        <v>125456823</v>
       </c>
       <c r="B42" t="n">
         <v>57635</v>
@@ -4940,10 +4946,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533556</v>
+        <v>533580</v>
       </c>
       <c r="R42" t="n">
-        <v>6885155</v>
+        <v>6885391</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4980,7 +4986,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5007,10 +5013,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125456823</v>
+        <v>125448879</v>
       </c>
       <c r="B43" t="n">
-        <v>57635</v>
+        <v>98269</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5019,43 +5025,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533580</v>
+        <v>533558</v>
       </c>
       <c r="R43" t="n">
-        <v>6885391</v>
+        <v>6885696</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5088,11 +5093,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -7686,10 +7686,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125451445</v>
+        <v>125450747</v>
       </c>
       <c r="B68" t="n">
-        <v>80057</v>
+        <v>98290</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7702,34 +7702,38 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533474</v>
+        <v>533545</v>
       </c>
       <c r="R68" t="n">
-        <v>6885569</v>
+        <v>6885577</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7788,10 +7792,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125451954</v>
+        <v>125451445</v>
       </c>
       <c r="B69" t="n">
-        <v>56828</v>
+        <v>80057</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7800,43 +7804,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533479</v>
+        <v>533474</v>
       </c>
       <c r="R69" t="n">
-        <v>6885506</v>
+        <v>6885569</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7895,10 +7894,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125450747</v>
+        <v>125451954</v>
       </c>
       <c r="B70" t="n">
-        <v>98290</v>
+        <v>56828</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7907,30 +7906,31 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>102612</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -7939,10 +7939,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533545</v>
+        <v>533479</v>
       </c>
       <c r="R70" t="n">
-        <v>6885577</v>
+        <v>6885506</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 19766-2025 artfynd.xlsx
+++ b/artfynd/A 19766-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125452107</v>
+        <v>125449421</v>
       </c>
       <c r="B2" t="n">
-        <v>57811</v>
+        <v>91220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,48 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533485</v>
+        <v>533564</v>
       </c>
       <c r="R2" t="n">
-        <v>6885472</v>
+        <v>6885654</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,37 +772,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125450747</v>
+        <v>125454035</v>
       </c>
       <c r="B3" t="n">
-        <v>98345</v>
+        <v>78967</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533545</v>
+        <v>533438</v>
       </c>
       <c r="R3" t="n">
-        <v>6885577</v>
+        <v>6885340</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125449421</v>
+        <v>125452441</v>
       </c>
       <c r="B4" t="n">
-        <v>91220</v>
+        <v>91238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -922,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533564</v>
+        <v>533485</v>
       </c>
       <c r="R4" t="n">
-        <v>6885654</v>
+        <v>6885472</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125454035</v>
+        <v>125454495</v>
       </c>
       <c r="B5" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,27 +982,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1024,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533438</v>
+        <v>533467</v>
       </c>
       <c r="R5" t="n">
-        <v>6885340</v>
+        <v>6885270</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,6 +1047,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125452441</v>
+        <v>125452107</v>
       </c>
       <c r="B6" t="n">
-        <v>91238</v>
+        <v>57811</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1097,24 +1089,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
@@ -1183,38 +1189,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125454495</v>
+        <v>125450747</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>98345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1223,10 +1228,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533467</v>
+        <v>533545</v>
       </c>
       <c r="R7" t="n">
-        <v>6885270</v>
+        <v>6885577</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,11 +1264,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1290,38 +1290,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125458714</v>
+        <v>125455201</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>98324</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>200</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1330,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533683</v>
+        <v>533571</v>
       </c>
       <c r="R8" t="n">
-        <v>6885420</v>
+        <v>6885153</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,11 +1365,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,7 +1391,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125455042</v>
+        <v>125458714</v>
       </c>
       <c r="B9" t="n">
         <v>57651</v>
@@ -1437,10 +1431,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533556</v>
+        <v>533683</v>
       </c>
       <c r="R9" t="n">
-        <v>6885155</v>
+        <v>6885420</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1477,7 +1471,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1504,37 +1498,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125455201</v>
+        <v>125455042</v>
       </c>
       <c r="B10" t="n">
-        <v>98324</v>
+        <v>57651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>200</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1543,10 +1538,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533571</v>
+        <v>533556</v>
       </c>
       <c r="R10" t="n">
-        <v>6885153</v>
+        <v>6885155</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1579,6 +1574,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -3305,50 +3305,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125457210</v>
+        <v>125449273</v>
       </c>
       <c r="B28" t="n">
-        <v>57651</v>
+        <v>98324</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>37</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533578</v>
+        <v>533550</v>
       </c>
       <c r="R28" t="n">
-        <v>6885205</v>
+        <v>6885685</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3381,11 +3380,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3412,7 +3406,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125456654</v>
+        <v>125457210</v>
       </c>
       <c r="B29" t="n">
         <v>57651</v>
@@ -3448,14 +3442,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533587</v>
+        <v>533578</v>
       </c>
       <c r="R29" t="n">
-        <v>6885384</v>
+        <v>6885205</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3492,7 +3486,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3519,7 +3513,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125455421</v>
+        <v>125456654</v>
       </c>
       <c r="B30" t="n">
         <v>57651</v>
@@ -3547,26 +3541,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533497</v>
+        <v>533587</v>
       </c>
       <c r="R30" t="n">
-        <v>6885148</v>
+        <v>6885384</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3599,6 +3589,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3625,37 +3620,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125457445</v>
+        <v>125455421</v>
       </c>
       <c r="B31" t="n">
-        <v>98324</v>
+        <v>57651</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3664,10 +3664,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533577</v>
+        <v>533497</v>
       </c>
       <c r="R31" t="n">
-        <v>6885438</v>
+        <v>6885148</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3726,37 +3726,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125451793</v>
+        <v>125451213</v>
       </c>
       <c r="B32" t="n">
-        <v>98324</v>
+        <v>98345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533474</v>
+        <v>533490</v>
       </c>
       <c r="R32" t="n">
-        <v>6885517</v>
+        <v>6885584</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3827,45 +3827,49 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125448667</v>
+        <v>125457445</v>
       </c>
       <c r="B33" t="n">
-        <v>80070</v>
+        <v>98324</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533560</v>
+        <v>533577</v>
       </c>
       <c r="R33" t="n">
-        <v>6885711</v>
+        <v>6885438</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3924,37 +3928,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125451213</v>
+        <v>125451793</v>
       </c>
       <c r="B34" t="n">
-        <v>98345</v>
+        <v>98324</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3963,10 +3967,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533490</v>
+        <v>533474</v>
       </c>
       <c r="R34" t="n">
-        <v>6885584</v>
+        <v>6885517</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4025,49 +4029,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125449273</v>
+        <v>125448667</v>
       </c>
       <c r="B35" t="n">
-        <v>98324</v>
+        <v>80070</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533550</v>
+        <v>533560</v>
       </c>
       <c r="R35" t="n">
-        <v>6885685</v>
+        <v>6885711</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4324,10 +4324,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125456221</v>
+        <v>125456538</v>
       </c>
       <c r="B38" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4335,34 +4335,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533478</v>
+        <v>533543</v>
       </c>
       <c r="R38" t="n">
-        <v>6884944</v>
+        <v>6885069</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4395,6 +4400,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4421,7 +4431,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125450387</v>
+        <v>125456221</v>
       </c>
       <c r="B39" t="n">
         <v>78967</v>
@@ -4452,14 +4462,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533528</v>
+        <v>533478</v>
       </c>
       <c r="R39" t="n">
-        <v>6885627</v>
+        <v>6884944</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4518,10 +4528,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125456538</v>
+        <v>125450387</v>
       </c>
       <c r="B40" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4529,39 +4539,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533543</v>
+        <v>533528</v>
       </c>
       <c r="R40" t="n">
-        <v>6885069</v>
+        <v>6885627</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4594,11 +4599,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4625,49 +4625,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125451578</v>
+        <v>125448393</v>
       </c>
       <c r="B41" t="n">
-        <v>98324</v>
+        <v>97202</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533480</v>
+        <v>533568</v>
       </c>
       <c r="R41" t="n">
-        <v>6885534</v>
+        <v>6885736</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4726,45 +4722,49 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125448393</v>
+        <v>125451578</v>
       </c>
       <c r="B42" t="n">
-        <v>97202</v>
+        <v>98324</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533568</v>
+        <v>533480</v>
       </c>
       <c r="R42" t="n">
-        <v>6885736</v>
+        <v>6885534</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -7425,37 +7425,38 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125452794</v>
+        <v>125450235</v>
       </c>
       <c r="B69" t="n">
-        <v>98324</v>
+        <v>57651</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -7464,10 +7465,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533476</v>
+        <v>533551</v>
       </c>
       <c r="R69" t="n">
-        <v>6885492</v>
+        <v>6885632</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7500,6 +7501,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7526,38 +7532,37 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125450235</v>
+        <v>125452794</v>
       </c>
       <c r="B70" t="n">
-        <v>57651</v>
+        <v>98324</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -7566,10 +7571,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533551</v>
+        <v>533476</v>
       </c>
       <c r="R70" t="n">
-        <v>6885632</v>
+        <v>6885492</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7602,11 +7607,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8142,10 +8142,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125450898</v>
+        <v>125456406</v>
       </c>
       <c r="B76" t="n">
-        <v>80070</v>
+        <v>57648</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8153,39 +8153,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>533518</v>
+        <v>533520</v>
       </c>
       <c r="R76" t="n">
-        <v>6885534</v>
+        <v>6885018</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8244,10 +8244,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125456406</v>
+        <v>125450898</v>
       </c>
       <c r="B77" t="n">
-        <v>57648</v>
+        <v>80070</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8255,39 +8255,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>533520</v>
+        <v>533518</v>
       </c>
       <c r="R77" t="n">
-        <v>6885018</v>
+        <v>6885534</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8346,50 +8346,49 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125459043</v>
+        <v>125458100</v>
       </c>
       <c r="B78" t="n">
-        <v>57651</v>
+        <v>98324</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>533634</v>
+        <v>533578</v>
       </c>
       <c r="R78" t="n">
-        <v>6885654</v>
+        <v>6885205</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8422,11 +8421,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8453,32 +8447,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125454123</v>
+        <v>125453817</v>
       </c>
       <c r="B79" t="n">
-        <v>97202</v>
+        <v>80070</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8488,10 +8482,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>533490</v>
+        <v>533455</v>
       </c>
       <c r="R79" t="n">
-        <v>6885291</v>
+        <v>6885379</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8550,10 +8544,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125453817</v>
+        <v>125456371</v>
       </c>
       <c r="B80" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8561,34 +8555,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>533455</v>
+        <v>533602</v>
       </c>
       <c r="R80" t="n">
-        <v>6885379</v>
+        <v>6885362</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8647,10 +8641,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125456371</v>
+        <v>125455827</v>
       </c>
       <c r="B81" t="n">
-        <v>78967</v>
+        <v>91220</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8658,21 +8652,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8682,10 +8676,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>533602</v>
+        <v>533479</v>
       </c>
       <c r="R81" t="n">
-        <v>6885362</v>
+        <v>6884999</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8744,10 +8738,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125455827</v>
+        <v>125459043</v>
       </c>
       <c r="B82" t="n">
-        <v>91220</v>
+        <v>57651</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8755,34 +8749,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533479</v>
+        <v>533634</v>
       </c>
       <c r="R82" t="n">
-        <v>6884999</v>
+        <v>6885654</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8815,6 +8814,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8841,49 +8845,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125458100</v>
+        <v>125454123</v>
       </c>
       <c r="B83" t="n">
-        <v>98324</v>
+        <v>97202</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>533578</v>
+        <v>533490</v>
       </c>
       <c r="R83" t="n">
-        <v>6885205</v>
+        <v>6885291</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>

--- a/artfynd/A 19766-2025 artfynd.xlsx
+++ b/artfynd/A 19766-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125449421</v>
+        <v>125450747</v>
       </c>
       <c r="B2" t="n">
-        <v>91220</v>
+        <v>98352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533564</v>
+        <v>533545</v>
       </c>
       <c r="R2" t="n">
-        <v>6885654</v>
+        <v>6885577</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -877,7 +881,7 @@
         <v>125452441</v>
       </c>
       <c r="B4" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125454495</v>
+        <v>125449421</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>91227</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,39 +986,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533467</v>
+        <v>533564</v>
       </c>
       <c r="R5" t="n">
-        <v>6885270</v>
+        <v>6885654</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,11 +1046,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125452107</v>
+        <v>125454495</v>
       </c>
       <c r="B6" t="n">
-        <v>57811</v>
+        <v>57651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,36 +1083,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1127,10 +1112,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533485</v>
+        <v>533467</v>
       </c>
       <c r="R6" t="n">
-        <v>6885472</v>
+        <v>6885270</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,6 +1148,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,37 +1179,47 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125450747</v>
+        <v>125452107</v>
       </c>
       <c r="B7" t="n">
-        <v>98345</v>
+        <v>57811</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533545</v>
+        <v>533485</v>
       </c>
       <c r="R7" t="n">
-        <v>6885577</v>
+        <v>6885472</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,7 +1293,7 @@
         <v>125455201</v>
       </c>
       <c r="B8" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1896,37 +1896,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125450058</v>
+        <v>125449144</v>
       </c>
       <c r="B14" t="n">
-        <v>98345</v>
+        <v>57651</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1935,10 +1936,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533564</v>
+        <v>533538</v>
       </c>
       <c r="R14" t="n">
-        <v>6885654</v>
+        <v>6885703</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1971,6 +1972,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2104,38 +2110,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125449144</v>
+        <v>125450058</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>98352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2144,10 +2149,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533538</v>
+        <v>533564</v>
       </c>
       <c r="R16" t="n">
-        <v>6885703</v>
+        <v>6885654</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2180,11 +2185,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2214,7 +2214,7 @@
         <v>125448798</v>
       </c>
       <c r="B17" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2312,49 +2312,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125449821</v>
+        <v>125448326</v>
       </c>
       <c r="B18" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>533559</v>
+        <v>533568</v>
       </c>
       <c r="R18" t="n">
-        <v>6885649</v>
+        <v>6885736</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2413,49 +2409,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125449118</v>
+        <v>125449383</v>
       </c>
       <c r="B19" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>533549</v>
+        <v>533564</v>
       </c>
       <c r="R19" t="n">
-        <v>6885695</v>
+        <v>6885654</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2485,19 +2477,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2524,10 +2506,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125452738</v>
+        <v>125449396</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2535,21 +2517,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2559,10 +2541,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>533500</v>
+        <v>533550</v>
       </c>
       <c r="R20" t="n">
-        <v>6885440</v>
+        <v>6885685</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2621,45 +2603,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125452859</v>
+        <v>125449821</v>
       </c>
       <c r="B21" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>533466</v>
+        <v>533559</v>
       </c>
       <c r="R21" t="n">
-        <v>6885506</v>
+        <v>6885649</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2718,45 +2704,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125456251</v>
+        <v>125449118</v>
       </c>
       <c r="B22" t="n">
-        <v>91220</v>
+        <v>98331</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533497</v>
+        <v>533549</v>
       </c>
       <c r="R22" t="n">
-        <v>6884966</v>
+        <v>6885695</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2786,9 +2776,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2815,10 +2815,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125453277</v>
+        <v>125452738</v>
       </c>
       <c r="B23" t="n">
-        <v>57811</v>
+        <v>78967</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2826,39 +2826,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533421</v>
+        <v>533500</v>
       </c>
       <c r="R23" t="n">
-        <v>6885458</v>
+        <v>6885440</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2917,45 +2912,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125451751</v>
+        <v>125456251</v>
       </c>
       <c r="B24" t="n">
-        <v>97202</v>
+        <v>91227</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533503</v>
+        <v>533497</v>
       </c>
       <c r="R24" t="n">
-        <v>6885498</v>
+        <v>6884966</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3014,7 +3009,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125448326</v>
+        <v>125452859</v>
       </c>
       <c r="B25" t="n">
         <v>78967</v>
@@ -3049,10 +3044,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533568</v>
+        <v>533466</v>
       </c>
       <c r="R25" t="n">
-        <v>6885736</v>
+        <v>6885506</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3111,10 +3106,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125449383</v>
+        <v>125453277</v>
       </c>
       <c r="B26" t="n">
-        <v>78967</v>
+        <v>57811</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3122,34 +3117,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533564</v>
+        <v>533421</v>
       </c>
       <c r="R26" t="n">
-        <v>6885654</v>
+        <v>6885458</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3208,32 +3208,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125449396</v>
+        <v>125451751</v>
       </c>
       <c r="B27" t="n">
-        <v>80070</v>
+        <v>97209</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533550</v>
+        <v>533503</v>
       </c>
       <c r="R27" t="n">
-        <v>6885685</v>
+        <v>6885498</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3305,10 +3305,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125449273</v>
+        <v>125457445</v>
       </c>
       <c r="B28" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3340,14 +3340,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533550</v>
+        <v>533577</v>
       </c>
       <c r="R28" t="n">
-        <v>6885685</v>
+        <v>6885438</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3406,50 +3406,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125457210</v>
+        <v>125451793</v>
       </c>
       <c r="B29" t="n">
-        <v>57651</v>
+        <v>98331</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>200</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533578</v>
+        <v>533474</v>
       </c>
       <c r="R29" t="n">
-        <v>6885205</v>
+        <v>6885517</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3482,11 +3481,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3513,10 +3507,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125456654</v>
+        <v>125448667</v>
       </c>
       <c r="B30" t="n">
-        <v>57651</v>
+        <v>80070</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3524,39 +3518,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533587</v>
+        <v>533560</v>
       </c>
       <c r="R30" t="n">
-        <v>6885384</v>
+        <v>6885711</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3589,11 +3578,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3620,7 +3604,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125455421</v>
+        <v>125457210</v>
       </c>
       <c r="B31" t="n">
         <v>57651</v>
@@ -3648,14 +3632,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3664,10 +3644,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533497</v>
+        <v>533578</v>
       </c>
       <c r="R31" t="n">
-        <v>6885148</v>
+        <v>6885205</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3700,6 +3680,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3726,37 +3711,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125451213</v>
+        <v>125456654</v>
       </c>
       <c r="B32" t="n">
-        <v>98345</v>
+        <v>57651</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3765,10 +3751,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533490</v>
+        <v>533587</v>
       </c>
       <c r="R32" t="n">
-        <v>6885584</v>
+        <v>6885384</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3801,6 +3787,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3827,37 +3818,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125457445</v>
+        <v>125455421</v>
       </c>
       <c r="B33" t="n">
-        <v>98324</v>
+        <v>57651</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3866,10 +3862,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533577</v>
+        <v>533497</v>
       </c>
       <c r="R33" t="n">
-        <v>6885438</v>
+        <v>6885148</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3928,37 +3924,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125451793</v>
+        <v>125451213</v>
       </c>
       <c r="B34" t="n">
-        <v>98324</v>
+        <v>98352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3967,10 +3963,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533474</v>
+        <v>533490</v>
       </c>
       <c r="R34" t="n">
-        <v>6885517</v>
+        <v>6885584</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4029,45 +4025,49 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125448667</v>
+        <v>125449273</v>
       </c>
       <c r="B35" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533560</v>
+        <v>533550</v>
       </c>
       <c r="R35" t="n">
-        <v>6885711</v>
+        <v>6885685</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4126,49 +4126,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125450818</v>
+        <v>125450637</v>
       </c>
       <c r="B36" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533494</v>
+        <v>533545</v>
       </c>
       <c r="R36" t="n">
-        <v>6885624</v>
+        <v>6885577</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4227,45 +4223,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125450637</v>
+        <v>125450818</v>
       </c>
       <c r="B37" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533545</v>
+        <v>533494</v>
       </c>
       <c r="R37" t="n">
-        <v>6885577</v>
+        <v>6885624</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4625,45 +4625,49 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125448393</v>
+        <v>125451578</v>
       </c>
       <c r="B41" t="n">
-        <v>97202</v>
+        <v>98331</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533568</v>
+        <v>533480</v>
       </c>
       <c r="R41" t="n">
-        <v>6885736</v>
+        <v>6885534</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4722,49 +4726,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125451578</v>
+        <v>125448393</v>
       </c>
       <c r="B42" t="n">
-        <v>98324</v>
+        <v>97209</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533480</v>
+        <v>533568</v>
       </c>
       <c r="R42" t="n">
-        <v>6885534</v>
+        <v>6885736</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4823,10 +4823,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125449555</v>
+        <v>125456823</v>
       </c>
       <c r="B43" t="n">
-        <v>80070</v>
+        <v>57651</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4834,34 +4834,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533527</v>
+        <v>533580</v>
       </c>
       <c r="R43" t="n">
-        <v>6885657</v>
+        <v>6885391</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4894,6 +4899,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4920,7 +4930,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125456823</v>
+        <v>125456232</v>
       </c>
       <c r="B44" t="n">
         <v>57651</v>
@@ -4951,7 +4961,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4960,10 +4970,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533580</v>
+        <v>533493</v>
       </c>
       <c r="R44" t="n">
-        <v>6885391</v>
+        <v>6884951</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5000,7 +5010,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall.  Mest äldre spår men öven något färskt</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5027,10 +5037,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125456232</v>
+        <v>125449555</v>
       </c>
       <c r="B45" t="n">
-        <v>57651</v>
+        <v>80070</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5038,39 +5048,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533493</v>
+        <v>533527</v>
       </c>
       <c r="R45" t="n">
-        <v>6884951</v>
+        <v>6885657</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5103,11 +5108,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.  Mest äldre spår men öven något färskt</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5137,7 +5137,7 @@
         <v>125456035</v>
       </c>
       <c r="B46" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>125457380</v>
       </c>
       <c r="B50" t="n">
-        <v>91513</v>
+        <v>91520</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>125451692</v>
       </c>
       <c r="B52" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5836,10 +5836,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125459017</v>
+        <v>125448879</v>
       </c>
       <c r="B53" t="n">
-        <v>91887</v>
+        <v>98331</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5847,34 +5847,38 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533634</v>
+        <v>533558</v>
       </c>
       <c r="R53" t="n">
-        <v>6885654</v>
+        <v>6885696</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5933,45 +5937,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125451445</v>
+        <v>125453495</v>
       </c>
       <c r="B54" t="n">
-        <v>80099</v>
+        <v>57651</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>533474</v>
+        <v>533487</v>
       </c>
       <c r="R54" t="n">
-        <v>6885569</v>
+        <v>6885398</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6004,6 +6013,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6030,54 +6044,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125452337</v>
+        <v>125451445</v>
       </c>
       <c r="B55" t="n">
-        <v>78967</v>
+        <v>80099</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>533485</v>
+        <v>533474</v>
       </c>
       <c r="R55" t="n">
-        <v>6885472</v>
+        <v>6885569</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6136,37 +6141,42 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125448879</v>
+        <v>125452337</v>
       </c>
       <c r="B56" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6175,10 +6185,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>533558</v>
+        <v>533485</v>
       </c>
       <c r="R56" t="n">
-        <v>6885696</v>
+        <v>6885472</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6237,50 +6247,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125453495</v>
+        <v>125459017</v>
       </c>
       <c r="B57" t="n">
-        <v>57651</v>
+        <v>91894</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>533487</v>
+        <v>533634</v>
       </c>
       <c r="R57" t="n">
-        <v>6885398</v>
+        <v>6885654</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6313,11 +6318,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6344,45 +6344,49 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125457312</v>
+        <v>125456355</v>
       </c>
       <c r="B58" t="n">
-        <v>91220</v>
+        <v>98331</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>533577</v>
+        <v>533513</v>
       </c>
       <c r="R58" t="n">
-        <v>6885438</v>
+        <v>6885005</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6441,10 +6445,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125455687</v>
+        <v>125457312</v>
       </c>
       <c r="B59" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6476,10 +6480,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>533469</v>
+        <v>533577</v>
       </c>
       <c r="R59" t="n">
-        <v>6885049</v>
+        <v>6885438</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6538,10 +6542,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125452374</v>
+        <v>125455687</v>
       </c>
       <c r="B60" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6569,14 +6573,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>533550</v>
+        <v>533469</v>
       </c>
       <c r="R60" t="n">
-        <v>6885458</v>
+        <v>6885049</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6635,49 +6639,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125456355</v>
+        <v>125452374</v>
       </c>
       <c r="B61" t="n">
-        <v>98324</v>
+        <v>91227</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>533513</v>
+        <v>533550</v>
       </c>
       <c r="R61" t="n">
-        <v>6885005</v>
+        <v>6885458</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6833,10 +6833,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125451409</v>
+        <v>125456968</v>
       </c>
       <c r="B63" t="n">
-        <v>57651</v>
+        <v>91227</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6844,39 +6844,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>533498</v>
+        <v>533562</v>
       </c>
       <c r="R63" t="n">
-        <v>6885552</v>
+        <v>6885408</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6909,11 +6904,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall. Både äldre spår och färska</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6940,10 +6930,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125456968</v>
+        <v>125448352</v>
       </c>
       <c r="B64" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6971,14 +6961,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>533562</v>
+        <v>533568</v>
       </c>
       <c r="R64" t="n">
-        <v>6885408</v>
+        <v>6885736</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7037,10 +7027,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125448352</v>
+        <v>125451409</v>
       </c>
       <c r="B65" t="n">
-        <v>91220</v>
+        <v>57651</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7048,34 +7038,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>533568</v>
+        <v>533498</v>
       </c>
       <c r="R65" t="n">
-        <v>6885736</v>
+        <v>6885552</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7108,6 +7103,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall. Både äldre spår och färska</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7134,45 +7134,50 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125454471</v>
+        <v>125448834</v>
       </c>
       <c r="B66" t="n">
-        <v>80070</v>
+        <v>58019</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>533467</v>
+        <v>533571</v>
       </c>
       <c r="R66" t="n">
-        <v>6885270</v>
+        <v>6885716</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7231,45 +7236,49 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125451247</v>
+        <v>125452794</v>
       </c>
       <c r="B67" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>533498</v>
+        <v>533476</v>
       </c>
       <c r="R67" t="n">
-        <v>6885552</v>
+        <v>6885492</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7328,10 +7337,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125451627</v>
+        <v>125449765</v>
       </c>
       <c r="B68" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7339,21 +7348,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7363,10 +7372,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533471</v>
+        <v>533527</v>
       </c>
       <c r="R68" t="n">
-        <v>6885526</v>
+        <v>6885657</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7425,10 +7434,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125450235</v>
+        <v>125448531</v>
       </c>
       <c r="B69" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7436,39 +7445,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533551</v>
+        <v>533571</v>
       </c>
       <c r="R69" t="n">
-        <v>6885632</v>
+        <v>6885716</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7501,11 +7505,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7532,49 +7531,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125452794</v>
+        <v>125454471</v>
       </c>
       <c r="B70" t="n">
-        <v>98324</v>
+        <v>80070</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533476</v>
+        <v>533467</v>
       </c>
       <c r="R70" t="n">
-        <v>6885492</v>
+        <v>6885270</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7633,7 +7628,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125449765</v>
+        <v>125451247</v>
       </c>
       <c r="B71" t="n">
         <v>78967</v>
@@ -7668,10 +7663,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>533527</v>
+        <v>533498</v>
       </c>
       <c r="R71" t="n">
-        <v>6885657</v>
+        <v>6885552</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7730,10 +7725,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125448531</v>
+        <v>125451627</v>
       </c>
       <c r="B72" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7741,21 +7736,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7765,10 +7760,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>533571</v>
+        <v>533471</v>
       </c>
       <c r="R72" t="n">
-        <v>6885716</v>
+        <v>6885526</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7827,27 +7822,27 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125448834</v>
+        <v>125450235</v>
       </c>
       <c r="B73" t="n">
-        <v>58019</v>
+        <v>57651</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7858,7 +7853,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -7867,10 +7862,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>533571</v>
+        <v>533551</v>
       </c>
       <c r="R73" t="n">
-        <v>6885716</v>
+        <v>6885632</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7903,6 +7898,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8346,49 +8346,50 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125458100</v>
+        <v>125459043</v>
       </c>
       <c r="B78" t="n">
-        <v>98324</v>
+        <v>57651</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>533578</v>
+        <v>533634</v>
       </c>
       <c r="R78" t="n">
-        <v>6885205</v>
+        <v>6885654</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8421,6 +8422,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8447,45 +8453,49 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125453817</v>
+        <v>125458100</v>
       </c>
       <c r="B79" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>533455</v>
+        <v>533578</v>
       </c>
       <c r="R79" t="n">
-        <v>6885379</v>
+        <v>6885205</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8544,10 +8554,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125456371</v>
+        <v>125453817</v>
       </c>
       <c r="B80" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8555,34 +8565,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>533602</v>
+        <v>533455</v>
       </c>
       <c r="R80" t="n">
-        <v>6885362</v>
+        <v>6885379</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8644,7 +8654,7 @@
         <v>125455827</v>
       </c>
       <c r="B81" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8738,10 +8748,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125459043</v>
+        <v>125456371</v>
       </c>
       <c r="B82" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8749,39 +8759,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533634</v>
+        <v>533602</v>
       </c>
       <c r="R82" t="n">
-        <v>6885654</v>
+        <v>6885362</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8814,11 +8819,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8848,7 +8848,7 @@
         <v>125454123</v>
       </c>
       <c r="B83" t="n">
-        <v>97202</v>
+        <v>97209</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8942,10 +8942,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125456250</v>
+        <v>125449196</v>
       </c>
       <c r="B84" t="n">
-        <v>91238</v>
+        <v>57651</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8953,43 +8953,43 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>533602</v>
+        <v>533558</v>
       </c>
       <c r="R84" t="n">
-        <v>6885362</v>
+        <v>6885696</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9048,45 +9048,49 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125458140</v>
+        <v>125450671</v>
       </c>
       <c r="B85" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>533574</v>
+        <v>533493</v>
       </c>
       <c r="R85" t="n">
-        <v>6885198</v>
+        <v>6885612</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9145,49 +9149,54 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125450671</v>
+        <v>125456250</v>
       </c>
       <c r="B86" t="n">
-        <v>98324</v>
+        <v>91245</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>533493</v>
+        <v>533602</v>
       </c>
       <c r="R86" t="n">
-        <v>6885612</v>
+        <v>6885362</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9246,10 +9255,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125449196</v>
+        <v>125458140</v>
       </c>
       <c r="B87" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9257,43 +9266,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>533558</v>
+        <v>533574</v>
       </c>
       <c r="R87" t="n">
-        <v>6885696</v>
+        <v>6885198</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9352,7 +9352,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125458930</v>
+        <v>125449549</v>
       </c>
       <c r="B88" t="n">
         <v>80070</v>
@@ -9387,10 +9387,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>533634</v>
+        <v>533559</v>
       </c>
       <c r="R88" t="n">
-        <v>6885654</v>
+        <v>6885649</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9449,45 +9449,49 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125457133</v>
+        <v>125456788</v>
       </c>
       <c r="B89" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>533574</v>
+        <v>533556</v>
       </c>
       <c r="R89" t="n">
-        <v>6885404</v>
+        <v>6885155</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9546,38 +9550,37 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125450505</v>
+        <v>125450718</v>
       </c>
       <c r="B90" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -9586,10 +9589,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>533526</v>
+        <v>533537</v>
       </c>
       <c r="R90" t="n">
-        <v>6885605</v>
+        <v>6885571</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9648,45 +9651,49 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125457466</v>
+        <v>125450452</v>
       </c>
       <c r="B91" t="n">
-        <v>91220</v>
+        <v>98331</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>533602</v>
+        <v>533508</v>
       </c>
       <c r="R91" t="n">
-        <v>6885362</v>
+        <v>6885633</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9745,10 +9752,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125450188</v>
+        <v>125458930</v>
       </c>
       <c r="B92" t="n">
-        <v>57651</v>
+        <v>80070</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9756,39 +9763,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>533539</v>
+        <v>533634</v>
       </c>
       <c r="R92" t="n">
-        <v>6885634</v>
+        <v>6885654</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9821,11 +9823,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9852,10 +9849,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125452660</v>
+        <v>125457466</v>
       </c>
       <c r="B93" t="n">
-        <v>57651</v>
+        <v>91227</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9863,43 +9860,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>533535</v>
+        <v>533602</v>
       </c>
       <c r="R93" t="n">
-        <v>6885468</v>
+        <v>6885362</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9958,49 +9946,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125456788</v>
+        <v>125457133</v>
       </c>
       <c r="B94" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>533556</v>
+        <v>533574</v>
       </c>
       <c r="R94" t="n">
-        <v>6885155</v>
+        <v>6885404</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10059,37 +10043,38 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125450718</v>
+        <v>125450505</v>
       </c>
       <c r="B95" t="n">
-        <v>98324</v>
+        <v>80070</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -10098,10 +10083,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>533537</v>
+        <v>533526</v>
       </c>
       <c r="R95" t="n">
-        <v>6885571</v>
+        <v>6885605</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10160,37 +10145,38 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125450452</v>
+        <v>125450188</v>
       </c>
       <c r="B96" t="n">
-        <v>98324</v>
+        <v>57651</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -10199,10 +10185,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>533508</v>
+        <v>533539</v>
       </c>
       <c r="R96" t="n">
-        <v>6885633</v>
+        <v>6885634</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10235,6 +10221,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10261,10 +10252,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125449549</v>
+        <v>125452660</v>
       </c>
       <c r="B97" t="n">
-        <v>80070</v>
+        <v>57651</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10272,34 +10263,43 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>533559</v>
+        <v>533535</v>
       </c>
       <c r="R97" t="n">
-        <v>6885649</v>
+        <v>6885468</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>

--- a/artfynd/A 19766-2025 artfynd.xlsx
+++ b/artfynd/A 19766-2025 artfynd.xlsx
@@ -675,37 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125450747</v>
+        <v>125452107</v>
       </c>
       <c r="B2" t="n">
-        <v>98352</v>
+        <v>57811</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533545</v>
+        <v>533485</v>
       </c>
       <c r="R2" t="n">
-        <v>6885577</v>
+        <v>6885472</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,38 +786,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125454035</v>
+        <v>125450747</v>
       </c>
       <c r="B3" t="n">
-        <v>78967</v>
+        <v>98352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -816,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533438</v>
+        <v>533545</v>
       </c>
       <c r="R3" t="n">
-        <v>6885340</v>
+        <v>6885577</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125452441</v>
+        <v>125449421</v>
       </c>
       <c r="B4" t="n">
-        <v>91245</v>
+        <v>91227</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -913,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533485</v>
+        <v>533564</v>
       </c>
       <c r="R4" t="n">
-        <v>6885472</v>
+        <v>6885654</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125449421</v>
+        <v>125454495</v>
       </c>
       <c r="B5" t="n">
-        <v>91227</v>
+        <v>57651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,34 +995,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533564</v>
+        <v>533467</v>
       </c>
       <c r="R5" t="n">
-        <v>6885654</v>
+        <v>6885270</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,6 +1060,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1072,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125454495</v>
+        <v>125454035</v>
       </c>
       <c r="B6" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,27 +1102,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1112,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533467</v>
+        <v>533438</v>
       </c>
       <c r="R6" t="n">
-        <v>6885270</v>
+        <v>6885340</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,11 +1167,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1179,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125452107</v>
+        <v>125452441</v>
       </c>
       <c r="B7" t="n">
-        <v>57811</v>
+        <v>91245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1190,38 +1204,24 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
@@ -3305,37 +3305,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125457445</v>
+        <v>125457210</v>
       </c>
       <c r="B28" t="n">
-        <v>98331</v>
+        <v>57651</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>37</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3344,10 +3345,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533577</v>
+        <v>533578</v>
       </c>
       <c r="R28" t="n">
-        <v>6885438</v>
+        <v>6885205</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3380,6 +3381,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3406,37 +3412,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125451793</v>
+        <v>125456654</v>
       </c>
       <c r="B29" t="n">
-        <v>98331</v>
+        <v>57651</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>200</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3445,10 +3452,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533474</v>
+        <v>533587</v>
       </c>
       <c r="R29" t="n">
-        <v>6885517</v>
+        <v>6885384</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3481,6 +3488,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3507,10 +3519,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125448667</v>
+        <v>125455421</v>
       </c>
       <c r="B30" t="n">
-        <v>80070</v>
+        <v>57651</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3518,34 +3530,43 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533560</v>
+        <v>533497</v>
       </c>
       <c r="R30" t="n">
-        <v>6885711</v>
+        <v>6885148</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3604,38 +3625,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125457210</v>
+        <v>125457445</v>
       </c>
       <c r="B31" t="n">
-        <v>57651</v>
+        <v>98331</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>37</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3644,10 +3664,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533578</v>
+        <v>533577</v>
       </c>
       <c r="R31" t="n">
-        <v>6885205</v>
+        <v>6885438</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3680,11 +3700,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3711,38 +3726,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125456654</v>
+        <v>125451793</v>
       </c>
       <c r="B32" t="n">
-        <v>57651</v>
+        <v>98331</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>200</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3751,10 +3765,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533587</v>
+        <v>533474</v>
       </c>
       <c r="R32" t="n">
-        <v>6885384</v>
+        <v>6885517</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3787,11 +3801,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3818,10 +3827,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125455421</v>
+        <v>125448667</v>
       </c>
       <c r="B33" t="n">
-        <v>57651</v>
+        <v>80070</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3829,43 +3838,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533497</v>
+        <v>533560</v>
       </c>
       <c r="R33" t="n">
-        <v>6885148</v>
+        <v>6885711</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4126,45 +4126,49 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125450637</v>
+        <v>125450818</v>
       </c>
       <c r="B36" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533545</v>
+        <v>533494</v>
       </c>
       <c r="R36" t="n">
-        <v>6885577</v>
+        <v>6885624</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4223,49 +4227,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125450818</v>
+        <v>125450637</v>
       </c>
       <c r="B37" t="n">
-        <v>98331</v>
+        <v>78967</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533494</v>
+        <v>533545</v>
       </c>
       <c r="R37" t="n">
-        <v>6885624</v>
+        <v>6885577</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4324,10 +4324,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125456538</v>
+        <v>125456221</v>
       </c>
       <c r="B38" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4335,39 +4335,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533543</v>
+        <v>533478</v>
       </c>
       <c r="R38" t="n">
-        <v>6885069</v>
+        <v>6884944</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4400,11 +4395,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4431,7 +4421,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125456221</v>
+        <v>125450387</v>
       </c>
       <c r="B39" t="n">
         <v>78967</v>
@@ -4462,14 +4452,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533478</v>
+        <v>533528</v>
       </c>
       <c r="R39" t="n">
-        <v>6884944</v>
+        <v>6885627</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4528,10 +4518,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125450387</v>
+        <v>125456538</v>
       </c>
       <c r="B40" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4539,34 +4529,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533528</v>
+        <v>533543</v>
       </c>
       <c r="R40" t="n">
-        <v>6885627</v>
+        <v>6885069</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4599,6 +4594,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4823,10 +4823,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125456823</v>
+        <v>125449555</v>
       </c>
       <c r="B43" t="n">
-        <v>57651</v>
+        <v>80070</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4834,39 +4834,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533580</v>
+        <v>533527</v>
       </c>
       <c r="R43" t="n">
-        <v>6885391</v>
+        <v>6885657</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4899,11 +4894,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4930,7 +4920,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125456232</v>
+        <v>125456823</v>
       </c>
       <c r="B44" t="n">
         <v>57651</v>
@@ -4961,7 +4951,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4970,10 +4960,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533493</v>
+        <v>533580</v>
       </c>
       <c r="R44" t="n">
-        <v>6884951</v>
+        <v>6885391</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5010,7 +5000,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack på tall.  Mest äldre spår men öven något färskt</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5037,10 +5027,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125449555</v>
+        <v>125456232</v>
       </c>
       <c r="B45" t="n">
-        <v>80070</v>
+        <v>57651</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5048,34 +5038,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533527</v>
+        <v>533493</v>
       </c>
       <c r="R45" t="n">
-        <v>6885657</v>
+        <v>6884951</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5108,6 +5103,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Mest äldre spår men öven något färskt</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -7134,50 +7134,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125448834</v>
+        <v>125451247</v>
       </c>
       <c r="B66" t="n">
-        <v>58019</v>
+        <v>78967</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>533571</v>
+        <v>533498</v>
       </c>
       <c r="R66" t="n">
-        <v>6885716</v>
+        <v>6885552</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7337,10 +7332,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125449765</v>
+        <v>125454471</v>
       </c>
       <c r="B68" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7348,21 +7343,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7372,10 +7367,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533527</v>
+        <v>533467</v>
       </c>
       <c r="R68" t="n">
-        <v>6885657</v>
+        <v>6885270</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7434,10 +7429,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125448531</v>
+        <v>125451627</v>
       </c>
       <c r="B69" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7445,21 +7440,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7469,10 +7464,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533571</v>
+        <v>533471</v>
       </c>
       <c r="R69" t="n">
-        <v>6885716</v>
+        <v>6885526</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7531,10 +7526,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125454471</v>
+        <v>125449765</v>
       </c>
       <c r="B70" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7542,21 +7537,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7566,10 +7561,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533467</v>
+        <v>533527</v>
       </c>
       <c r="R70" t="n">
-        <v>6885270</v>
+        <v>6885657</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7628,7 +7623,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125451247</v>
+        <v>125448531</v>
       </c>
       <c r="B71" t="n">
         <v>78967</v>
@@ -7663,10 +7658,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>533498</v>
+        <v>533571</v>
       </c>
       <c r="R71" t="n">
-        <v>6885552</v>
+        <v>6885716</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7725,10 +7720,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125451627</v>
+        <v>125450235</v>
       </c>
       <c r="B72" t="n">
-        <v>80070</v>
+        <v>57651</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7736,34 +7731,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>533471</v>
+        <v>533551</v>
       </c>
       <c r="R72" t="n">
-        <v>6885526</v>
+        <v>6885632</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7796,6 +7796,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7822,27 +7827,27 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125450235</v>
+        <v>125448834</v>
       </c>
       <c r="B73" t="n">
-        <v>57651</v>
+        <v>58019</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7853,7 +7858,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -7862,10 +7867,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>533551</v>
+        <v>533571</v>
       </c>
       <c r="R73" t="n">
-        <v>6885632</v>
+        <v>6885716</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7898,11 +7903,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8346,50 +8346,49 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125459043</v>
+        <v>125458100</v>
       </c>
       <c r="B78" t="n">
-        <v>57651</v>
+        <v>98331</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>533634</v>
+        <v>533578</v>
       </c>
       <c r="R78" t="n">
-        <v>6885654</v>
+        <v>6885205</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8422,11 +8421,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8453,49 +8447,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125458100</v>
+        <v>125454123</v>
       </c>
       <c r="B79" t="n">
-        <v>98331</v>
+        <v>97209</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>533578</v>
+        <v>533490</v>
       </c>
       <c r="R79" t="n">
-        <v>6885205</v>
+        <v>6885291</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8554,10 +8544,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125453817</v>
+        <v>125459043</v>
       </c>
       <c r="B80" t="n">
-        <v>80070</v>
+        <v>57651</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8565,34 +8555,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>533455</v>
+        <v>533634</v>
       </c>
       <c r="R80" t="n">
-        <v>6885379</v>
+        <v>6885654</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8625,6 +8620,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8651,10 +8651,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125455827</v>
+        <v>125453817</v>
       </c>
       <c r="B81" t="n">
-        <v>91227</v>
+        <v>80070</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8662,34 +8662,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>533479</v>
+        <v>533455</v>
       </c>
       <c r="R81" t="n">
-        <v>6884999</v>
+        <v>6885379</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8748,10 +8748,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125456371</v>
+        <v>125455827</v>
       </c>
       <c r="B82" t="n">
-        <v>78967</v>
+        <v>91227</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8759,21 +8759,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8783,10 +8783,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533602</v>
+        <v>533479</v>
       </c>
       <c r="R82" t="n">
-        <v>6885362</v>
+        <v>6884999</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8845,45 +8845,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125454123</v>
+        <v>125456371</v>
       </c>
       <c r="B83" t="n">
-        <v>97209</v>
+        <v>78967</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>533490</v>
+        <v>533602</v>
       </c>
       <c r="R83" t="n">
-        <v>6885291</v>
+        <v>6885362</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>

--- a/artfynd/A 19766-2025 artfynd.xlsx
+++ b/artfynd/A 19766-2025 artfynd.xlsx
@@ -675,47 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125452107</v>
+        <v>125450747</v>
       </c>
       <c r="B2" t="n">
-        <v>57811</v>
+        <v>98352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533485</v>
+        <v>533545</v>
       </c>
       <c r="R2" t="n">
-        <v>6885472</v>
+        <v>6885577</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,37 +776,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125450747</v>
+        <v>125454035</v>
       </c>
       <c r="B3" t="n">
-        <v>98352</v>
+        <v>78967</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533545</v>
+        <v>533438</v>
       </c>
       <c r="R3" t="n">
-        <v>6885577</v>
+        <v>6885340</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125449421</v>
+        <v>125452441</v>
       </c>
       <c r="B4" t="n">
-        <v>91227</v>
+        <v>91245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +889,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -922,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533564</v>
+        <v>533485</v>
       </c>
       <c r="R4" t="n">
-        <v>6885654</v>
+        <v>6885472</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125454495</v>
+        <v>125449421</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>91227</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,39 +986,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533467</v>
+        <v>533564</v>
       </c>
       <c r="R5" t="n">
-        <v>6885270</v>
+        <v>6885654</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,11 +1046,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125454035</v>
+        <v>125454495</v>
       </c>
       <c r="B6" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1102,27 +1083,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1131,10 +1112,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533438</v>
+        <v>533467</v>
       </c>
       <c r="R6" t="n">
-        <v>6885340</v>
+        <v>6885270</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,6 +1148,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,10 +1179,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125452441</v>
+        <v>125452107</v>
       </c>
       <c r="B7" t="n">
-        <v>91245</v>
+        <v>57811</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1204,24 +1190,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
@@ -2603,37 +2603,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125449821</v>
+        <v>125453277</v>
       </c>
       <c r="B21" t="n">
-        <v>98331</v>
+        <v>57811</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2642,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>533559</v>
+        <v>533421</v>
       </c>
       <c r="R21" t="n">
-        <v>6885649</v>
+        <v>6885458</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2704,49 +2705,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125449118</v>
+        <v>125452738</v>
       </c>
       <c r="B22" t="n">
-        <v>98331</v>
+        <v>78967</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533549</v>
+        <v>533500</v>
       </c>
       <c r="R22" t="n">
-        <v>6885695</v>
+        <v>6885440</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2776,19 +2773,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2815,10 +2802,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125452738</v>
+        <v>125456251</v>
       </c>
       <c r="B23" t="n">
-        <v>78967</v>
+        <v>91227</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2826,34 +2813,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533500</v>
+        <v>533497</v>
       </c>
       <c r="R23" t="n">
-        <v>6885440</v>
+        <v>6884966</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2912,10 +2899,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125456251</v>
+        <v>125452859</v>
       </c>
       <c r="B24" t="n">
-        <v>91227</v>
+        <v>78967</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2923,34 +2910,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533497</v>
+        <v>533466</v>
       </c>
       <c r="R24" t="n">
-        <v>6884966</v>
+        <v>6885506</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3009,32 +2996,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125452859</v>
+        <v>125451751</v>
       </c>
       <c r="B25" t="n">
-        <v>78967</v>
+        <v>97209</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3044,10 +3031,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533466</v>
+        <v>533503</v>
       </c>
       <c r="R25" t="n">
-        <v>6885506</v>
+        <v>6885498</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3106,38 +3093,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125453277</v>
+        <v>125449821</v>
       </c>
       <c r="B26" t="n">
-        <v>57811</v>
+        <v>98331</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3146,10 +3132,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533421</v>
+        <v>533559</v>
       </c>
       <c r="R26" t="n">
-        <v>6885458</v>
+        <v>6885649</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3208,45 +3194,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125451751</v>
+        <v>125449118</v>
       </c>
       <c r="B27" t="n">
-        <v>97209</v>
+        <v>98331</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533503</v>
+        <v>533549</v>
       </c>
       <c r="R27" t="n">
-        <v>6885498</v>
+        <v>6885695</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3276,9 +3266,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4126,49 +4126,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125450818</v>
+        <v>125450637</v>
       </c>
       <c r="B36" t="n">
-        <v>98331</v>
+        <v>78967</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533494</v>
+        <v>533545</v>
       </c>
       <c r="R36" t="n">
-        <v>6885624</v>
+        <v>6885577</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4227,45 +4223,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125450637</v>
+        <v>125450818</v>
       </c>
       <c r="B37" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533545</v>
+        <v>533494</v>
       </c>
       <c r="R37" t="n">
-        <v>6885577</v>
+        <v>6885624</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4823,10 +4823,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125449555</v>
+        <v>125456823</v>
       </c>
       <c r="B43" t="n">
-        <v>80070</v>
+        <v>57651</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4834,34 +4834,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533527</v>
+        <v>533580</v>
       </c>
       <c r="R43" t="n">
-        <v>6885657</v>
+        <v>6885391</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4894,6 +4899,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4920,7 +4930,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125456823</v>
+        <v>125456232</v>
       </c>
       <c r="B44" t="n">
         <v>57651</v>
@@ -4951,7 +4961,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4960,10 +4970,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533580</v>
+        <v>533493</v>
       </c>
       <c r="R44" t="n">
-        <v>6885391</v>
+        <v>6884951</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5000,7 +5010,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall.  Mest äldre spår men öven något färskt</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5027,10 +5037,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125456232</v>
+        <v>125449555</v>
       </c>
       <c r="B45" t="n">
-        <v>57651</v>
+        <v>80070</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5038,39 +5048,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533493</v>
+        <v>533527</v>
       </c>
       <c r="R45" t="n">
-        <v>6884951</v>
+        <v>6885657</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5103,11 +5108,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.  Mest äldre spår men öven något färskt</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5836,49 +5836,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125448879</v>
+        <v>125451445</v>
       </c>
       <c r="B53" t="n">
-        <v>98331</v>
+        <v>80099</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533558</v>
+        <v>533474</v>
       </c>
       <c r="R53" t="n">
-        <v>6885696</v>
+        <v>6885569</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5937,10 +5933,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125453495</v>
+        <v>125452337</v>
       </c>
       <c r="B54" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5948,27 +5944,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5977,10 +5977,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>533487</v>
+        <v>533485</v>
       </c>
       <c r="R54" t="n">
-        <v>6885398</v>
+        <v>6885472</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6013,11 +6013,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6044,32 +6039,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125451445</v>
+        <v>125459017</v>
       </c>
       <c r="B55" t="n">
-        <v>80099</v>
+        <v>91894</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>898</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6079,10 +6074,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>533474</v>
+        <v>533634</v>
       </c>
       <c r="R55" t="n">
-        <v>6885569</v>
+        <v>6885654</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6141,42 +6136,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125452337</v>
+        <v>125448879</v>
       </c>
       <c r="B56" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6185,10 +6175,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>533485</v>
+        <v>533558</v>
       </c>
       <c r="R56" t="n">
-        <v>6885472</v>
+        <v>6885696</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6247,45 +6237,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125459017</v>
+        <v>125453495</v>
       </c>
       <c r="B57" t="n">
-        <v>91894</v>
+        <v>57651</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>533634</v>
+        <v>533487</v>
       </c>
       <c r="R57" t="n">
-        <v>6885654</v>
+        <v>6885398</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6318,6 +6313,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6344,49 +6344,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125456355</v>
+        <v>125457312</v>
       </c>
       <c r="B58" t="n">
-        <v>98331</v>
+        <v>91227</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>533513</v>
+        <v>533577</v>
       </c>
       <c r="R58" t="n">
-        <v>6885005</v>
+        <v>6885438</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6445,7 +6441,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125457312</v>
+        <v>125455687</v>
       </c>
       <c r="B59" t="n">
         <v>91227</v>
@@ -6480,10 +6476,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>533577</v>
+        <v>533469</v>
       </c>
       <c r="R59" t="n">
-        <v>6885438</v>
+        <v>6885049</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6542,7 +6538,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125455687</v>
+        <v>125452374</v>
       </c>
       <c r="B60" t="n">
         <v>91227</v>
@@ -6573,14 +6569,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>533469</v>
+        <v>533550</v>
       </c>
       <c r="R60" t="n">
-        <v>6885049</v>
+        <v>6885458</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6639,45 +6635,49 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125452374</v>
+        <v>125456355</v>
       </c>
       <c r="B61" t="n">
-        <v>91227</v>
+        <v>98331</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>533550</v>
+        <v>533513</v>
       </c>
       <c r="R61" t="n">
-        <v>6885458</v>
+        <v>6885005</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6736,10 +6736,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125450152</v>
+        <v>125451409</v>
       </c>
       <c r="B62" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6747,34 +6747,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>533539</v>
+        <v>533498</v>
       </c>
       <c r="R62" t="n">
-        <v>6885645</v>
+        <v>6885552</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6807,6 +6812,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall. Både äldre spår och färska</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6833,10 +6843,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125456968</v>
+        <v>125450152</v>
       </c>
       <c r="B63" t="n">
-        <v>91227</v>
+        <v>78967</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6844,34 +6854,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>533562</v>
+        <v>533539</v>
       </c>
       <c r="R63" t="n">
-        <v>6885408</v>
+        <v>6885645</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6930,7 +6940,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125448352</v>
+        <v>125456968</v>
       </c>
       <c r="B64" t="n">
         <v>91227</v>
@@ -6961,14 +6971,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>533568</v>
+        <v>533562</v>
       </c>
       <c r="R64" t="n">
-        <v>6885736</v>
+        <v>6885408</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7027,10 +7037,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125451409</v>
+        <v>125448352</v>
       </c>
       <c r="B65" t="n">
-        <v>57651</v>
+        <v>91227</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7038,39 +7048,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>533498</v>
+        <v>533568</v>
       </c>
       <c r="R65" t="n">
-        <v>6885552</v>
+        <v>6885736</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7103,11 +7108,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall. Både äldre spår och färska</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8142,10 +8142,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125456406</v>
+        <v>125450898</v>
       </c>
       <c r="B76" t="n">
-        <v>57648</v>
+        <v>80070</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8153,39 +8153,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>533520</v>
+        <v>533518</v>
       </c>
       <c r="R76" t="n">
-        <v>6885018</v>
+        <v>6885534</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8244,10 +8244,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125450898</v>
+        <v>125456406</v>
       </c>
       <c r="B77" t="n">
-        <v>80070</v>
+        <v>57648</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8255,39 +8255,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>533518</v>
+        <v>533520</v>
       </c>
       <c r="R77" t="n">
-        <v>6885534</v>
+        <v>6885018</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8346,49 +8346,50 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125458100</v>
+        <v>125459043</v>
       </c>
       <c r="B78" t="n">
-        <v>98331</v>
+        <v>57651</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>533578</v>
+        <v>533634</v>
       </c>
       <c r="R78" t="n">
-        <v>6885205</v>
+        <v>6885654</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8421,6 +8422,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8447,45 +8453,49 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125454123</v>
+        <v>125458100</v>
       </c>
       <c r="B79" t="n">
-        <v>97209</v>
+        <v>98331</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>533490</v>
+        <v>533578</v>
       </c>
       <c r="R79" t="n">
-        <v>6885291</v>
+        <v>6885205</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8544,10 +8554,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125459043</v>
+        <v>125453817</v>
       </c>
       <c r="B80" t="n">
-        <v>57651</v>
+        <v>80070</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8555,39 +8565,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>533634</v>
+        <v>533455</v>
       </c>
       <c r="R80" t="n">
-        <v>6885654</v>
+        <v>6885379</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8620,11 +8625,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8651,10 +8651,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125453817</v>
+        <v>125455827</v>
       </c>
       <c r="B81" t="n">
-        <v>80070</v>
+        <v>91227</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8662,34 +8662,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>533455</v>
+        <v>533479</v>
       </c>
       <c r="R81" t="n">
-        <v>6885379</v>
+        <v>6884999</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8748,10 +8748,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125455827</v>
+        <v>125456371</v>
       </c>
       <c r="B82" t="n">
-        <v>91227</v>
+        <v>78967</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8759,21 +8759,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8783,10 +8783,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533479</v>
+        <v>533602</v>
       </c>
       <c r="R82" t="n">
-        <v>6884999</v>
+        <v>6885362</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8845,45 +8845,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125456371</v>
+        <v>125454123</v>
       </c>
       <c r="B83" t="n">
-        <v>78967</v>
+        <v>97209</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>533602</v>
+        <v>533490</v>
       </c>
       <c r="R83" t="n">
-        <v>6885362</v>
+        <v>6885291</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>

--- a/artfynd/A 19766-2025 artfynd.xlsx
+++ b/artfynd/A 19766-2025 artfynd.xlsx
@@ -675,37 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125450747</v>
+        <v>125454035</v>
       </c>
       <c r="B2" t="n">
-        <v>98352</v>
+        <v>78968</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533545</v>
+        <v>533438</v>
       </c>
       <c r="R2" t="n">
-        <v>6885577</v>
+        <v>6885340</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125454035</v>
+        <v>125452441</v>
       </c>
       <c r="B3" t="n">
-        <v>78967</v>
+        <v>91246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,39 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533438</v>
+        <v>533485</v>
       </c>
       <c r="R3" t="n">
-        <v>6885340</v>
+        <v>6885472</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125452441</v>
+        <v>125454495</v>
       </c>
       <c r="B4" t="n">
-        <v>91245</v>
+        <v>57651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,34 +885,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533485</v>
+        <v>533467</v>
       </c>
       <c r="R4" t="n">
-        <v>6885472</v>
+        <v>6885270</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,6 +950,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -975,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125449421</v>
+        <v>125452107</v>
       </c>
       <c r="B5" t="n">
-        <v>91227</v>
+        <v>57811</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,34 +992,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533564</v>
+        <v>533485</v>
       </c>
       <c r="R5" t="n">
-        <v>6885654</v>
+        <v>6885472</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,38 +1092,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125454495</v>
+        <v>125450747</v>
       </c>
       <c r="B6" t="n">
-        <v>57651</v>
+        <v>98355</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1112,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533467</v>
+        <v>533545</v>
       </c>
       <c r="R6" t="n">
-        <v>6885270</v>
+        <v>6885577</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,11 +1167,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1179,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125452107</v>
+        <v>125449421</v>
       </c>
       <c r="B7" t="n">
-        <v>57811</v>
+        <v>91228</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1190,48 +1204,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533485</v>
+        <v>533564</v>
       </c>
       <c r="R7" t="n">
-        <v>6885472</v>
+        <v>6885654</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,37 +1290,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125455201</v>
+        <v>125458714</v>
       </c>
       <c r="B8" t="n">
-        <v>98331</v>
+        <v>57651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>200</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1329,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533571</v>
+        <v>533683</v>
       </c>
       <c r="R8" t="n">
-        <v>6885153</v>
+        <v>6885420</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1365,6 +1366,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1391,7 +1397,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125458714</v>
+        <v>125455042</v>
       </c>
       <c r="B9" t="n">
         <v>57651</v>
@@ -1431,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533683</v>
+        <v>533556</v>
       </c>
       <c r="R9" t="n">
-        <v>6885420</v>
+        <v>6885155</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,7 +1477,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,38 +1504,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125455042</v>
+        <v>125455201</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>98334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>200</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1538,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533556</v>
+        <v>533571</v>
       </c>
       <c r="R10" t="n">
-        <v>6885155</v>
+        <v>6885153</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,11 +1579,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1605,45 +1605,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125453207</v>
+        <v>125450058</v>
       </c>
       <c r="B11" t="n">
-        <v>80070</v>
+        <v>98355</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533421</v>
+        <v>533564</v>
       </c>
       <c r="R11" t="n">
-        <v>6885458</v>
+        <v>6885654</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1702,10 +1706,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125455217</v>
+        <v>125449144</v>
       </c>
       <c r="B12" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1713,34 +1717,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533571</v>
+        <v>533538</v>
       </c>
       <c r="R12" t="n">
-        <v>6885153</v>
+        <v>6885703</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1773,6 +1782,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1799,10 +1813,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125453918</v>
+        <v>125449764</v>
       </c>
       <c r="B13" t="n">
-        <v>80070</v>
+        <v>57651</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1810,34 +1824,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533477</v>
+        <v>533559</v>
       </c>
       <c r="R13" t="n">
-        <v>6885329</v>
+        <v>6885649</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1870,6 +1889,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1896,10 +1920,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125449144</v>
+        <v>125455217</v>
       </c>
       <c r="B14" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1907,39 +1931,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533538</v>
+        <v>533571</v>
       </c>
       <c r="R14" t="n">
-        <v>6885703</v>
+        <v>6885153</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1972,11 +1991,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2003,10 +2017,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125449764</v>
+        <v>125453918</v>
       </c>
       <c r="B15" t="n">
-        <v>57651</v>
+        <v>80071</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2014,39 +2028,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>533559</v>
+        <v>533477</v>
       </c>
       <c r="R15" t="n">
-        <v>6885649</v>
+        <v>6885329</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,11 +2088,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2110,49 +2114,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125450058</v>
+        <v>125453207</v>
       </c>
       <c r="B16" t="n">
-        <v>98352</v>
+        <v>80071</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533564</v>
+        <v>533421</v>
       </c>
       <c r="R16" t="n">
-        <v>6885654</v>
+        <v>6885458</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,7 +2214,7 @@
         <v>125448798</v>
       </c>
       <c r="B17" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125448326</v>
+        <v>125452738</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>533568</v>
+        <v>533500</v>
       </c>
       <c r="R18" t="n">
-        <v>6885736</v>
+        <v>6885440</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125449383</v>
+        <v>125452859</v>
       </c>
       <c r="B19" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>533564</v>
+        <v>533466</v>
       </c>
       <c r="R19" t="n">
-        <v>6885654</v>
+        <v>6885506</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2506,10 +2506,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125449396</v>
+        <v>125456251</v>
       </c>
       <c r="B20" t="n">
-        <v>80070</v>
+        <v>91228</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2517,34 +2517,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>533550</v>
+        <v>533497</v>
       </c>
       <c r="R20" t="n">
-        <v>6885685</v>
+        <v>6884966</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2705,10 +2705,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125452738</v>
+        <v>125449396</v>
       </c>
       <c r="B22" t="n">
-        <v>78967</v>
+        <v>80071</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2716,21 +2716,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533500</v>
+        <v>533550</v>
       </c>
       <c r="R22" t="n">
-        <v>6885440</v>
+        <v>6885685</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125456251</v>
+        <v>125449383</v>
       </c>
       <c r="B23" t="n">
-        <v>91227</v>
+        <v>78968</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2813,34 +2813,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533497</v>
+        <v>533564</v>
       </c>
       <c r="R23" t="n">
-        <v>6884966</v>
+        <v>6885654</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125452859</v>
+        <v>125448326</v>
       </c>
       <c r="B24" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533466</v>
+        <v>533568</v>
       </c>
       <c r="R24" t="n">
-        <v>6885506</v>
+        <v>6885736</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2996,45 +2996,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125451751</v>
+        <v>125449821</v>
       </c>
       <c r="B25" t="n">
-        <v>97209</v>
+        <v>98334</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533503</v>
+        <v>533559</v>
       </c>
       <c r="R25" t="n">
-        <v>6885498</v>
+        <v>6885649</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3093,10 +3097,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125449821</v>
+        <v>125449118</v>
       </c>
       <c r="B26" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3123,7 +3127,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3132,10 +3136,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533559</v>
+        <v>533549</v>
       </c>
       <c r="R26" t="n">
-        <v>6885649</v>
+        <v>6885695</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3165,9 +3169,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3194,49 +3208,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125449118</v>
+        <v>125451751</v>
       </c>
       <c r="B27" t="n">
-        <v>98331</v>
+        <v>97212</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533549</v>
+        <v>533503</v>
       </c>
       <c r="R27" t="n">
-        <v>6885695</v>
+        <v>6885498</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3266,19 +3276,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3305,50 +3305,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125457210</v>
+        <v>125449273</v>
       </c>
       <c r="B28" t="n">
-        <v>57651</v>
+        <v>98334</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>37</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533578</v>
+        <v>533550</v>
       </c>
       <c r="R28" t="n">
-        <v>6885205</v>
+        <v>6885685</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3381,11 +3380,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3412,7 +3406,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125456654</v>
+        <v>125455421</v>
       </c>
       <c r="B29" t="n">
         <v>57651</v>
@@ -3440,22 +3434,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533587</v>
+        <v>533497</v>
       </c>
       <c r="R29" t="n">
-        <v>6885384</v>
+        <v>6885148</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3488,11 +3486,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3519,7 +3512,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125455421</v>
+        <v>125457210</v>
       </c>
       <c r="B30" t="n">
         <v>57651</v>
@@ -3547,14 +3540,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3563,10 +3552,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533497</v>
+        <v>533578</v>
       </c>
       <c r="R30" t="n">
-        <v>6885148</v>
+        <v>6885205</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3599,6 +3588,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3625,49 +3619,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125457445</v>
+        <v>125456654</v>
       </c>
       <c r="B31" t="n">
-        <v>98331</v>
+        <v>57651</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>37</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533577</v>
+        <v>533587</v>
       </c>
       <c r="R31" t="n">
-        <v>6885438</v>
+        <v>6885384</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3700,6 +3695,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3726,37 +3726,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125451793</v>
+        <v>125451213</v>
       </c>
       <c r="B32" t="n">
-        <v>98331</v>
+        <v>98355</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533474</v>
+        <v>533490</v>
       </c>
       <c r="R32" t="n">
-        <v>6885517</v>
+        <v>6885584</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3830,7 +3830,7 @@
         <v>125448667</v>
       </c>
       <c r="B33" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3924,49 +3924,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125451213</v>
+        <v>125457445</v>
       </c>
       <c r="B34" t="n">
-        <v>98352</v>
+        <v>98334</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>37</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533490</v>
+        <v>533577</v>
       </c>
       <c r="R34" t="n">
-        <v>6885584</v>
+        <v>6885438</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4025,10 +4025,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125449273</v>
+        <v>125451793</v>
       </c>
       <c r="B35" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4064,10 +4064,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533550</v>
+        <v>533474</v>
       </c>
       <c r="R35" t="n">
-        <v>6885685</v>
+        <v>6885517</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4129,7 +4129,7 @@
         <v>125450637</v>
       </c>
       <c r="B36" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>125450818</v>
       </c>
       <c r="B37" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>125456221</v>
       </c>
       <c r="B38" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>125450387</v>
       </c>
       <c r="B39" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>125451578</v>
       </c>
       <c r="B41" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>125448393</v>
       </c>
       <c r="B42" t="n">
-        <v>97209</v>
+        <v>97212</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>125449555</v>
       </c>
       <c r="B45" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>125456035</v>
       </c>
       <c r="B46" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5333,10 +5333,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125450555</v>
+        <v>125457380</v>
       </c>
       <c r="B48" t="n">
-        <v>78967</v>
+        <v>91524</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5344,34 +5344,43 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533508</v>
+        <v>533577</v>
       </c>
       <c r="R48" t="n">
-        <v>6885633</v>
+        <v>6885438</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5433,7 +5442,7 @@
         <v>125451683</v>
       </c>
       <c r="B49" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5527,10 +5536,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125457380</v>
+        <v>125450555</v>
       </c>
       <c r="B50" t="n">
-        <v>91520</v>
+        <v>78968</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5538,43 +5547,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>533577</v>
+        <v>533508</v>
       </c>
       <c r="R50" t="n">
-        <v>6885438</v>
+        <v>6885633</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5633,38 +5633,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125451954</v>
+        <v>125451692</v>
       </c>
       <c r="B51" t="n">
-        <v>56834</v>
+        <v>98334</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>22</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5673,10 +5672,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>533479</v>
+        <v>533471</v>
       </c>
       <c r="R51" t="n">
-        <v>6885506</v>
+        <v>6885526</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5735,37 +5734,38 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125451692</v>
+        <v>125451954</v>
       </c>
       <c r="B52" t="n">
-        <v>98331</v>
+        <v>56834</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>22</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5774,10 +5774,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>533471</v>
+        <v>533479</v>
       </c>
       <c r="R52" t="n">
-        <v>6885526</v>
+        <v>6885506</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5836,32 +5836,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125451445</v>
+        <v>125459017</v>
       </c>
       <c r="B53" t="n">
-        <v>80099</v>
+        <v>91898</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>898</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5871,10 +5871,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533474</v>
+        <v>533634</v>
       </c>
       <c r="R53" t="n">
-        <v>6885569</v>
+        <v>6885654</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5936,7 +5936,7 @@
         <v>125452337</v>
       </c>
       <c r="B54" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6039,32 +6039,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125459017</v>
+        <v>125451445</v>
       </c>
       <c r="B55" t="n">
-        <v>91894</v>
+        <v>80100</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>898</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6074,10 +6074,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>533634</v>
+        <v>533474</v>
       </c>
       <c r="R55" t="n">
-        <v>6885654</v>
+        <v>6885569</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6136,37 +6136,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125448879</v>
+        <v>125453495</v>
       </c>
       <c r="B56" t="n">
-        <v>98331</v>
+        <v>57651</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6175,10 +6176,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>533558</v>
+        <v>533487</v>
       </c>
       <c r="R56" t="n">
-        <v>6885696</v>
+        <v>6885398</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6211,6 +6212,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6237,38 +6243,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125453495</v>
+        <v>125448879</v>
       </c>
       <c r="B57" t="n">
-        <v>57651</v>
+        <v>98334</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6277,10 +6282,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>533487</v>
+        <v>533558</v>
       </c>
       <c r="R57" t="n">
-        <v>6885398</v>
+        <v>6885696</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6313,11 +6318,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6347,7 +6347,7 @@
         <v>125457312</v>
       </c>
       <c r="B58" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>125455687</v>
       </c>
       <c r="B59" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>125452374</v>
       </c>
       <c r="B60" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>125456355</v>
       </c>
       <c r="B61" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125451409</v>
+        <v>125450152</v>
       </c>
       <c r="B62" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6747,39 +6747,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>533498</v>
+        <v>533539</v>
       </c>
       <c r="R62" t="n">
-        <v>6885552</v>
+        <v>6885645</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6812,11 +6807,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall. Både äldre spår och färska</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6843,10 +6833,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125450152</v>
+        <v>125456968</v>
       </c>
       <c r="B63" t="n">
-        <v>78967</v>
+        <v>91228</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6854,34 +6844,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>533539</v>
+        <v>533562</v>
       </c>
       <c r="R63" t="n">
-        <v>6885645</v>
+        <v>6885408</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6940,10 +6930,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125456968</v>
+        <v>125451409</v>
       </c>
       <c r="B64" t="n">
-        <v>91227</v>
+        <v>57651</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6951,34 +6941,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>533562</v>
+        <v>533498</v>
       </c>
       <c r="R64" t="n">
-        <v>6885408</v>
+        <v>6885552</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7011,6 +7006,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall. Både äldre spår och färska</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7040,7 +7040,7 @@
         <v>125448352</v>
       </c>
       <c r="B65" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7134,10 +7134,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125451247</v>
+        <v>125450235</v>
       </c>
       <c r="B66" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7145,34 +7145,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>533498</v>
+        <v>533551</v>
       </c>
       <c r="R66" t="n">
-        <v>6885552</v>
+        <v>6885632</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7205,6 +7210,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7231,49 +7241,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125452794</v>
+        <v>125451627</v>
       </c>
       <c r="B67" t="n">
-        <v>98331</v>
+        <v>80071</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>533476</v>
+        <v>533471</v>
       </c>
       <c r="R67" t="n">
-        <v>6885492</v>
+        <v>6885526</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7332,10 +7338,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125454471</v>
+        <v>125451247</v>
       </c>
       <c r="B68" t="n">
-        <v>80070</v>
+        <v>78968</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7343,21 +7349,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7367,10 +7373,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533467</v>
+        <v>533498</v>
       </c>
       <c r="R68" t="n">
-        <v>6885270</v>
+        <v>6885552</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7429,10 +7435,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125451627</v>
+        <v>125454471</v>
       </c>
       <c r="B69" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7464,10 +7470,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533471</v>
+        <v>533467</v>
       </c>
       <c r="R69" t="n">
-        <v>6885526</v>
+        <v>6885270</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7526,45 +7532,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125449765</v>
+        <v>125448834</v>
       </c>
       <c r="B70" t="n">
-        <v>78967</v>
+        <v>58020</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533527</v>
+        <v>533571</v>
       </c>
       <c r="R70" t="n">
-        <v>6885657</v>
+        <v>6885716</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7623,10 +7634,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125448531</v>
+        <v>125449765</v>
       </c>
       <c r="B71" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7658,10 +7669,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>533571</v>
+        <v>533527</v>
       </c>
       <c r="R71" t="n">
-        <v>6885716</v>
+        <v>6885657</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7720,10 +7731,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125450235</v>
+        <v>125448531</v>
       </c>
       <c r="B72" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7731,39 +7742,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>533551</v>
+        <v>533571</v>
       </c>
       <c r="R72" t="n">
-        <v>6885632</v>
+        <v>6885716</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7796,11 +7802,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7827,38 +7828,37 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125448834</v>
+        <v>125452794</v>
       </c>
       <c r="B73" t="n">
-        <v>58019</v>
+        <v>98334</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -7867,10 +7867,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>533571</v>
+        <v>533476</v>
       </c>
       <c r="R73" t="n">
-        <v>6885716</v>
+        <v>6885492</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7929,10 +7929,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125456893</v>
+        <v>125452693</v>
       </c>
       <c r="B74" t="n">
-        <v>57651</v>
+        <v>56227</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7940,48 +7940,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>533561</v>
+        <v>533485</v>
       </c>
       <c r="R74" t="n">
-        <v>6885192</v>
+        <v>6885472</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8040,10 +8031,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125452693</v>
+        <v>125456893</v>
       </c>
       <c r="B75" t="n">
-        <v>56227</v>
+        <v>57651</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8051,39 +8042,48 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>533485</v>
+        <v>533561</v>
       </c>
       <c r="R75" t="n">
-        <v>6885472</v>
+        <v>6885192</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8142,10 +8142,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125450898</v>
+        <v>125456406</v>
       </c>
       <c r="B76" t="n">
-        <v>80070</v>
+        <v>57648</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8153,39 +8153,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>533518</v>
+        <v>533520</v>
       </c>
       <c r="R76" t="n">
-        <v>6885534</v>
+        <v>6885018</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8244,10 +8244,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125456406</v>
+        <v>125450898</v>
       </c>
       <c r="B77" t="n">
-        <v>57648</v>
+        <v>80071</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8255,39 +8255,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>533520</v>
+        <v>533518</v>
       </c>
       <c r="R77" t="n">
-        <v>6885018</v>
+        <v>6885534</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8346,10 +8346,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125459043</v>
+        <v>125455827</v>
       </c>
       <c r="B78" t="n">
-        <v>57651</v>
+        <v>91228</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8357,39 +8357,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>533634</v>
+        <v>533479</v>
       </c>
       <c r="R78" t="n">
-        <v>6885654</v>
+        <v>6884999</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8422,11 +8417,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8453,49 +8443,50 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125458100</v>
+        <v>125459043</v>
       </c>
       <c r="B79" t="n">
-        <v>98331</v>
+        <v>57651</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>533578</v>
+        <v>533634</v>
       </c>
       <c r="R79" t="n">
-        <v>6885205</v>
+        <v>6885654</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8528,6 +8519,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8554,32 +8550,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125453817</v>
+        <v>125454123</v>
       </c>
       <c r="B80" t="n">
-        <v>80070</v>
+        <v>97212</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8589,10 +8585,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>533455</v>
+        <v>533490</v>
       </c>
       <c r="R80" t="n">
-        <v>6885379</v>
+        <v>6885291</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8651,10 +8647,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125455827</v>
+        <v>125456371</v>
       </c>
       <c r="B81" t="n">
-        <v>91227</v>
+        <v>78968</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8662,21 +8658,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8686,10 +8682,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>533479</v>
+        <v>533602</v>
       </c>
       <c r="R81" t="n">
-        <v>6884999</v>
+        <v>6885362</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8748,10 +8744,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125456371</v>
+        <v>125453817</v>
       </c>
       <c r="B82" t="n">
-        <v>78967</v>
+        <v>80071</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8759,34 +8755,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533602</v>
+        <v>533455</v>
       </c>
       <c r="R82" t="n">
-        <v>6885362</v>
+        <v>6885379</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8845,45 +8841,49 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125454123</v>
+        <v>125458100</v>
       </c>
       <c r="B83" t="n">
-        <v>97209</v>
+        <v>98334</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>533490</v>
+        <v>533578</v>
       </c>
       <c r="R83" t="n">
-        <v>6885291</v>
+        <v>6885205</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9051,7 +9051,7 @@
         <v>125450671</v>
       </c>
       <c r="B85" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9149,10 +9149,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125456250</v>
+        <v>125458140</v>
       </c>
       <c r="B86" t="n">
-        <v>91245</v>
+        <v>78968</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9160,43 +9160,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>533602</v>
+        <v>533574</v>
       </c>
       <c r="R86" t="n">
-        <v>6885362</v>
+        <v>6885198</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9255,10 +9246,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125458140</v>
+        <v>125456250</v>
       </c>
       <c r="B87" t="n">
-        <v>78967</v>
+        <v>91246</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9266,34 +9257,43 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>533574</v>
+        <v>533602</v>
       </c>
       <c r="R87" t="n">
-        <v>6885198</v>
+        <v>6885362</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9352,10 +9352,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125449549</v>
+        <v>125458930</v>
       </c>
       <c r="B88" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9387,10 +9387,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>533559</v>
+        <v>533634</v>
       </c>
       <c r="R88" t="n">
-        <v>6885649</v>
+        <v>6885654</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9449,49 +9449,50 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125456788</v>
+        <v>125450505</v>
       </c>
       <c r="B89" t="n">
-        <v>98331</v>
+        <v>80071</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>130</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>533556</v>
+        <v>533526</v>
       </c>
       <c r="R89" t="n">
-        <v>6885155</v>
+        <v>6885605</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9550,49 +9551,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125450718</v>
+        <v>125457133</v>
       </c>
       <c r="B90" t="n">
-        <v>98331</v>
+        <v>78968</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>533537</v>
+        <v>533574</v>
       </c>
       <c r="R90" t="n">
-        <v>6885571</v>
+        <v>6885404</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9651,49 +9648,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125450452</v>
+        <v>125457466</v>
       </c>
       <c r="B91" t="n">
-        <v>98331</v>
+        <v>91228</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>533508</v>
+        <v>533602</v>
       </c>
       <c r="R91" t="n">
-        <v>6885633</v>
+        <v>6885362</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9752,10 +9745,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125458930</v>
+        <v>125450188</v>
       </c>
       <c r="B92" t="n">
-        <v>80070</v>
+        <v>57651</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9763,34 +9756,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>533634</v>
+        <v>533539</v>
       </c>
       <c r="R92" t="n">
-        <v>6885654</v>
+        <v>6885634</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9823,6 +9821,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9849,10 +9852,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125457466</v>
+        <v>125452660</v>
       </c>
       <c r="B93" t="n">
-        <v>91227</v>
+        <v>57651</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9860,34 +9863,43 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>533602</v>
+        <v>533535</v>
       </c>
       <c r="R93" t="n">
-        <v>6885362</v>
+        <v>6885468</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9946,45 +9958,49 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125457133</v>
+        <v>125456788</v>
       </c>
       <c r="B94" t="n">
-        <v>78967</v>
+        <v>98334</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>533574</v>
+        <v>533556</v>
       </c>
       <c r="R94" t="n">
-        <v>6885404</v>
+        <v>6885155</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10043,38 +10059,37 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125450505</v>
+        <v>125450452</v>
       </c>
       <c r="B95" t="n">
-        <v>80070</v>
+        <v>98334</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -10083,10 +10098,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>533526</v>
+        <v>533508</v>
       </c>
       <c r="R95" t="n">
-        <v>6885605</v>
+        <v>6885633</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10145,10 +10160,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125450188</v>
+        <v>125449549</v>
       </c>
       <c r="B96" t="n">
-        <v>57651</v>
+        <v>80071</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10156,39 +10171,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>533539</v>
+        <v>533559</v>
       </c>
       <c r="R96" t="n">
-        <v>6885634</v>
+        <v>6885649</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10221,11 +10231,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10252,42 +10257,37 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125452660</v>
+        <v>125450718</v>
       </c>
       <c r="B97" t="n">
-        <v>57651</v>
+        <v>98334</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -10296,10 +10296,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>533535</v>
+        <v>533537</v>
       </c>
       <c r="R97" t="n">
-        <v>6885468</v>
+        <v>6885571</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>

--- a/artfynd/A 19766-2025 artfynd.xlsx
+++ b/artfynd/A 19766-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125454035</v>
+        <v>125452107</v>
       </c>
       <c r="B2" t="n">
-        <v>78968</v>
+        <v>57811</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533438</v>
+        <v>533485</v>
       </c>
       <c r="R2" t="n">
-        <v>6885340</v>
+        <v>6885472</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,45 +786,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125452441</v>
+        <v>125450747</v>
       </c>
       <c r="B3" t="n">
-        <v>91246</v>
+        <v>98355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533485</v>
+        <v>533545</v>
       </c>
       <c r="R3" t="n">
-        <v>6885472</v>
+        <v>6885577</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125454495</v>
+        <v>125449421</v>
       </c>
       <c r="B4" t="n">
-        <v>57651</v>
+        <v>91228</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,39 +898,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533467</v>
+        <v>533564</v>
       </c>
       <c r="R4" t="n">
-        <v>6885270</v>
+        <v>6885654</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,11 +958,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125452107</v>
+        <v>125454035</v>
       </c>
       <c r="B5" t="n">
-        <v>57811</v>
+        <v>78968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,36 +995,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1030,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533485</v>
+        <v>533438</v>
       </c>
       <c r="R5" t="n">
-        <v>6885472</v>
+        <v>6885340</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,49 +1086,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125450747</v>
+        <v>125452441</v>
       </c>
       <c r="B6" t="n">
-        <v>98355</v>
+        <v>91246</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533545</v>
+        <v>533485</v>
       </c>
       <c r="R6" t="n">
-        <v>6885577</v>
+        <v>6885472</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,10 +1183,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125449421</v>
+        <v>125454495</v>
       </c>
       <c r="B7" t="n">
-        <v>91228</v>
+        <v>57651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1204,34 +1194,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533564</v>
+        <v>533467</v>
       </c>
       <c r="R7" t="n">
-        <v>6885654</v>
+        <v>6885270</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1264,6 +1259,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1605,37 +1605,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125450058</v>
+        <v>125448798</v>
       </c>
       <c r="B11" t="n">
-        <v>98355</v>
+        <v>98334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533564</v>
+        <v>533560</v>
       </c>
       <c r="R11" t="n">
-        <v>6885654</v>
+        <v>6885711</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1706,10 +1706,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125449144</v>
+        <v>125455217</v>
       </c>
       <c r="B12" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1717,39 +1717,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533538</v>
+        <v>533571</v>
       </c>
       <c r="R12" t="n">
-        <v>6885703</v>
+        <v>6885153</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1782,11 +1777,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1813,10 +1803,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125449764</v>
+        <v>125453918</v>
       </c>
       <c r="B13" t="n">
-        <v>57651</v>
+        <v>80071</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1824,39 +1814,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533559</v>
+        <v>533477</v>
       </c>
       <c r="R13" t="n">
-        <v>6885649</v>
+        <v>6885329</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1889,11 +1874,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1920,10 +1900,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125455217</v>
+        <v>125453207</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>80071</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1931,34 +1911,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533571</v>
+        <v>533421</v>
       </c>
       <c r="R14" t="n">
-        <v>6885153</v>
+        <v>6885458</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2017,45 +1997,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125453918</v>
+        <v>125450058</v>
       </c>
       <c r="B15" t="n">
-        <v>80071</v>
+        <v>98355</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>533477</v>
+        <v>533564</v>
       </c>
       <c r="R15" t="n">
-        <v>6885329</v>
+        <v>6885654</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2114,10 +2098,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125453207</v>
+        <v>125449144</v>
       </c>
       <c r="B16" t="n">
-        <v>80071</v>
+        <v>57651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2125,34 +2109,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533421</v>
+        <v>533538</v>
       </c>
       <c r="R16" t="n">
-        <v>6885458</v>
+        <v>6885703</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2185,6 +2174,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2211,37 +2205,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125448798</v>
+        <v>125449764</v>
       </c>
       <c r="B17" t="n">
-        <v>98334</v>
+        <v>57651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>90</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2250,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>533560</v>
+        <v>533559</v>
       </c>
       <c r="R17" t="n">
-        <v>6885711</v>
+        <v>6885649</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2286,6 +2281,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2603,10 +2603,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125453277</v>
+        <v>125449396</v>
       </c>
       <c r="B21" t="n">
-        <v>57811</v>
+        <v>80071</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2614,39 +2614,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>533421</v>
+        <v>533550</v>
       </c>
       <c r="R21" t="n">
-        <v>6885458</v>
+        <v>6885685</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2705,10 +2700,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125449396</v>
+        <v>125449383</v>
       </c>
       <c r="B22" t="n">
-        <v>80071</v>
+        <v>78968</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2716,21 +2711,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2740,10 +2735,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533550</v>
+        <v>533564</v>
       </c>
       <c r="R22" t="n">
-        <v>6885685</v>
+        <v>6885654</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2802,7 +2797,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125449383</v>
+        <v>125448326</v>
       </c>
       <c r="B23" t="n">
         <v>78968</v>
@@ -2837,10 +2832,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533564</v>
+        <v>533568</v>
       </c>
       <c r="R23" t="n">
-        <v>6885654</v>
+        <v>6885736</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2899,10 +2894,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125448326</v>
+        <v>125453277</v>
       </c>
       <c r="B24" t="n">
-        <v>78968</v>
+        <v>57811</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2910,34 +2905,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533568</v>
+        <v>533421</v>
       </c>
       <c r="R24" t="n">
-        <v>6885736</v>
+        <v>6885458</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2996,49 +2996,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125449821</v>
+        <v>125451751</v>
       </c>
       <c r="B25" t="n">
-        <v>98334</v>
+        <v>97212</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533559</v>
+        <v>533503</v>
       </c>
       <c r="R25" t="n">
-        <v>6885649</v>
+        <v>6885498</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3097,7 +3093,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125449118</v>
+        <v>125449821</v>
       </c>
       <c r="B26" t="n">
         <v>98334</v>
@@ -3127,7 +3123,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3136,10 +3132,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533549</v>
+        <v>533559</v>
       </c>
       <c r="R26" t="n">
-        <v>6885695</v>
+        <v>6885649</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3169,19 +3165,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3208,45 +3194,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125451751</v>
+        <v>125449118</v>
       </c>
       <c r="B27" t="n">
-        <v>97212</v>
+        <v>98334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533503</v>
+        <v>533549</v>
       </c>
       <c r="R27" t="n">
-        <v>6885498</v>
+        <v>6885695</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3276,9 +3266,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3305,7 +3305,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125449273</v>
+        <v>125457445</v>
       </c>
       <c r="B28" t="n">
         <v>98334</v>
@@ -3340,14 +3340,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533550</v>
+        <v>533577</v>
       </c>
       <c r="R28" t="n">
-        <v>6885685</v>
+        <v>6885438</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3406,54 +3406,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125455421</v>
+        <v>125451793</v>
       </c>
       <c r="B29" t="n">
-        <v>57651</v>
+        <v>98334</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533497</v>
+        <v>533474</v>
       </c>
       <c r="R29" t="n">
-        <v>6885148</v>
+        <v>6885517</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3512,50 +3507,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125457210</v>
+        <v>125451213</v>
       </c>
       <c r="B30" t="n">
-        <v>57651</v>
+        <v>98355</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533578</v>
+        <v>533490</v>
       </c>
       <c r="R30" t="n">
-        <v>6885205</v>
+        <v>6885584</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3588,11 +3582,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3619,10 +3608,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125456654</v>
+        <v>125448667</v>
       </c>
       <c r="B31" t="n">
-        <v>57651</v>
+        <v>80071</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3630,39 +3619,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533587</v>
+        <v>533560</v>
       </c>
       <c r="R31" t="n">
-        <v>6885384</v>
+        <v>6885711</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3695,11 +3679,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3726,37 +3705,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125451213</v>
+        <v>125449273</v>
       </c>
       <c r="B32" t="n">
-        <v>98355</v>
+        <v>98334</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>37</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3765,10 +3744,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533490</v>
+        <v>533550</v>
       </c>
       <c r="R32" t="n">
-        <v>6885584</v>
+        <v>6885685</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3827,10 +3806,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125448667</v>
+        <v>125455421</v>
       </c>
       <c r="B33" t="n">
-        <v>80071</v>
+        <v>57651</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3838,34 +3817,43 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533560</v>
+        <v>533497</v>
       </c>
       <c r="R33" t="n">
-        <v>6885711</v>
+        <v>6885148</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3924,37 +3912,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125457445</v>
+        <v>125457210</v>
       </c>
       <c r="B34" t="n">
-        <v>98334</v>
+        <v>57651</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>37</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3963,10 +3952,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533577</v>
+        <v>533578</v>
       </c>
       <c r="R34" t="n">
-        <v>6885438</v>
+        <v>6885205</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3999,6 +3988,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4025,37 +4019,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125451793</v>
+        <v>125456654</v>
       </c>
       <c r="B35" t="n">
-        <v>98334</v>
+        <v>57651</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>200</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4064,10 +4059,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533474</v>
+        <v>533587</v>
       </c>
       <c r="R35" t="n">
-        <v>6885517</v>
+        <v>6885384</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4100,6 +4095,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4324,45 +4324,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125456221</v>
+        <v>125448393</v>
       </c>
       <c r="B38" t="n">
-        <v>78968</v>
+        <v>97212</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533478</v>
+        <v>533568</v>
       </c>
       <c r="R38" t="n">
-        <v>6884944</v>
+        <v>6885736</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4421,45 +4421,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125450387</v>
+        <v>125451578</v>
       </c>
       <c r="B39" t="n">
-        <v>78968</v>
+        <v>98334</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533528</v>
+        <v>533480</v>
       </c>
       <c r="R39" t="n">
-        <v>6885627</v>
+        <v>6885534</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4625,49 +4629,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125451578</v>
+        <v>125456221</v>
       </c>
       <c r="B41" t="n">
-        <v>98334</v>
+        <v>78968</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533480</v>
+        <v>533478</v>
       </c>
       <c r="R41" t="n">
-        <v>6885534</v>
+        <v>6884944</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4726,32 +4726,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125448393</v>
+        <v>125450387</v>
       </c>
       <c r="B42" t="n">
-        <v>97212</v>
+        <v>78968</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533568</v>
+        <v>533528</v>
       </c>
       <c r="R42" t="n">
-        <v>6885736</v>
+        <v>6885627</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5134,10 +5134,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125456035</v>
+        <v>125456732</v>
       </c>
       <c r="B46" t="n">
-        <v>91228</v>
+        <v>57648</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5145,34 +5145,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533444</v>
+        <v>533566</v>
       </c>
       <c r="R46" t="n">
-        <v>6884916</v>
+        <v>6885119</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5231,10 +5236,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125456732</v>
+        <v>125456035</v>
       </c>
       <c r="B47" t="n">
-        <v>57648</v>
+        <v>91228</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5242,39 +5247,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>533566</v>
+        <v>533444</v>
       </c>
       <c r="R47" t="n">
-        <v>6885119</v>
+        <v>6884916</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6344,45 +6344,49 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125457312</v>
+        <v>125456355</v>
       </c>
       <c r="B58" t="n">
-        <v>91228</v>
+        <v>98334</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>533577</v>
+        <v>533513</v>
       </c>
       <c r="R58" t="n">
-        <v>6885438</v>
+        <v>6885005</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6441,7 +6445,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125455687</v>
+        <v>125457312</v>
       </c>
       <c r="B59" t="n">
         <v>91228</v>
@@ -6476,10 +6480,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>533469</v>
+        <v>533577</v>
       </c>
       <c r="R59" t="n">
-        <v>6885049</v>
+        <v>6885438</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6538,7 +6542,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125452374</v>
+        <v>125455687</v>
       </c>
       <c r="B60" t="n">
         <v>91228</v>
@@ -6569,14 +6573,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>533550</v>
+        <v>533469</v>
       </c>
       <c r="R60" t="n">
-        <v>6885458</v>
+        <v>6885049</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6635,49 +6639,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125456355</v>
+        <v>125452374</v>
       </c>
       <c r="B61" t="n">
-        <v>98334</v>
+        <v>91228</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>533513</v>
+        <v>533550</v>
       </c>
       <c r="R61" t="n">
-        <v>6885005</v>
+        <v>6885458</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8346,10 +8346,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125455827</v>
+        <v>125456371</v>
       </c>
       <c r="B78" t="n">
-        <v>91228</v>
+        <v>78968</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8357,21 +8357,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8381,10 +8381,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>533479</v>
+        <v>533602</v>
       </c>
       <c r="R78" t="n">
-        <v>6884999</v>
+        <v>6885362</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8443,10 +8443,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125459043</v>
+        <v>125453817</v>
       </c>
       <c r="B79" t="n">
-        <v>57651</v>
+        <v>80071</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8454,39 +8454,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>533634</v>
+        <v>533455</v>
       </c>
       <c r="R79" t="n">
-        <v>6885654</v>
+        <v>6885379</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8519,11 +8514,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8550,45 +8540,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125454123</v>
+        <v>125455827</v>
       </c>
       <c r="B80" t="n">
-        <v>97212</v>
+        <v>91228</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>533490</v>
+        <v>533479</v>
       </c>
       <c r="R80" t="n">
-        <v>6885291</v>
+        <v>6884999</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8647,10 +8637,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125456371</v>
+        <v>125459043</v>
       </c>
       <c r="B81" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8658,34 +8648,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>533602</v>
+        <v>533634</v>
       </c>
       <c r="R81" t="n">
-        <v>6885362</v>
+        <v>6885654</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8718,6 +8713,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8744,32 +8744,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125453817</v>
+        <v>125454123</v>
       </c>
       <c r="B82" t="n">
-        <v>80071</v>
+        <v>97212</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8779,10 +8779,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533455</v>
+        <v>533490</v>
       </c>
       <c r="R82" t="n">
-        <v>6885379</v>
+        <v>6885291</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>

--- a/artfynd/A 19766-2025 artfynd.xlsx
+++ b/artfynd/A 19766-2025 artfynd.xlsx
@@ -786,49 +786,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125450747</v>
+        <v>125452441</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>91250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533545</v>
+        <v>533485</v>
       </c>
       <c r="R3" t="n">
-        <v>6885577</v>
+        <v>6885472</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +886,7 @@
         <v>125449421</v>
       </c>
       <c r="B4" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,10 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125454035</v>
+        <v>125454495</v>
       </c>
       <c r="B5" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,27 +991,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1024,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533438</v>
+        <v>533467</v>
       </c>
       <c r="R5" t="n">
-        <v>6885340</v>
+        <v>6885270</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,6 +1056,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,45 +1087,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125452441</v>
+        <v>125450747</v>
       </c>
       <c r="B6" t="n">
-        <v>91246</v>
+        <v>98359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533485</v>
+        <v>533545</v>
       </c>
       <c r="R6" t="n">
-        <v>6885472</v>
+        <v>6885577</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125454495</v>
+        <v>125454035</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,27 +1199,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1223,10 +1228,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533467</v>
+        <v>533438</v>
       </c>
       <c r="R7" t="n">
-        <v>6885270</v>
+        <v>6885340</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,11 +1264,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1290,38 +1290,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125458714</v>
+        <v>125455201</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>98338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>200</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1330,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533683</v>
+        <v>533571</v>
       </c>
       <c r="R8" t="n">
-        <v>6885420</v>
+        <v>6885153</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,11 +1365,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,7 +1391,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125455042</v>
+        <v>125458714</v>
       </c>
       <c r="B9" t="n">
         <v>57651</v>
@@ -1437,10 +1431,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533556</v>
+        <v>533683</v>
       </c>
       <c r="R9" t="n">
-        <v>6885155</v>
+        <v>6885420</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1477,7 +1471,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1504,37 +1498,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125455201</v>
+        <v>125455042</v>
       </c>
       <c r="B10" t="n">
-        <v>98334</v>
+        <v>57651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>200</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1543,10 +1538,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533571</v>
+        <v>533556</v>
       </c>
       <c r="R10" t="n">
-        <v>6885153</v>
+        <v>6885155</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1579,6 +1574,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1605,37 +1605,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125448798</v>
+        <v>125450058</v>
       </c>
       <c r="B11" t="n">
-        <v>98334</v>
+        <v>98359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533560</v>
+        <v>533564</v>
       </c>
       <c r="R11" t="n">
-        <v>6885711</v>
+        <v>6885654</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1706,45 +1706,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125455217</v>
+        <v>125448798</v>
       </c>
       <c r="B12" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533571</v>
+        <v>533560</v>
       </c>
       <c r="R12" t="n">
-        <v>6885153</v>
+        <v>6885711</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1803,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125453918</v>
+        <v>125453207</v>
       </c>
       <c r="B13" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533477</v>
+        <v>533421</v>
       </c>
       <c r="R13" t="n">
-        <v>6885329</v>
+        <v>6885458</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125453207</v>
+        <v>125455217</v>
       </c>
       <c r="B14" t="n">
-        <v>80071</v>
+        <v>78972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1911,34 +1915,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533421</v>
+        <v>533571</v>
       </c>
       <c r="R14" t="n">
-        <v>6885458</v>
+        <v>6885153</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1997,49 +2001,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125450058</v>
+        <v>125453918</v>
       </c>
       <c r="B15" t="n">
-        <v>98355</v>
+        <v>80075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>533564</v>
+        <v>533477</v>
       </c>
       <c r="R15" t="n">
-        <v>6885654</v>
+        <v>6885329</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2312,32 +2312,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125452738</v>
+        <v>125451751</v>
       </c>
       <c r="B18" t="n">
-        <v>78968</v>
+        <v>97216</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>533500</v>
+        <v>533503</v>
       </c>
       <c r="R18" t="n">
-        <v>6885440</v>
+        <v>6885498</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,45 +2409,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125452859</v>
+        <v>125449821</v>
       </c>
       <c r="B19" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>533466</v>
+        <v>533559</v>
       </c>
       <c r="R19" t="n">
-        <v>6885506</v>
+        <v>6885649</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2506,45 +2510,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125456251</v>
+        <v>125449118</v>
       </c>
       <c r="B20" t="n">
-        <v>91228</v>
+        <v>98338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>533497</v>
+        <v>533549</v>
       </c>
       <c r="R20" t="n">
-        <v>6884966</v>
+        <v>6885695</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2574,9 +2582,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2603,10 +2621,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125449396</v>
+        <v>125453277</v>
       </c>
       <c r="B21" t="n">
-        <v>80071</v>
+        <v>57811</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2614,34 +2632,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>533550</v>
+        <v>533421</v>
       </c>
       <c r="R21" t="n">
-        <v>6885685</v>
+        <v>6885458</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2700,10 +2723,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125449383</v>
+        <v>125452738</v>
       </c>
       <c r="B22" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2735,10 +2758,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533564</v>
+        <v>533500</v>
       </c>
       <c r="R22" t="n">
-        <v>6885654</v>
+        <v>6885440</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2797,10 +2820,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125448326</v>
+        <v>125452859</v>
       </c>
       <c r="B23" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2832,10 +2855,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533568</v>
+        <v>533466</v>
       </c>
       <c r="R23" t="n">
-        <v>6885736</v>
+        <v>6885506</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2894,10 +2917,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125453277</v>
+        <v>125449383</v>
       </c>
       <c r="B24" t="n">
-        <v>57811</v>
+        <v>78972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2905,39 +2928,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533421</v>
+        <v>533564</v>
       </c>
       <c r="R24" t="n">
-        <v>6885458</v>
+        <v>6885654</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2996,32 +3014,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125451751</v>
+        <v>125448326</v>
       </c>
       <c r="B25" t="n">
-        <v>97212</v>
+        <v>78972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3031,10 +3049,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533503</v>
+        <v>533568</v>
       </c>
       <c r="R25" t="n">
-        <v>6885498</v>
+        <v>6885736</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3093,49 +3111,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125449821</v>
+        <v>125456251</v>
       </c>
       <c r="B26" t="n">
-        <v>98334</v>
+        <v>91232</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533559</v>
+        <v>533497</v>
       </c>
       <c r="R26" t="n">
-        <v>6885649</v>
+        <v>6884966</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3194,49 +3208,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125449118</v>
+        <v>125449396</v>
       </c>
       <c r="B27" t="n">
-        <v>98334</v>
+        <v>80075</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533549</v>
+        <v>533550</v>
       </c>
       <c r="R27" t="n">
-        <v>6885695</v>
+        <v>6885685</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3266,19 +3276,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3305,10 +3305,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125457445</v>
+        <v>125449273</v>
       </c>
       <c r="B28" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3340,14 +3340,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533577</v>
+        <v>533550</v>
       </c>
       <c r="R28" t="n">
-        <v>6885438</v>
+        <v>6885685</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3406,49 +3406,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125451793</v>
+        <v>125448667</v>
       </c>
       <c r="B29" t="n">
-        <v>98334</v>
+        <v>80075</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533474</v>
+        <v>533560</v>
       </c>
       <c r="R29" t="n">
-        <v>6885517</v>
+        <v>6885711</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3507,49 +3503,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125451213</v>
+        <v>125457210</v>
       </c>
       <c r="B30" t="n">
-        <v>98355</v>
+        <v>57651</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533490</v>
+        <v>533578</v>
       </c>
       <c r="R30" t="n">
-        <v>6885584</v>
+        <v>6885205</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3582,6 +3579,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3608,10 +3610,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125448667</v>
+        <v>125456654</v>
       </c>
       <c r="B31" t="n">
-        <v>80071</v>
+        <v>57651</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3619,34 +3621,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533560</v>
+        <v>533587</v>
       </c>
       <c r="R31" t="n">
-        <v>6885711</v>
+        <v>6885384</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3679,6 +3686,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3705,49 +3717,54 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125449273</v>
+        <v>125455421</v>
       </c>
       <c r="B32" t="n">
-        <v>98334</v>
+        <v>57651</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533550</v>
+        <v>533497</v>
       </c>
       <c r="R32" t="n">
-        <v>6885685</v>
+        <v>6885148</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3806,42 +3823,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125455421</v>
+        <v>125457445</v>
       </c>
       <c r="B33" t="n">
-        <v>57651</v>
+        <v>98338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>37</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3850,10 +3862,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533497</v>
+        <v>533577</v>
       </c>
       <c r="R33" t="n">
-        <v>6885148</v>
+        <v>6885438</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3912,50 +3924,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125457210</v>
+        <v>125451793</v>
       </c>
       <c r="B34" t="n">
-        <v>57651</v>
+        <v>98338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>200</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533578</v>
+        <v>533474</v>
       </c>
       <c r="R34" t="n">
-        <v>6885205</v>
+        <v>6885517</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3988,11 +3999,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4019,38 +4025,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125456654</v>
+        <v>125451213</v>
       </c>
       <c r="B35" t="n">
-        <v>57651</v>
+        <v>98359</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4059,10 +4064,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533587</v>
+        <v>533490</v>
       </c>
       <c r="R35" t="n">
-        <v>6885384</v>
+        <v>6885584</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4095,11 +4100,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4129,7 +4129,7 @@
         <v>125450637</v>
       </c>
       <c r="B36" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>125450818</v>
       </c>
       <c r="B37" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>125448393</v>
       </c>
       <c r="B38" t="n">
-        <v>97212</v>
+        <v>97216</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4421,49 +4421,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125451578</v>
+        <v>125456221</v>
       </c>
       <c r="B39" t="n">
-        <v>98334</v>
+        <v>78972</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533480</v>
+        <v>533478</v>
       </c>
       <c r="R39" t="n">
-        <v>6885534</v>
+        <v>6884944</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4522,10 +4518,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125456538</v>
+        <v>125450387</v>
       </c>
       <c r="B40" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4533,39 +4529,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533543</v>
+        <v>533528</v>
       </c>
       <c r="R40" t="n">
-        <v>6885069</v>
+        <v>6885627</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4598,11 +4589,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4629,45 +4615,49 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125456221</v>
+        <v>125451578</v>
       </c>
       <c r="B41" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533478</v>
+        <v>533480</v>
       </c>
       <c r="R41" t="n">
-        <v>6884944</v>
+        <v>6885534</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4726,10 +4716,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125450387</v>
+        <v>125456538</v>
       </c>
       <c r="B42" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4737,34 +4727,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533528</v>
+        <v>533543</v>
       </c>
       <c r="R42" t="n">
-        <v>6885627</v>
+        <v>6885069</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4797,6 +4792,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4823,10 +4823,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125456823</v>
+        <v>125449555</v>
       </c>
       <c r="B43" t="n">
-        <v>57651</v>
+        <v>80075</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4834,39 +4834,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533580</v>
+        <v>533527</v>
       </c>
       <c r="R43" t="n">
-        <v>6885391</v>
+        <v>6885657</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4899,11 +4894,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4930,7 +4920,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125456232</v>
+        <v>125456823</v>
       </c>
       <c r="B44" t="n">
         <v>57651</v>
@@ -4961,7 +4951,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4970,10 +4960,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533493</v>
+        <v>533580</v>
       </c>
       <c r="R44" t="n">
-        <v>6884951</v>
+        <v>6885391</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5010,7 +5000,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack på tall.  Mest äldre spår men öven något färskt</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5037,10 +5027,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125449555</v>
+        <v>125456232</v>
       </c>
       <c r="B45" t="n">
-        <v>80071</v>
+        <v>57651</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5048,34 +5038,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533527</v>
+        <v>533493</v>
       </c>
       <c r="R45" t="n">
-        <v>6885657</v>
+        <v>6884951</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5108,6 +5103,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Mest äldre spår men öven något färskt</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5239,7 +5239,7 @@
         <v>125456035</v>
       </c>
       <c r="B47" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>125457380</v>
       </c>
       <c r="B48" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5439,32 +5439,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125451683</v>
+        <v>125450555</v>
       </c>
       <c r="B49" t="n">
-        <v>80100</v>
+        <v>78972</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5474,10 +5474,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>533471</v>
+        <v>533508</v>
       </c>
       <c r="R49" t="n">
-        <v>6885526</v>
+        <v>6885633</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5536,32 +5536,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125450555</v>
+        <v>125451683</v>
       </c>
       <c r="B50" t="n">
-        <v>78968</v>
+        <v>80104</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5571,10 +5571,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>533508</v>
+        <v>533471</v>
       </c>
       <c r="R50" t="n">
-        <v>6885633</v>
+        <v>6885526</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5633,37 +5633,38 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125451692</v>
+        <v>125451954</v>
       </c>
       <c r="B51" t="n">
-        <v>98334</v>
+        <v>56834</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>22</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5672,10 +5673,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>533471</v>
+        <v>533479</v>
       </c>
       <c r="R51" t="n">
-        <v>6885526</v>
+        <v>6885506</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5734,38 +5735,37 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125451954</v>
+        <v>125451692</v>
       </c>
       <c r="B52" t="n">
-        <v>56834</v>
+        <v>98338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>22</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5774,10 +5774,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>533479</v>
+        <v>533471</v>
       </c>
       <c r="R52" t="n">
-        <v>6885506</v>
+        <v>6885526</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5836,10 +5836,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125459017</v>
+        <v>125448879</v>
       </c>
       <c r="B53" t="n">
-        <v>91898</v>
+        <v>98338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5847,34 +5847,38 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533634</v>
+        <v>533558</v>
       </c>
       <c r="R53" t="n">
-        <v>6885654</v>
+        <v>6885696</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5936,7 +5940,7 @@
         <v>125452337</v>
       </c>
       <c r="B54" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6042,7 +6046,7 @@
         <v>125451445</v>
       </c>
       <c r="B55" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6136,50 +6140,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125453495</v>
+        <v>125459017</v>
       </c>
       <c r="B56" t="n">
-        <v>57651</v>
+        <v>91902</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>533487</v>
+        <v>533634</v>
       </c>
       <c r="R56" t="n">
-        <v>6885398</v>
+        <v>6885654</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6212,11 +6211,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6243,37 +6237,38 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125448879</v>
+        <v>125453495</v>
       </c>
       <c r="B57" t="n">
-        <v>98334</v>
+        <v>57651</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6282,10 +6277,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>533558</v>
+        <v>533487</v>
       </c>
       <c r="R57" t="n">
-        <v>6885696</v>
+        <v>6885398</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6318,6 +6313,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6347,7 +6347,7 @@
         <v>125456355</v>
       </c>
       <c r="B58" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>125457312</v>
       </c>
       <c r="B59" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>125455687</v>
       </c>
       <c r="B60" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>125452374</v>
       </c>
       <c r="B61" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125450152</v>
+        <v>125456968</v>
       </c>
       <c r="B62" t="n">
-        <v>78968</v>
+        <v>91232</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6747,34 +6747,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>533539</v>
+        <v>533562</v>
       </c>
       <c r="R62" t="n">
-        <v>6885645</v>
+        <v>6885408</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6833,10 +6833,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125456968</v>
+        <v>125450152</v>
       </c>
       <c r="B63" t="n">
-        <v>91228</v>
+        <v>78972</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6844,34 +6844,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>533562</v>
+        <v>533539</v>
       </c>
       <c r="R63" t="n">
-        <v>6885408</v>
+        <v>6885645</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6930,10 +6930,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125451409</v>
+        <v>125448352</v>
       </c>
       <c r="B64" t="n">
-        <v>57651</v>
+        <v>91232</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6941,39 +6941,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>533498</v>
+        <v>533568</v>
       </c>
       <c r="R64" t="n">
-        <v>6885552</v>
+        <v>6885736</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7006,11 +7001,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall. Både äldre spår och färska</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7037,10 +7027,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125448352</v>
+        <v>125451409</v>
       </c>
       <c r="B65" t="n">
-        <v>91228</v>
+        <v>57651</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7048,34 +7038,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>533568</v>
+        <v>533498</v>
       </c>
       <c r="R65" t="n">
-        <v>6885736</v>
+        <v>6885552</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7108,6 +7103,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall. Både äldre spår och färska</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7134,27 +7134,27 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125450235</v>
+        <v>125448834</v>
       </c>
       <c r="B66" t="n">
-        <v>57651</v>
+        <v>58020</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7165,7 +7165,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7174,10 +7174,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>533551</v>
+        <v>533571</v>
       </c>
       <c r="R66" t="n">
-        <v>6885632</v>
+        <v>6885716</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7210,11 +7210,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7241,45 +7236,49 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125451627</v>
+        <v>125452794</v>
       </c>
       <c r="B67" t="n">
-        <v>80071</v>
+        <v>98338</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>533471</v>
+        <v>533476</v>
       </c>
       <c r="R67" t="n">
-        <v>6885526</v>
+        <v>6885492</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7338,10 +7337,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125451247</v>
+        <v>125450235</v>
       </c>
       <c r="B68" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7349,34 +7348,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533498</v>
+        <v>533551</v>
       </c>
       <c r="R68" t="n">
-        <v>6885552</v>
+        <v>6885632</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7409,6 +7413,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7438,7 +7447,7 @@
         <v>125454471</v>
       </c>
       <c r="B69" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7532,50 +7541,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125448834</v>
+        <v>125451247</v>
       </c>
       <c r="B70" t="n">
-        <v>58020</v>
+        <v>78972</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533571</v>
+        <v>533498</v>
       </c>
       <c r="R70" t="n">
-        <v>6885716</v>
+        <v>6885552</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7634,10 +7638,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125449765</v>
+        <v>125451627</v>
       </c>
       <c r="B71" t="n">
-        <v>78968</v>
+        <v>80075</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7645,21 +7649,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7669,10 +7673,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>533527</v>
+        <v>533471</v>
       </c>
       <c r="R71" t="n">
-        <v>6885657</v>
+        <v>6885526</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7731,10 +7735,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125448531</v>
+        <v>125449765</v>
       </c>
       <c r="B72" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7766,10 +7770,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>533571</v>
+        <v>533527</v>
       </c>
       <c r="R72" t="n">
-        <v>6885716</v>
+        <v>6885657</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7828,49 +7832,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125452794</v>
+        <v>125448531</v>
       </c>
       <c r="B73" t="n">
-        <v>98334</v>
+        <v>78972</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>533476</v>
+        <v>533571</v>
       </c>
       <c r="R73" t="n">
-        <v>6885492</v>
+        <v>6885716</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7929,10 +7929,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125452693</v>
+        <v>125456893</v>
       </c>
       <c r="B74" t="n">
-        <v>56227</v>
+        <v>57651</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7940,39 +7940,48 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>533485</v>
+        <v>533561</v>
       </c>
       <c r="R74" t="n">
-        <v>6885472</v>
+        <v>6885192</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8031,10 +8040,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125456893</v>
+        <v>125452693</v>
       </c>
       <c r="B75" t="n">
-        <v>57651</v>
+        <v>56227</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8042,48 +8051,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>533561</v>
+        <v>533485</v>
       </c>
       <c r="R75" t="n">
-        <v>6885192</v>
+        <v>6885472</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8142,10 +8142,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125456406</v>
+        <v>125450898</v>
       </c>
       <c r="B76" t="n">
-        <v>57648</v>
+        <v>80075</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8153,39 +8153,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>533520</v>
+        <v>533518</v>
       </c>
       <c r="R76" t="n">
-        <v>6885018</v>
+        <v>6885534</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8244,10 +8244,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125450898</v>
+        <v>125456406</v>
       </c>
       <c r="B77" t="n">
-        <v>80071</v>
+        <v>57648</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8255,39 +8255,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>533518</v>
+        <v>533520</v>
       </c>
       <c r="R77" t="n">
-        <v>6885534</v>
+        <v>6885018</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8346,45 +8346,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125456371</v>
+        <v>125454123</v>
       </c>
       <c r="B78" t="n">
-        <v>78968</v>
+        <v>97216</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>533602</v>
+        <v>533490</v>
       </c>
       <c r="R78" t="n">
-        <v>6885362</v>
+        <v>6885291</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8443,45 +8443,49 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125453817</v>
+        <v>125458100</v>
       </c>
       <c r="B79" t="n">
-        <v>80071</v>
+        <v>98338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>533455</v>
+        <v>533578</v>
       </c>
       <c r="R79" t="n">
-        <v>6885379</v>
+        <v>6885205</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8540,10 +8544,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125455827</v>
+        <v>125459043</v>
       </c>
       <c r="B80" t="n">
-        <v>91228</v>
+        <v>57651</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8551,34 +8555,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>533479</v>
+        <v>533634</v>
       </c>
       <c r="R80" t="n">
-        <v>6884999</v>
+        <v>6885654</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8611,6 +8620,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8637,10 +8651,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125459043</v>
+        <v>125453817</v>
       </c>
       <c r="B81" t="n">
-        <v>57651</v>
+        <v>80075</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8648,39 +8662,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>533634</v>
+        <v>533455</v>
       </c>
       <c r="R81" t="n">
-        <v>6885654</v>
+        <v>6885379</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8713,11 +8722,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8744,45 +8748,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125454123</v>
+        <v>125456371</v>
       </c>
       <c r="B82" t="n">
-        <v>97212</v>
+        <v>78972</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533490</v>
+        <v>533602</v>
       </c>
       <c r="R82" t="n">
-        <v>6885291</v>
+        <v>6885362</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8841,49 +8845,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125458100</v>
+        <v>125455827</v>
       </c>
       <c r="B83" t="n">
-        <v>98334</v>
+        <v>91232</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>533578</v>
+        <v>533479</v>
       </c>
       <c r="R83" t="n">
-        <v>6885205</v>
+        <v>6884999</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8942,10 +8942,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125449196</v>
+        <v>125458140</v>
       </c>
       <c r="B84" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8953,43 +8953,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>533558</v>
+        <v>533574</v>
       </c>
       <c r="R84" t="n">
-        <v>6885696</v>
+        <v>6885198</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9051,7 +9042,7 @@
         <v>125450671</v>
       </c>
       <c r="B85" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9149,10 +9140,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125458140</v>
+        <v>125449196</v>
       </c>
       <c r="B86" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9160,34 +9151,43 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>533574</v>
+        <v>533558</v>
       </c>
       <c r="R86" t="n">
-        <v>6885198</v>
+        <v>6885696</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9249,7 +9249,7 @@
         <v>125456250</v>
       </c>
       <c r="B87" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9352,45 +9352,49 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125458930</v>
+        <v>125450718</v>
       </c>
       <c r="B88" t="n">
-        <v>80071</v>
+        <v>98338</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>533634</v>
+        <v>533537</v>
       </c>
       <c r="R88" t="n">
-        <v>6885654</v>
+        <v>6885571</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9449,38 +9453,37 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125450505</v>
+        <v>125450452</v>
       </c>
       <c r="B89" t="n">
-        <v>80071</v>
+        <v>98338</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -9489,10 +9492,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>533526</v>
+        <v>533508</v>
       </c>
       <c r="R89" t="n">
-        <v>6885605</v>
+        <v>6885633</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9551,45 +9554,49 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125457133</v>
+        <v>125456788</v>
       </c>
       <c r="B90" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>533574</v>
+        <v>533556</v>
       </c>
       <c r="R90" t="n">
-        <v>6885404</v>
+        <v>6885155</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9648,10 +9655,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125457466</v>
+        <v>125457133</v>
       </c>
       <c r="B91" t="n">
-        <v>91228</v>
+        <v>78972</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9659,21 +9666,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9683,10 +9690,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>533602</v>
+        <v>533574</v>
       </c>
       <c r="R91" t="n">
-        <v>6885362</v>
+        <v>6885404</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9745,10 +9752,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125450188</v>
+        <v>125457466</v>
       </c>
       <c r="B92" t="n">
-        <v>57651</v>
+        <v>91232</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9756,39 +9763,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>533539</v>
+        <v>533602</v>
       </c>
       <c r="R92" t="n">
-        <v>6885634</v>
+        <v>6885362</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9821,11 +9823,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9852,10 +9849,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125452660</v>
+        <v>125449549</v>
       </c>
       <c r="B93" t="n">
-        <v>57651</v>
+        <v>80075</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9863,43 +9860,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>533535</v>
+        <v>533559</v>
       </c>
       <c r="R93" t="n">
-        <v>6885468</v>
+        <v>6885649</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9958,49 +9946,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125456788</v>
+        <v>125458930</v>
       </c>
       <c r="B94" t="n">
-        <v>98334</v>
+        <v>80075</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>533556</v>
+        <v>533634</v>
       </c>
       <c r="R94" t="n">
-        <v>6885155</v>
+        <v>6885654</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10059,37 +10043,38 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125450452</v>
+        <v>125450505</v>
       </c>
       <c r="B95" t="n">
-        <v>98334</v>
+        <v>80075</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -10098,10 +10083,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>533508</v>
+        <v>533526</v>
       </c>
       <c r="R95" t="n">
-        <v>6885633</v>
+        <v>6885605</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10160,10 +10145,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125449549</v>
+        <v>125450188</v>
       </c>
       <c r="B96" t="n">
-        <v>80071</v>
+        <v>57651</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10171,34 +10156,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>533559</v>
+        <v>533539</v>
       </c>
       <c r="R96" t="n">
-        <v>6885649</v>
+        <v>6885634</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10231,6 +10221,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10257,37 +10252,42 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125450718</v>
+        <v>125452660</v>
       </c>
       <c r="B97" t="n">
-        <v>98334</v>
+        <v>57651</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -10296,10 +10296,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>533537</v>
+        <v>533535</v>
       </c>
       <c r="R97" t="n">
-        <v>6885571</v>
+        <v>6885468</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>

--- a/artfynd/A 19766-2025 artfynd.xlsx
+++ b/artfynd/A 19766-2025 artfynd.xlsx
@@ -675,47 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125452107</v>
+        <v>125450747</v>
       </c>
       <c r="B2" t="n">
-        <v>57811</v>
+        <v>98359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533485</v>
+        <v>533545</v>
       </c>
       <c r="R2" t="n">
-        <v>6885472</v>
+        <v>6885577</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125452441</v>
+        <v>125452107</v>
       </c>
       <c r="B3" t="n">
-        <v>91250</v>
+        <v>57811</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,24 +787,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
@@ -883,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125449421</v>
+        <v>125454035</v>
       </c>
       <c r="B4" t="n">
-        <v>91232</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,34 +898,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533564</v>
+        <v>533438</v>
       </c>
       <c r="R4" t="n">
-        <v>6885654</v>
+        <v>6885340</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125454495</v>
+        <v>125452441</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>91250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -991,39 +1000,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533467</v>
+        <v>533485</v>
       </c>
       <c r="R5" t="n">
-        <v>6885270</v>
+        <v>6885472</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,11 +1060,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,37 +1086,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125450747</v>
+        <v>125454495</v>
       </c>
       <c r="B6" t="n">
-        <v>98359</v>
+        <v>57651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533545</v>
+        <v>533467</v>
       </c>
       <c r="R6" t="n">
-        <v>6885577</v>
+        <v>6885270</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1162,6 +1162,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125454035</v>
+        <v>125449421</v>
       </c>
       <c r="B7" t="n">
-        <v>78972</v>
+        <v>91232</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,39 +1204,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533438</v>
+        <v>533564</v>
       </c>
       <c r="R7" t="n">
-        <v>6885340</v>
+        <v>6885654</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125453207</v>
+        <v>125449144</v>
       </c>
       <c r="B13" t="n">
-        <v>80075</v>
+        <v>57651</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1818,34 +1818,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533421</v>
+        <v>533538</v>
       </c>
       <c r="R13" t="n">
-        <v>6885458</v>
+        <v>6885703</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1878,6 +1883,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1904,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125455217</v>
+        <v>125449764</v>
       </c>
       <c r="B14" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,34 +1925,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533571</v>
+        <v>533559</v>
       </c>
       <c r="R14" t="n">
-        <v>6885153</v>
+        <v>6885649</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1975,6 +1990,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2001,7 +2021,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125453918</v>
+        <v>125453207</v>
       </c>
       <c r="B15" t="n">
         <v>80075</v>
@@ -2036,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>533477</v>
+        <v>533421</v>
       </c>
       <c r="R15" t="n">
-        <v>6885329</v>
+        <v>6885458</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2098,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125449144</v>
+        <v>125455217</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2109,39 +2129,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533538</v>
+        <v>533571</v>
       </c>
       <c r="R16" t="n">
-        <v>6885703</v>
+        <v>6885153</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2174,11 +2189,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125449764</v>
+        <v>125453918</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>80075</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2216,39 +2226,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>533559</v>
+        <v>533477</v>
       </c>
       <c r="R17" t="n">
-        <v>6885649</v>
+        <v>6885329</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2281,11 +2286,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -4324,45 +4324,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125448393</v>
+        <v>125456221</v>
       </c>
       <c r="B38" t="n">
-        <v>97216</v>
+        <v>78972</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533568</v>
+        <v>533478</v>
       </c>
       <c r="R38" t="n">
-        <v>6885736</v>
+        <v>6884944</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4421,7 +4421,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125456221</v>
+        <v>125450387</v>
       </c>
       <c r="B39" t="n">
         <v>78972</v>
@@ -4452,14 +4452,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533478</v>
+        <v>533528</v>
       </c>
       <c r="R39" t="n">
-        <v>6884944</v>
+        <v>6885627</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4518,10 +4518,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125450387</v>
+        <v>125456538</v>
       </c>
       <c r="B40" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4529,34 +4529,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533528</v>
+        <v>533543</v>
       </c>
       <c r="R40" t="n">
-        <v>6885627</v>
+        <v>6885069</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4589,6 +4594,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4716,50 +4726,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125456538</v>
+        <v>125448393</v>
       </c>
       <c r="B42" t="n">
-        <v>57651</v>
+        <v>97216</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533543</v>
+        <v>533568</v>
       </c>
       <c r="R42" t="n">
-        <v>6885069</v>
+        <v>6885736</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4792,11 +4797,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5134,10 +5134,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125456732</v>
+        <v>125456035</v>
       </c>
       <c r="B46" t="n">
-        <v>57648</v>
+        <v>91232</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5145,39 +5145,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533566</v>
+        <v>533444</v>
       </c>
       <c r="R46" t="n">
-        <v>6885119</v>
+        <v>6884916</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5236,10 +5231,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125456035</v>
+        <v>125456732</v>
       </c>
       <c r="B47" t="n">
-        <v>91232</v>
+        <v>57648</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5247,34 +5242,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>533444</v>
+        <v>533566</v>
       </c>
       <c r="R47" t="n">
-        <v>6884916</v>
+        <v>6885119</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6736,7 +6736,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125456968</v>
+        <v>125448352</v>
       </c>
       <c r="B62" t="n">
         <v>91232</v>
@@ -6767,14 +6767,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>533562</v>
+        <v>533568</v>
       </c>
       <c r="R62" t="n">
-        <v>6885408</v>
+        <v>6885736</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6833,10 +6833,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125450152</v>
+        <v>125451409</v>
       </c>
       <c r="B63" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6844,34 +6844,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>533539</v>
+        <v>533498</v>
       </c>
       <c r="R63" t="n">
-        <v>6885645</v>
+        <v>6885552</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6904,6 +6909,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall. Både äldre spår och färska</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6930,7 +6940,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125448352</v>
+        <v>125456968</v>
       </c>
       <c r="B64" t="n">
         <v>91232</v>
@@ -6961,14 +6971,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>533568</v>
+        <v>533562</v>
       </c>
       <c r="R64" t="n">
-        <v>6885736</v>
+        <v>6885408</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7027,10 +7037,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125451409</v>
+        <v>125450152</v>
       </c>
       <c r="B65" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7038,39 +7048,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>533498</v>
+        <v>533539</v>
       </c>
       <c r="R65" t="n">
-        <v>6885552</v>
+        <v>6885645</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7103,11 +7108,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall. Både äldre spår och färska</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9352,7 +9352,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125450718</v>
+        <v>125456788</v>
       </c>
       <c r="B88" t="n">
         <v>98338</v>
@@ -9382,19 +9382,19 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>130</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>533537</v>
+        <v>533556</v>
       </c>
       <c r="R88" t="n">
-        <v>6885571</v>
+        <v>6885155</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9453,7 +9453,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125450452</v>
+        <v>125450718</v>
       </c>
       <c r="B89" t="n">
         <v>98338</v>
@@ -9483,7 +9483,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -9492,10 +9492,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>533508</v>
+        <v>533537</v>
       </c>
       <c r="R89" t="n">
-        <v>6885633</v>
+        <v>6885571</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9554,7 +9554,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125456788</v>
+        <v>125450452</v>
       </c>
       <c r="B90" t="n">
         <v>98338</v>
@@ -9584,19 +9584,19 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>533556</v>
+        <v>533508</v>
       </c>
       <c r="R90" t="n">
-        <v>6885155</v>
+        <v>6885633</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9655,10 +9655,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125457133</v>
+        <v>125449549</v>
       </c>
       <c r="B91" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9666,34 +9666,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>533574</v>
+        <v>533559</v>
       </c>
       <c r="R91" t="n">
-        <v>6885404</v>
+        <v>6885649</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9849,7 +9849,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125449549</v>
+        <v>125458930</v>
       </c>
       <c r="B93" t="n">
         <v>80075</v>
@@ -9884,10 +9884,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>533559</v>
+        <v>533634</v>
       </c>
       <c r="R93" t="n">
-        <v>6885649</v>
+        <v>6885654</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9946,10 +9946,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125458930</v>
+        <v>125457133</v>
       </c>
       <c r="B94" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9957,34 +9957,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>533634</v>
+        <v>533574</v>
       </c>
       <c r="R94" t="n">
-        <v>6885654</v>
+        <v>6885404</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>

--- a/artfynd/A 19766-2025 artfynd.xlsx
+++ b/artfynd/A 19766-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125450747</v>
+        <v>125449421</v>
       </c>
       <c r="B2" t="n">
-        <v>98359</v>
+        <v>91232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533545</v>
+        <v>533564</v>
       </c>
       <c r="R2" t="n">
-        <v>6885577</v>
+        <v>6885654</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125452107</v>
+        <v>125454035</v>
       </c>
       <c r="B3" t="n">
-        <v>57811</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,36 +783,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533485</v>
+        <v>533438</v>
       </c>
       <c r="R3" t="n">
-        <v>6885472</v>
+        <v>6885340</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125454035</v>
+        <v>125452441</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>91250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,39 +885,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533438</v>
+        <v>533485</v>
       </c>
       <c r="R4" t="n">
-        <v>6885340</v>
+        <v>6885472</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125452441</v>
+        <v>125454495</v>
       </c>
       <c r="B5" t="n">
-        <v>91250</v>
+        <v>57651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,34 +982,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533485</v>
+        <v>533467</v>
       </c>
       <c r="R5" t="n">
-        <v>6885472</v>
+        <v>6885270</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,6 +1047,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125454495</v>
+        <v>125452107</v>
       </c>
       <c r="B6" t="n">
-        <v>57651</v>
+        <v>57811</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1097,27 +1089,36 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1126,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533467</v>
+        <v>533485</v>
       </c>
       <c r="R6" t="n">
-        <v>6885270</v>
+        <v>6885472</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1162,11 +1163,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,45 +1189,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125449421</v>
+        <v>125450747</v>
       </c>
       <c r="B7" t="n">
-        <v>91232</v>
+        <v>98360</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533564</v>
+        <v>533545</v>
       </c>
       <c r="R7" t="n">
-        <v>6885654</v>
+        <v>6885577</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,37 +1290,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125455201</v>
+        <v>125458714</v>
       </c>
       <c r="B8" t="n">
-        <v>98338</v>
+        <v>57651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>200</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1329,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533571</v>
+        <v>533683</v>
       </c>
       <c r="R8" t="n">
-        <v>6885153</v>
+        <v>6885420</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1365,6 +1366,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1391,7 +1397,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125458714</v>
+        <v>125455042</v>
       </c>
       <c r="B9" t="n">
         <v>57651</v>
@@ -1431,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533683</v>
+        <v>533556</v>
       </c>
       <c r="R9" t="n">
-        <v>6885420</v>
+        <v>6885155</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,7 +1477,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,38 +1504,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125455042</v>
+        <v>125455201</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>98339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>200</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1538,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533556</v>
+        <v>533571</v>
       </c>
       <c r="R10" t="n">
-        <v>6885155</v>
+        <v>6885153</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,11 +1579,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1605,37 +1605,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125450058</v>
+        <v>125448798</v>
       </c>
       <c r="B11" t="n">
-        <v>98359</v>
+        <v>98339</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533564</v>
+        <v>533560</v>
       </c>
       <c r="R11" t="n">
-        <v>6885654</v>
+        <v>6885711</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1706,49 +1706,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125448798</v>
+        <v>125455217</v>
       </c>
       <c r="B12" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533560</v>
+        <v>533571</v>
       </c>
       <c r="R12" t="n">
-        <v>6885711</v>
+        <v>6885153</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,10 +1803,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125449144</v>
+        <v>125453918</v>
       </c>
       <c r="B13" t="n">
-        <v>57651</v>
+        <v>80075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1818,39 +1814,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533538</v>
+        <v>533477</v>
       </c>
       <c r="R13" t="n">
-        <v>6885703</v>
+        <v>6885329</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1883,11 +1874,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,10 +1900,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125449764</v>
+        <v>125453207</v>
       </c>
       <c r="B14" t="n">
-        <v>57651</v>
+        <v>80075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1925,39 +1911,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533559</v>
+        <v>533421</v>
       </c>
       <c r="R14" t="n">
-        <v>6885649</v>
+        <v>6885458</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1990,11 +1971,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2021,10 +1997,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125453207</v>
+        <v>125449144</v>
       </c>
       <c r="B15" t="n">
-        <v>80075</v>
+        <v>57651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,34 +2008,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>533421</v>
+        <v>533538</v>
       </c>
       <c r="R15" t="n">
-        <v>6885458</v>
+        <v>6885703</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2092,6 +2073,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2118,10 +2104,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125455217</v>
+        <v>125449764</v>
       </c>
       <c r="B16" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,34 +2115,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533571</v>
+        <v>533559</v>
       </c>
       <c r="R16" t="n">
-        <v>6885153</v>
+        <v>6885649</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2189,6 +2180,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2215,45 +2211,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125453918</v>
+        <v>125450058</v>
       </c>
       <c r="B17" t="n">
-        <v>80075</v>
+        <v>98360</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>533477</v>
+        <v>533564</v>
       </c>
       <c r="R17" t="n">
-        <v>6885329</v>
+        <v>6885654</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,45 +2312,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125451751</v>
+        <v>125456251</v>
       </c>
       <c r="B18" t="n">
-        <v>97216</v>
+        <v>91232</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>533503</v>
+        <v>533497</v>
       </c>
       <c r="R18" t="n">
-        <v>6885498</v>
+        <v>6884966</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,49 +2409,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125449821</v>
+        <v>125448326</v>
       </c>
       <c r="B19" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>533559</v>
+        <v>533568</v>
       </c>
       <c r="R19" t="n">
-        <v>6885649</v>
+        <v>6885736</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2510,49 +2506,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125449118</v>
+        <v>125449383</v>
       </c>
       <c r="B20" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>533549</v>
+        <v>533564</v>
       </c>
       <c r="R20" t="n">
-        <v>6885695</v>
+        <v>6885654</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2582,19 +2574,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2621,10 +2603,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125453277</v>
+        <v>125449396</v>
       </c>
       <c r="B21" t="n">
-        <v>57811</v>
+        <v>80075</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2632,39 +2614,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>533421</v>
+        <v>533550</v>
       </c>
       <c r="R21" t="n">
-        <v>6885458</v>
+        <v>6885685</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2917,10 +2894,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125449383</v>
+        <v>125453277</v>
       </c>
       <c r="B24" t="n">
-        <v>78972</v>
+        <v>57811</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2928,34 +2905,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533564</v>
+        <v>533421</v>
       </c>
       <c r="R24" t="n">
-        <v>6885654</v>
+        <v>6885458</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3014,45 +2996,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125448326</v>
+        <v>125449118</v>
       </c>
       <c r="B25" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533568</v>
+        <v>533549</v>
       </c>
       <c r="R25" t="n">
-        <v>6885736</v>
+        <v>6885695</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3082,9 +3068,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3111,45 +3107,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125456251</v>
+        <v>125449821</v>
       </c>
       <c r="B26" t="n">
-        <v>91232</v>
+        <v>98339</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533497</v>
+        <v>533559</v>
       </c>
       <c r="R26" t="n">
-        <v>6884966</v>
+        <v>6885649</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3208,32 +3208,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125449396</v>
+        <v>125451751</v>
       </c>
       <c r="B27" t="n">
-        <v>80075</v>
+        <v>97217</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533550</v>
+        <v>533503</v>
       </c>
       <c r="R27" t="n">
-        <v>6885685</v>
+        <v>6885498</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3305,49 +3305,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125449273</v>
+        <v>125457210</v>
       </c>
       <c r="B28" t="n">
-        <v>98338</v>
+        <v>57651</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>37</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533550</v>
+        <v>533578</v>
       </c>
       <c r="R28" t="n">
-        <v>6885685</v>
+        <v>6885205</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3380,6 +3381,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3406,10 +3412,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125448667</v>
+        <v>125456654</v>
       </c>
       <c r="B29" t="n">
-        <v>80075</v>
+        <v>57651</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3417,34 +3423,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533560</v>
+        <v>533587</v>
       </c>
       <c r="R29" t="n">
-        <v>6885711</v>
+        <v>6885384</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3477,6 +3488,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3503,7 +3519,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125457210</v>
+        <v>125455421</v>
       </c>
       <c r="B30" t="n">
         <v>57651</v>
@@ -3531,10 +3547,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3543,10 +3563,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533578</v>
+        <v>533497</v>
       </c>
       <c r="R30" t="n">
-        <v>6885205</v>
+        <v>6885148</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3579,11 +3599,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3610,38 +3625,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125456654</v>
+        <v>125451793</v>
       </c>
       <c r="B31" t="n">
-        <v>57651</v>
+        <v>98339</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>200</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3650,10 +3664,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533587</v>
+        <v>533474</v>
       </c>
       <c r="R31" t="n">
-        <v>6885384</v>
+        <v>6885517</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3686,11 +3700,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3717,10 +3726,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125455421</v>
+        <v>125448667</v>
       </c>
       <c r="B32" t="n">
-        <v>57651</v>
+        <v>80075</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3728,43 +3737,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533497</v>
+        <v>533560</v>
       </c>
       <c r="R32" t="n">
-        <v>6885148</v>
+        <v>6885711</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3823,10 +3823,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125457445</v>
+        <v>125449273</v>
       </c>
       <c r="B33" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3858,14 +3858,14 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533577</v>
+        <v>533550</v>
       </c>
       <c r="R33" t="n">
-        <v>6885438</v>
+        <v>6885685</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3924,37 +3924,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125451793</v>
+        <v>125451213</v>
       </c>
       <c r="B34" t="n">
-        <v>98338</v>
+        <v>98360</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533474</v>
+        <v>533490</v>
       </c>
       <c r="R34" t="n">
-        <v>6885517</v>
+        <v>6885584</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4025,49 +4025,49 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125451213</v>
+        <v>125457445</v>
       </c>
       <c r="B35" t="n">
-        <v>98359</v>
+        <v>98339</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>37</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533490</v>
+        <v>533577</v>
       </c>
       <c r="R35" t="n">
-        <v>6885584</v>
+        <v>6885438</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4126,45 +4126,49 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125450637</v>
+        <v>125450818</v>
       </c>
       <c r="B36" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533545</v>
+        <v>533494</v>
       </c>
       <c r="R36" t="n">
-        <v>6885577</v>
+        <v>6885624</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4223,49 +4227,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125450818</v>
+        <v>125450637</v>
       </c>
       <c r="B37" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533494</v>
+        <v>533545</v>
       </c>
       <c r="R37" t="n">
-        <v>6885624</v>
+        <v>6885577</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4324,45 +4324,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125456221</v>
+        <v>125448393</v>
       </c>
       <c r="B38" t="n">
-        <v>78972</v>
+        <v>97217</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533478</v>
+        <v>533568</v>
       </c>
       <c r="R38" t="n">
-        <v>6884944</v>
+        <v>6885736</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4421,45 +4421,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125450387</v>
+        <v>125451578</v>
       </c>
       <c r="B39" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533528</v>
+        <v>533480</v>
       </c>
       <c r="R39" t="n">
-        <v>6885627</v>
+        <v>6885534</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4518,10 +4522,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125456538</v>
+        <v>125456221</v>
       </c>
       <c r="B40" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4529,39 +4533,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533543</v>
+        <v>533478</v>
       </c>
       <c r="R40" t="n">
-        <v>6885069</v>
+        <v>6884944</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4594,11 +4593,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4625,49 +4619,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125451578</v>
+        <v>125450387</v>
       </c>
       <c r="B41" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533480</v>
+        <v>533528</v>
       </c>
       <c r="R41" t="n">
-        <v>6885534</v>
+        <v>6885627</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4726,45 +4716,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125448393</v>
+        <v>125456538</v>
       </c>
       <c r="B42" t="n">
-        <v>97216</v>
+        <v>57651</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533568</v>
+        <v>533543</v>
       </c>
       <c r="R42" t="n">
-        <v>6885736</v>
+        <v>6885069</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4797,6 +4792,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5134,10 +5134,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125456035</v>
+        <v>125456732</v>
       </c>
       <c r="B46" t="n">
-        <v>91232</v>
+        <v>57648</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5145,34 +5145,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533444</v>
+        <v>533566</v>
       </c>
       <c r="R46" t="n">
-        <v>6884916</v>
+        <v>6885119</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5231,10 +5236,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125456732</v>
+        <v>125456035</v>
       </c>
       <c r="B47" t="n">
-        <v>57648</v>
+        <v>91232</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5242,39 +5247,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>533566</v>
+        <v>533444</v>
       </c>
       <c r="R47" t="n">
-        <v>6885119</v>
+        <v>6884916</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5333,10 +5333,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125457380</v>
+        <v>125450555</v>
       </c>
       <c r="B48" t="n">
-        <v>91528</v>
+        <v>78972</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5344,43 +5344,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533577</v>
+        <v>533508</v>
       </c>
       <c r="R48" t="n">
-        <v>6885438</v>
+        <v>6885633</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5439,10 +5430,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125450555</v>
+        <v>125451954</v>
       </c>
       <c r="B49" t="n">
-        <v>78972</v>
+        <v>56834</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5450,34 +5441,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>533508</v>
+        <v>533479</v>
       </c>
       <c r="R49" t="n">
-        <v>6885633</v>
+        <v>6885506</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5536,45 +5532,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125451683</v>
+        <v>125457380</v>
       </c>
       <c r="B50" t="n">
-        <v>80104</v>
+        <v>91528</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>533471</v>
+        <v>533577</v>
       </c>
       <c r="R50" t="n">
-        <v>6885526</v>
+        <v>6885438</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5633,50 +5638,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125451954</v>
+        <v>125451683</v>
       </c>
       <c r="B51" t="n">
-        <v>56834</v>
+        <v>80104</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>533479</v>
+        <v>533471</v>
       </c>
       <c r="R51" t="n">
-        <v>6885506</v>
+        <v>6885526</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5738,7 +5738,7 @@
         <v>125451692</v>
       </c>
       <c r="B52" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5836,10 +5836,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125448879</v>
+        <v>125459017</v>
       </c>
       <c r="B53" t="n">
-        <v>98338</v>
+        <v>91902</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5847,38 +5847,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>898</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533558</v>
+        <v>533634</v>
       </c>
       <c r="R53" t="n">
-        <v>6885696</v>
+        <v>6885654</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5937,10 +5933,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125452337</v>
+        <v>125453495</v>
       </c>
       <c r="B54" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5948,31 +5944,27 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5981,10 +5973,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>533485</v>
+        <v>533487</v>
       </c>
       <c r="R54" t="n">
-        <v>6885472</v>
+        <v>6885398</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6017,6 +6009,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6043,45 +6040,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125451445</v>
+        <v>125452337</v>
       </c>
       <c r="B55" t="n">
-        <v>80104</v>
+        <v>78972</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>533474</v>
+        <v>533485</v>
       </c>
       <c r="R55" t="n">
-        <v>6885569</v>
+        <v>6885472</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6140,32 +6146,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125459017</v>
+        <v>125451445</v>
       </c>
       <c r="B56" t="n">
-        <v>91902</v>
+        <v>80104</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>898</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6175,10 +6181,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>533634</v>
+        <v>533474</v>
       </c>
       <c r="R56" t="n">
-        <v>6885654</v>
+        <v>6885569</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6237,38 +6243,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125453495</v>
+        <v>125448879</v>
       </c>
       <c r="B57" t="n">
-        <v>57651</v>
+        <v>98339</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6277,10 +6282,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>533487</v>
+        <v>533558</v>
       </c>
       <c r="R57" t="n">
-        <v>6885398</v>
+        <v>6885696</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6313,11 +6318,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6344,49 +6344,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125456355</v>
+        <v>125457312</v>
       </c>
       <c r="B58" t="n">
-        <v>98338</v>
+        <v>91232</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>533513</v>
+        <v>533577</v>
       </c>
       <c r="R58" t="n">
-        <v>6885005</v>
+        <v>6885438</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6445,7 +6441,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125457312</v>
+        <v>125455687</v>
       </c>
       <c r="B59" t="n">
         <v>91232</v>
@@ -6480,10 +6476,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>533577</v>
+        <v>533469</v>
       </c>
       <c r="R59" t="n">
-        <v>6885438</v>
+        <v>6885049</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6542,7 +6538,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125455687</v>
+        <v>125452374</v>
       </c>
       <c r="B60" t="n">
         <v>91232</v>
@@ -6573,14 +6569,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>533469</v>
+        <v>533550</v>
       </c>
       <c r="R60" t="n">
-        <v>6885049</v>
+        <v>6885458</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6639,45 +6635,49 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125452374</v>
+        <v>125456355</v>
       </c>
       <c r="B61" t="n">
-        <v>91232</v>
+        <v>98339</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>533550</v>
+        <v>533513</v>
       </c>
       <c r="R61" t="n">
-        <v>6885458</v>
+        <v>6885005</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6833,10 +6833,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125451409</v>
+        <v>125456968</v>
       </c>
       <c r="B63" t="n">
-        <v>57651</v>
+        <v>91232</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6844,39 +6844,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>533498</v>
+        <v>533562</v>
       </c>
       <c r="R63" t="n">
-        <v>6885552</v>
+        <v>6885408</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6909,11 +6904,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall. Både äldre spår och färska</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6940,10 +6930,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125456968</v>
+        <v>125450152</v>
       </c>
       <c r="B64" t="n">
-        <v>91232</v>
+        <v>78972</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6951,34 +6941,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>533562</v>
+        <v>533539</v>
       </c>
       <c r="R64" t="n">
-        <v>6885408</v>
+        <v>6885645</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7037,10 +7027,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125450152</v>
+        <v>125451409</v>
       </c>
       <c r="B65" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7048,34 +7038,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>533539</v>
+        <v>533498</v>
       </c>
       <c r="R65" t="n">
-        <v>6885645</v>
+        <v>6885552</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7108,6 +7103,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall. Både äldre spår och färska</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7134,50 +7134,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125448834</v>
+        <v>125451247</v>
       </c>
       <c r="B66" t="n">
-        <v>58020</v>
+        <v>78972</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>533571</v>
+        <v>533498</v>
       </c>
       <c r="R66" t="n">
-        <v>6885716</v>
+        <v>6885552</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7236,37 +7231,38 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125452794</v>
+        <v>125448834</v>
       </c>
       <c r="B67" t="n">
-        <v>98338</v>
+        <v>58020</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7275,10 +7271,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>533476</v>
+        <v>533571</v>
       </c>
       <c r="R67" t="n">
-        <v>6885492</v>
+        <v>6885716</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7337,38 +7333,37 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125450235</v>
+        <v>125452794</v>
       </c>
       <c r="B68" t="n">
-        <v>57651</v>
+        <v>98339</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7377,10 +7372,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533551</v>
+        <v>533476</v>
       </c>
       <c r="R68" t="n">
-        <v>6885632</v>
+        <v>6885492</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7413,11 +7408,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7444,10 +7434,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125454471</v>
+        <v>125449765</v>
       </c>
       <c r="B69" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7455,21 +7445,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7479,10 +7469,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533467</v>
+        <v>533527</v>
       </c>
       <c r="R69" t="n">
-        <v>6885270</v>
+        <v>6885657</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7541,7 +7531,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125451247</v>
+        <v>125448531</v>
       </c>
       <c r="B70" t="n">
         <v>78972</v>
@@ -7576,10 +7566,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533498</v>
+        <v>533571</v>
       </c>
       <c r="R70" t="n">
-        <v>6885552</v>
+        <v>6885716</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7735,10 +7725,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125449765</v>
+        <v>125454471</v>
       </c>
       <c r="B72" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7746,21 +7736,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7770,10 +7760,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>533527</v>
+        <v>533467</v>
       </c>
       <c r="R72" t="n">
-        <v>6885657</v>
+        <v>6885270</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7832,10 +7822,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125448531</v>
+        <v>125450235</v>
       </c>
       <c r="B73" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7843,34 +7833,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>533571</v>
+        <v>533551</v>
       </c>
       <c r="R73" t="n">
-        <v>6885716</v>
+        <v>6885632</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7903,6 +7898,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7929,10 +7929,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125456893</v>
+        <v>125452693</v>
       </c>
       <c r="B74" t="n">
-        <v>57651</v>
+        <v>56227</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7940,48 +7940,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>533561</v>
+        <v>533485</v>
       </c>
       <c r="R74" t="n">
-        <v>6885192</v>
+        <v>6885472</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8040,10 +8031,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125452693</v>
+        <v>125456893</v>
       </c>
       <c r="B75" t="n">
-        <v>56227</v>
+        <v>57651</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8051,39 +8042,48 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>533485</v>
+        <v>533561</v>
       </c>
       <c r="R75" t="n">
-        <v>6885472</v>
+        <v>6885192</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8142,10 +8142,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125450898</v>
+        <v>125456406</v>
       </c>
       <c r="B76" t="n">
-        <v>80075</v>
+        <v>57648</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8153,39 +8153,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>533518</v>
+        <v>533520</v>
       </c>
       <c r="R76" t="n">
-        <v>6885534</v>
+        <v>6885018</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8244,10 +8244,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125456406</v>
+        <v>125450898</v>
       </c>
       <c r="B77" t="n">
-        <v>57648</v>
+        <v>80075</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8255,39 +8255,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>533520</v>
+        <v>533518</v>
       </c>
       <c r="R77" t="n">
-        <v>6885018</v>
+        <v>6885534</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8346,32 +8346,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125454123</v>
+        <v>125453817</v>
       </c>
       <c r="B78" t="n">
-        <v>97216</v>
+        <v>80075</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8381,10 +8381,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>533490</v>
+        <v>533455</v>
       </c>
       <c r="R78" t="n">
-        <v>6885291</v>
+        <v>6885379</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8443,49 +8443,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125458100</v>
+        <v>125455827</v>
       </c>
       <c r="B79" t="n">
-        <v>98338</v>
+        <v>91232</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>533578</v>
+        <v>533479</v>
       </c>
       <c r="R79" t="n">
-        <v>6885205</v>
+        <v>6884999</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8544,50 +8540,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125459043</v>
+        <v>125454123</v>
       </c>
       <c r="B80" t="n">
-        <v>57651</v>
+        <v>97217</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>533634</v>
+        <v>533490</v>
       </c>
       <c r="R80" t="n">
-        <v>6885654</v>
+        <v>6885291</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8620,11 +8611,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8651,45 +8637,49 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125453817</v>
+        <v>125458100</v>
       </c>
       <c r="B81" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>533455</v>
+        <v>533578</v>
       </c>
       <c r="R81" t="n">
-        <v>6885379</v>
+        <v>6885205</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8845,10 +8835,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125455827</v>
+        <v>125459043</v>
       </c>
       <c r="B83" t="n">
-        <v>91232</v>
+        <v>57651</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8856,34 +8846,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>533479</v>
+        <v>533634</v>
       </c>
       <c r="R83" t="n">
-        <v>6884999</v>
+        <v>6885654</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8916,6 +8911,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8942,10 +8942,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125458140</v>
+        <v>125456250</v>
       </c>
       <c r="B84" t="n">
-        <v>78972</v>
+        <v>91250</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8953,34 +8953,43 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>533574</v>
+        <v>533602</v>
       </c>
       <c r="R84" t="n">
-        <v>6885198</v>
+        <v>6885362</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9039,49 +9048,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125450671</v>
+        <v>125458140</v>
       </c>
       <c r="B85" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>533493</v>
+        <v>533574</v>
       </c>
       <c r="R85" t="n">
-        <v>6885612</v>
+        <v>6885198</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9246,54 +9251,49 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125456250</v>
+        <v>125450671</v>
       </c>
       <c r="B87" t="n">
-        <v>91250</v>
+        <v>98339</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>533602</v>
+        <v>533493</v>
       </c>
       <c r="R87" t="n">
-        <v>6885362</v>
+        <v>6885612</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9352,49 +9352,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125456788</v>
+        <v>125457466</v>
       </c>
       <c r="B88" t="n">
-        <v>98338</v>
+        <v>91232</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>533556</v>
+        <v>533602</v>
       </c>
       <c r="R88" t="n">
-        <v>6885155</v>
+        <v>6885362</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9453,49 +9449,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125450718</v>
+        <v>125449549</v>
       </c>
       <c r="B89" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>533537</v>
+        <v>533559</v>
       </c>
       <c r="R89" t="n">
-        <v>6885571</v>
+        <v>6885649</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9554,49 +9546,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125450452</v>
+        <v>125457133</v>
       </c>
       <c r="B90" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>533508</v>
+        <v>533574</v>
       </c>
       <c r="R90" t="n">
-        <v>6885633</v>
+        <v>6885404</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9655,7 +9643,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125449549</v>
+        <v>125458930</v>
       </c>
       <c r="B91" t="n">
         <v>80075</v>
@@ -9690,10 +9678,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>533559</v>
+        <v>533634</v>
       </c>
       <c r="R91" t="n">
-        <v>6885649</v>
+        <v>6885654</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9752,10 +9740,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125457466</v>
+        <v>125450505</v>
       </c>
       <c r="B92" t="n">
-        <v>91232</v>
+        <v>80075</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9763,34 +9751,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>533602</v>
+        <v>533526</v>
       </c>
       <c r="R92" t="n">
-        <v>6885362</v>
+        <v>6885605</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9849,10 +9842,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125458930</v>
+        <v>125450188</v>
       </c>
       <c r="B93" t="n">
-        <v>80075</v>
+        <v>57651</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9860,34 +9853,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>533634</v>
+        <v>533539</v>
       </c>
       <c r="R93" t="n">
-        <v>6885654</v>
+        <v>6885634</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9920,6 +9918,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9946,10 +9949,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125457133</v>
+        <v>125452660</v>
       </c>
       <c r="B94" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9957,34 +9960,43 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>533574</v>
+        <v>533535</v>
       </c>
       <c r="R94" t="n">
-        <v>6885404</v>
+        <v>6885468</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10043,50 +10055,49 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125450505</v>
+        <v>125456788</v>
       </c>
       <c r="B95" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>130</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>533526</v>
+        <v>533556</v>
       </c>
       <c r="R95" t="n">
-        <v>6885605</v>
+        <v>6885155</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10145,38 +10156,37 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125450188</v>
+        <v>125450718</v>
       </c>
       <c r="B96" t="n">
-        <v>57651</v>
+        <v>98339</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -10185,10 +10195,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>533539</v>
+        <v>533537</v>
       </c>
       <c r="R96" t="n">
-        <v>6885634</v>
+        <v>6885571</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10221,11 +10231,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10252,42 +10257,37 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125452660</v>
+        <v>125450452</v>
       </c>
       <c r="B97" t="n">
-        <v>57651</v>
+        <v>98339</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -10296,10 +10296,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>533535</v>
+        <v>533508</v>
       </c>
       <c r="R97" t="n">
-        <v>6885468</v>
+        <v>6885633</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>

--- a/artfynd/A 19766-2025 artfynd.xlsx
+++ b/artfynd/A 19766-2025 artfynd.xlsx
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125448326</v>
+        <v>125452738</v>
       </c>
       <c r="B19" t="n">
         <v>78972</v>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>533568</v>
+        <v>533500</v>
       </c>
       <c r="R19" t="n">
-        <v>6885736</v>
+        <v>6885440</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2506,7 +2506,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125449383</v>
+        <v>125452859</v>
       </c>
       <c r="B20" t="n">
         <v>78972</v>
@@ -2541,10 +2541,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>533564</v>
+        <v>533466</v>
       </c>
       <c r="R20" t="n">
-        <v>6885654</v>
+        <v>6885506</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2603,10 +2603,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125449396</v>
+        <v>125448326</v>
       </c>
       <c r="B21" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2614,21 +2614,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>533550</v>
+        <v>533568</v>
       </c>
       <c r="R21" t="n">
-        <v>6885685</v>
+        <v>6885736</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2700,7 +2700,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125452738</v>
+        <v>125449383</v>
       </c>
       <c r="B22" t="n">
         <v>78972</v>
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533500</v>
+        <v>533564</v>
       </c>
       <c r="R22" t="n">
-        <v>6885440</v>
+        <v>6885654</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125452859</v>
+        <v>125449396</v>
       </c>
       <c r="B23" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2808,21 +2808,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533466</v>
+        <v>533550</v>
       </c>
       <c r="R23" t="n">
-        <v>6885506</v>
+        <v>6885685</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2996,7 +2996,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125449118</v>
+        <v>125449821</v>
       </c>
       <c r="B25" t="n">
         <v>98339</v>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533549</v>
+        <v>533559</v>
       </c>
       <c r="R25" t="n">
-        <v>6885695</v>
+        <v>6885649</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3068,19 +3068,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3107,7 +3097,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125449821</v>
+        <v>125449118</v>
       </c>
       <c r="B26" t="n">
         <v>98339</v>
@@ -3137,7 +3127,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3146,10 +3136,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533559</v>
+        <v>533549</v>
       </c>
       <c r="R26" t="n">
-        <v>6885649</v>
+        <v>6885695</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3179,9 +3169,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4324,45 +4324,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125448393</v>
+        <v>125456221</v>
       </c>
       <c r="B38" t="n">
-        <v>97217</v>
+        <v>78972</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533568</v>
+        <v>533478</v>
       </c>
       <c r="R38" t="n">
-        <v>6885736</v>
+        <v>6884944</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4421,49 +4421,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125451578</v>
+        <v>125450387</v>
       </c>
       <c r="B39" t="n">
-        <v>98339</v>
+        <v>78972</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533480</v>
+        <v>533528</v>
       </c>
       <c r="R39" t="n">
-        <v>6885534</v>
+        <v>6885627</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4522,10 +4518,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125456221</v>
+        <v>125456538</v>
       </c>
       <c r="B40" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4533,34 +4529,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533478</v>
+        <v>533543</v>
       </c>
       <c r="R40" t="n">
-        <v>6884944</v>
+        <v>6885069</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4593,6 +4594,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4619,32 +4625,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125450387</v>
+        <v>125448393</v>
       </c>
       <c r="B41" t="n">
-        <v>78972</v>
+        <v>97217</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4654,10 +4660,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533528</v>
+        <v>533568</v>
       </c>
       <c r="R41" t="n">
-        <v>6885627</v>
+        <v>6885736</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4716,50 +4722,49 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125456538</v>
+        <v>125451578</v>
       </c>
       <c r="B42" t="n">
-        <v>57651</v>
+        <v>98339</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533543</v>
+        <v>533480</v>
       </c>
       <c r="R42" t="n">
-        <v>6885069</v>
+        <v>6885534</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4792,11 +4797,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5333,10 +5333,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125450555</v>
+        <v>125451954</v>
       </c>
       <c r="B48" t="n">
-        <v>78972</v>
+        <v>56834</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5344,34 +5344,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533508</v>
+        <v>533479</v>
       </c>
       <c r="R48" t="n">
-        <v>6885633</v>
+        <v>6885506</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5430,38 +5435,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125451954</v>
+        <v>125451692</v>
       </c>
       <c r="B49" t="n">
-        <v>56834</v>
+        <v>98339</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>22</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5470,10 +5474,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>533479</v>
+        <v>533471</v>
       </c>
       <c r="R49" t="n">
-        <v>6885506</v>
+        <v>6885526</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5638,32 +5642,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125451683</v>
+        <v>125450555</v>
       </c>
       <c r="B51" t="n">
-        <v>80104</v>
+        <v>78972</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5673,10 +5677,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>533471</v>
+        <v>533508</v>
       </c>
       <c r="R51" t="n">
-        <v>6885526</v>
+        <v>6885633</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5735,39 +5739,35 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125451692</v>
+        <v>125451683</v>
       </c>
       <c r="B52" t="n">
-        <v>98339</v>
+        <v>80104</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
@@ -5933,10 +5933,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125453495</v>
+        <v>125452337</v>
       </c>
       <c r="B54" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5944,27 +5944,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5973,10 +5977,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>533487</v>
+        <v>533485</v>
       </c>
       <c r="R54" t="n">
-        <v>6885398</v>
+        <v>6885472</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6009,11 +6013,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6040,54 +6039,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125452337</v>
+        <v>125451445</v>
       </c>
       <c r="B55" t="n">
-        <v>78972</v>
+        <v>80104</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>533485</v>
+        <v>533474</v>
       </c>
       <c r="R55" t="n">
-        <v>6885472</v>
+        <v>6885569</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6146,45 +6136,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125451445</v>
+        <v>125453495</v>
       </c>
       <c r="B56" t="n">
-        <v>80104</v>
+        <v>57651</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>533474</v>
+        <v>533487</v>
       </c>
       <c r="R56" t="n">
-        <v>6885569</v>
+        <v>6885398</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6217,6 +6212,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 19766-2025 artfynd.xlsx
+++ b/artfynd/A 19766-2025 artfynd.xlsx
@@ -1605,37 +1605,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125448798</v>
+        <v>125449144</v>
       </c>
       <c r="B11" t="n">
-        <v>98339</v>
+        <v>57651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>90</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1644,10 +1645,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533560</v>
+        <v>533538</v>
       </c>
       <c r="R11" t="n">
-        <v>6885711</v>
+        <v>6885703</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,6 +1681,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1706,10 +1712,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125455217</v>
+        <v>125449764</v>
       </c>
       <c r="B12" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1717,34 +1723,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533571</v>
+        <v>533559</v>
       </c>
       <c r="R12" t="n">
-        <v>6885153</v>
+        <v>6885649</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1777,6 +1788,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1803,10 +1819,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125453918</v>
+        <v>125455217</v>
       </c>
       <c r="B13" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1814,34 +1830,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533477</v>
+        <v>533571</v>
       </c>
       <c r="R13" t="n">
-        <v>6885329</v>
+        <v>6885153</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,7 +1916,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125453207</v>
+        <v>125453918</v>
       </c>
       <c r="B14" t="n">
         <v>80075</v>
@@ -1935,10 +1951,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533421</v>
+        <v>533477</v>
       </c>
       <c r="R14" t="n">
-        <v>6885458</v>
+        <v>6885329</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1997,10 +2013,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125449144</v>
+        <v>125453207</v>
       </c>
       <c r="B15" t="n">
-        <v>57651</v>
+        <v>80075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2008,39 +2024,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>533538</v>
+        <v>533421</v>
       </c>
       <c r="R15" t="n">
-        <v>6885703</v>
+        <v>6885458</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2073,11 +2084,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2104,38 +2110,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125449764</v>
+        <v>125448798</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>98339</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>90</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2144,10 +2149,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533559</v>
+        <v>533560</v>
       </c>
       <c r="R16" t="n">
-        <v>6885649</v>
+        <v>6885711</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2180,11 +2185,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125452738</v>
+        <v>125448326</v>
       </c>
       <c r="B19" t="n">
         <v>78972</v>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>533500</v>
+        <v>533568</v>
       </c>
       <c r="R19" t="n">
-        <v>6885440</v>
+        <v>6885736</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2506,7 +2506,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125452859</v>
+        <v>125449383</v>
       </c>
       <c r="B20" t="n">
         <v>78972</v>
@@ -2541,10 +2541,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>533466</v>
+        <v>533564</v>
       </c>
       <c r="R20" t="n">
-        <v>6885506</v>
+        <v>6885654</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2603,10 +2603,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125448326</v>
+        <v>125449396</v>
       </c>
       <c r="B21" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2614,21 +2614,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>533568</v>
+        <v>533550</v>
       </c>
       <c r="R21" t="n">
-        <v>6885736</v>
+        <v>6885685</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2700,7 +2700,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125449383</v>
+        <v>125452738</v>
       </c>
       <c r="B22" t="n">
         <v>78972</v>
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533564</v>
+        <v>533500</v>
       </c>
       <c r="R22" t="n">
-        <v>6885654</v>
+        <v>6885440</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125449396</v>
+        <v>125452859</v>
       </c>
       <c r="B23" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2808,21 +2808,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533550</v>
+        <v>533466</v>
       </c>
       <c r="R23" t="n">
-        <v>6885685</v>
+        <v>6885506</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2996,7 +2996,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125449821</v>
+        <v>125449118</v>
       </c>
       <c r="B25" t="n">
         <v>98339</v>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533559</v>
+        <v>533549</v>
       </c>
       <c r="R25" t="n">
-        <v>6885649</v>
+        <v>6885695</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3068,9 +3068,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3097,7 +3107,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125449118</v>
+        <v>125449821</v>
       </c>
       <c r="B26" t="n">
         <v>98339</v>
@@ -3127,7 +3137,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3136,10 +3146,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533549</v>
+        <v>533559</v>
       </c>
       <c r="R26" t="n">
-        <v>6885695</v>
+        <v>6885649</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3169,19 +3179,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4823,10 +4823,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125449555</v>
+        <v>125456823</v>
       </c>
       <c r="B43" t="n">
-        <v>80075</v>
+        <v>57651</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4834,34 +4834,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533527</v>
+        <v>533580</v>
       </c>
       <c r="R43" t="n">
-        <v>6885657</v>
+        <v>6885391</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4894,6 +4899,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4920,7 +4930,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125456823</v>
+        <v>125456232</v>
       </c>
       <c r="B44" t="n">
         <v>57651</v>
@@ -4951,7 +4961,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4960,10 +4970,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533580</v>
+        <v>533493</v>
       </c>
       <c r="R44" t="n">
-        <v>6885391</v>
+        <v>6884951</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5000,7 +5010,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall.  Mest äldre spår men öven något färskt</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5027,10 +5037,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125456232</v>
+        <v>125449555</v>
       </c>
       <c r="B45" t="n">
-        <v>57651</v>
+        <v>80075</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5038,39 +5048,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533493</v>
+        <v>533527</v>
       </c>
       <c r="R45" t="n">
-        <v>6884951</v>
+        <v>6885657</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5103,11 +5108,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.  Mest äldre spår men öven något färskt</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5134,10 +5134,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125456732</v>
+        <v>125456035</v>
       </c>
       <c r="B46" t="n">
-        <v>57648</v>
+        <v>91232</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5145,39 +5145,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533566</v>
+        <v>533444</v>
       </c>
       <c r="R46" t="n">
-        <v>6885119</v>
+        <v>6884916</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5236,10 +5231,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125456035</v>
+        <v>125456732</v>
       </c>
       <c r="B47" t="n">
-        <v>91232</v>
+        <v>57648</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5247,34 +5242,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>533444</v>
+        <v>533566</v>
       </c>
       <c r="R47" t="n">
-        <v>6884916</v>
+        <v>6885119</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5933,10 +5933,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125452337</v>
+        <v>125453495</v>
       </c>
       <c r="B54" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5944,31 +5944,27 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5977,10 +5973,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>533485</v>
+        <v>533487</v>
       </c>
       <c r="R54" t="n">
-        <v>6885472</v>
+        <v>6885398</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6013,6 +6009,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6039,45 +6040,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125451445</v>
+        <v>125452337</v>
       </c>
       <c r="B55" t="n">
-        <v>80104</v>
+        <v>78972</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>533474</v>
+        <v>533485</v>
       </c>
       <c r="R55" t="n">
-        <v>6885569</v>
+        <v>6885472</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6136,50 +6146,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125453495</v>
+        <v>125451445</v>
       </c>
       <c r="B56" t="n">
-        <v>57651</v>
+        <v>80104</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>533487</v>
+        <v>533474</v>
       </c>
       <c r="R56" t="n">
-        <v>6885398</v>
+        <v>6885569</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6212,11 +6217,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6344,45 +6344,49 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125457312</v>
+        <v>125456355</v>
       </c>
       <c r="B58" t="n">
-        <v>91232</v>
+        <v>98339</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>533577</v>
+        <v>533513</v>
       </c>
       <c r="R58" t="n">
-        <v>6885438</v>
+        <v>6885005</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6441,7 +6445,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125455687</v>
+        <v>125457312</v>
       </c>
       <c r="B59" t="n">
         <v>91232</v>
@@ -6476,10 +6480,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>533469</v>
+        <v>533577</v>
       </c>
       <c r="R59" t="n">
-        <v>6885049</v>
+        <v>6885438</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6538,7 +6542,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125452374</v>
+        <v>125455687</v>
       </c>
       <c r="B60" t="n">
         <v>91232</v>
@@ -6569,14 +6573,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>533550</v>
+        <v>533469</v>
       </c>
       <c r="R60" t="n">
-        <v>6885458</v>
+        <v>6885049</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6635,49 +6639,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125456355</v>
+        <v>125452374</v>
       </c>
       <c r="B61" t="n">
-        <v>98339</v>
+        <v>91232</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>533513</v>
+        <v>533550</v>
       </c>
       <c r="R61" t="n">
-        <v>6885005</v>
+        <v>6885458</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7134,7 +7134,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125451247</v>
+        <v>125449765</v>
       </c>
       <c r="B66" t="n">
         <v>78972</v>
@@ -7169,10 +7169,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>533498</v>
+        <v>533527</v>
       </c>
       <c r="R66" t="n">
-        <v>6885552</v>
+        <v>6885657</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7231,40 +7231,35 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125448834</v>
+        <v>125448531</v>
       </c>
       <c r="B67" t="n">
-        <v>58020</v>
+        <v>78972</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
@@ -7333,49 +7328,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125452794</v>
+        <v>125451247</v>
       </c>
       <c r="B68" t="n">
-        <v>98339</v>
+        <v>78972</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533476</v>
+        <v>533498</v>
       </c>
       <c r="R68" t="n">
-        <v>6885492</v>
+        <v>6885552</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7434,10 +7425,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125449765</v>
+        <v>125451627</v>
       </c>
       <c r="B69" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7445,21 +7436,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7469,10 +7460,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533527</v>
+        <v>533471</v>
       </c>
       <c r="R69" t="n">
-        <v>6885657</v>
+        <v>6885526</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7531,10 +7522,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125448531</v>
+        <v>125454471</v>
       </c>
       <c r="B70" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7542,21 +7533,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7566,10 +7557,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533571</v>
+        <v>533467</v>
       </c>
       <c r="R70" t="n">
-        <v>6885716</v>
+        <v>6885270</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7628,10 +7619,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125451627</v>
+        <v>125450235</v>
       </c>
       <c r="B71" t="n">
-        <v>80075</v>
+        <v>57651</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7639,34 +7630,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>533471</v>
+        <v>533551</v>
       </c>
       <c r="R71" t="n">
-        <v>6885526</v>
+        <v>6885632</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7699,6 +7695,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7725,45 +7726,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125454471</v>
+        <v>125448834</v>
       </c>
       <c r="B72" t="n">
-        <v>80075</v>
+        <v>58020</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>533467</v>
+        <v>533571</v>
       </c>
       <c r="R72" t="n">
-        <v>6885270</v>
+        <v>6885716</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7822,38 +7828,37 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125450235</v>
+        <v>125452794</v>
       </c>
       <c r="B73" t="n">
-        <v>57651</v>
+        <v>98339</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -7862,10 +7867,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>533551</v>
+        <v>533476</v>
       </c>
       <c r="R73" t="n">
-        <v>6885632</v>
+        <v>6885492</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7898,11 +7903,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 19766-2025 artfynd.xlsx
+++ b/artfynd/A 19766-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125449421</v>
+        <v>125454495</v>
       </c>
       <c r="B2" t="n">
-        <v>91232</v>
+        <v>57652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533564</v>
+        <v>533467</v>
       </c>
       <c r="R2" t="n">
-        <v>6885654</v>
+        <v>6885270</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,38 +782,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125454035</v>
+        <v>125450747</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>98362</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -812,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533438</v>
+        <v>533545</v>
       </c>
       <c r="R3" t="n">
-        <v>6885340</v>
+        <v>6885577</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125452441</v>
+        <v>125449421</v>
       </c>
       <c r="B4" t="n">
-        <v>91250</v>
+        <v>91234</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +894,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533485</v>
+        <v>533564</v>
       </c>
       <c r="R4" t="n">
-        <v>6885472</v>
+        <v>6885654</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125454495</v>
+        <v>125452441</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>91252</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,39 +991,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533467</v>
+        <v>533485</v>
       </c>
       <c r="R5" t="n">
-        <v>6885270</v>
+        <v>6885472</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,11 +1051,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1077,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125452107</v>
+        <v>125454035</v>
       </c>
       <c r="B6" t="n">
-        <v>57811</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,36 +1088,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1127,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533485</v>
+        <v>533438</v>
       </c>
       <c r="R6" t="n">
-        <v>6885472</v>
+        <v>6885340</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,37 +1179,47 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125450747</v>
+        <v>125452107</v>
       </c>
       <c r="B7" t="n">
-        <v>98360</v>
+        <v>57812</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533545</v>
+        <v>533485</v>
       </c>
       <c r="R7" t="n">
-        <v>6885577</v>
+        <v>6885472</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,7 +1293,7 @@
         <v>125458714</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>125455042</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>125455201</v>
       </c>
       <c r="B10" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>125449144</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>125449764</v>
       </c>
       <c r="B12" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,45 +1819,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125455217</v>
+        <v>125448798</v>
       </c>
       <c r="B13" t="n">
-        <v>78972</v>
+        <v>98341</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533571</v>
+        <v>533560</v>
       </c>
       <c r="R13" t="n">
-        <v>6885153</v>
+        <v>6885711</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1916,10 +1920,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125453918</v>
+        <v>125453207</v>
       </c>
       <c r="B14" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,10 +1955,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533477</v>
+        <v>533421</v>
       </c>
       <c r="R14" t="n">
-        <v>6885329</v>
+        <v>6885458</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2013,10 +2017,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125453207</v>
+        <v>125455217</v>
       </c>
       <c r="B15" t="n">
-        <v>80075</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2024,34 +2028,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>533421</v>
+        <v>533571</v>
       </c>
       <c r="R15" t="n">
-        <v>6885458</v>
+        <v>6885153</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2110,49 +2114,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125448798</v>
+        <v>125453918</v>
       </c>
       <c r="B16" t="n">
-        <v>98339</v>
+        <v>80076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533560</v>
+        <v>533477</v>
       </c>
       <c r="R16" t="n">
-        <v>6885711</v>
+        <v>6885329</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,7 +2214,7 @@
         <v>125450058</v>
       </c>
       <c r="B17" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125456251</v>
+        <v>125452738</v>
       </c>
       <c r="B18" t="n">
-        <v>91232</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,34 +2323,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>533497</v>
+        <v>533500</v>
       </c>
       <c r="R18" t="n">
-        <v>6884966</v>
+        <v>6885440</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125448326</v>
+        <v>125453277</v>
       </c>
       <c r="B19" t="n">
-        <v>78972</v>
+        <v>57812</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2420,34 +2420,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>533568</v>
+        <v>533421</v>
       </c>
       <c r="R19" t="n">
-        <v>6885736</v>
+        <v>6885458</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2506,32 +2511,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125449383</v>
+        <v>125451751</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>97219</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2541,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>533564</v>
+        <v>533503</v>
       </c>
       <c r="R20" t="n">
-        <v>6885654</v>
+        <v>6885498</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2606,7 +2611,7 @@
         <v>125449396</v>
       </c>
       <c r="B21" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2700,10 +2705,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125452738</v>
+        <v>125449383</v>
       </c>
       <c r="B22" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2735,10 +2740,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533500</v>
+        <v>533564</v>
       </c>
       <c r="R22" t="n">
-        <v>6885440</v>
+        <v>6885654</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2797,10 +2802,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125452859</v>
+        <v>125448326</v>
       </c>
       <c r="B23" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2832,10 +2837,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533466</v>
+        <v>533568</v>
       </c>
       <c r="R23" t="n">
-        <v>6885506</v>
+        <v>6885736</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2894,10 +2899,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125453277</v>
+        <v>125456251</v>
       </c>
       <c r="B24" t="n">
-        <v>57811</v>
+        <v>91234</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2905,39 +2910,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533421</v>
+        <v>533497</v>
       </c>
       <c r="R24" t="n">
-        <v>6885458</v>
+        <v>6884966</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2996,49 +2996,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125449118</v>
+        <v>125452859</v>
       </c>
       <c r="B25" t="n">
-        <v>98339</v>
+        <v>78973</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533549</v>
+        <v>533466</v>
       </c>
       <c r="R25" t="n">
-        <v>6885695</v>
+        <v>6885506</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3068,19 +3064,9 @@
           <t>2025-05-27</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3110,7 +3096,7 @@
         <v>125449821</v>
       </c>
       <c r="B26" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3208,45 +3194,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125451751</v>
+        <v>125449118</v>
       </c>
       <c r="B27" t="n">
-        <v>97217</v>
+        <v>98341</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533503</v>
+        <v>533549</v>
       </c>
       <c r="R27" t="n">
-        <v>6885498</v>
+        <v>6885695</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3276,9 +3266,19 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3305,50 +3305,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125457210</v>
+        <v>125449273</v>
       </c>
       <c r="B28" t="n">
-        <v>57651</v>
+        <v>98341</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>37</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533578</v>
+        <v>533550</v>
       </c>
       <c r="R28" t="n">
-        <v>6885205</v>
+        <v>6885685</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3381,11 +3380,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3412,38 +3406,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125456654</v>
+        <v>125451213</v>
       </c>
       <c r="B29" t="n">
-        <v>57651</v>
+        <v>98362</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3452,10 +3445,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533587</v>
+        <v>533490</v>
       </c>
       <c r="R29" t="n">
-        <v>6885384</v>
+        <v>6885584</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3488,11 +3481,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3519,10 +3507,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125455421</v>
+        <v>125448667</v>
       </c>
       <c r="B30" t="n">
-        <v>57651</v>
+        <v>80076</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3530,43 +3518,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533497</v>
+        <v>533560</v>
       </c>
       <c r="R30" t="n">
-        <v>6885148</v>
+        <v>6885711</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3625,10 +3604,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125451793</v>
+        <v>125457445</v>
       </c>
       <c r="B31" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3655,19 +3634,19 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>37</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533474</v>
+        <v>533577</v>
       </c>
       <c r="R31" t="n">
-        <v>6885517</v>
+        <v>6885438</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3726,45 +3705,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125448667</v>
+        <v>125451793</v>
       </c>
       <c r="B32" t="n">
-        <v>80075</v>
+        <v>98341</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533560</v>
+        <v>533474</v>
       </c>
       <c r="R32" t="n">
-        <v>6885711</v>
+        <v>6885517</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3823,49 +3806,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125449273</v>
+        <v>125455421</v>
       </c>
       <c r="B33" t="n">
-        <v>98339</v>
+        <v>57652</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533550</v>
+        <v>533497</v>
       </c>
       <c r="R33" t="n">
-        <v>6885685</v>
+        <v>6885148</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3924,49 +3912,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125451213</v>
+        <v>125457210</v>
       </c>
       <c r="B34" t="n">
-        <v>98360</v>
+        <v>57652</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533490</v>
+        <v>533578</v>
       </c>
       <c r="R34" t="n">
-        <v>6885584</v>
+        <v>6885205</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3999,6 +3988,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4025,49 +4019,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125457445</v>
+        <v>125456654</v>
       </c>
       <c r="B35" t="n">
-        <v>98339</v>
+        <v>57652</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>37</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533577</v>
+        <v>533587</v>
       </c>
       <c r="R35" t="n">
-        <v>6885438</v>
+        <v>6885384</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4100,6 +4095,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4126,49 +4126,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125450818</v>
+        <v>125450637</v>
       </c>
       <c r="B36" t="n">
-        <v>98339</v>
+        <v>78973</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533494</v>
+        <v>533545</v>
       </c>
       <c r="R36" t="n">
-        <v>6885624</v>
+        <v>6885577</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4227,45 +4223,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125450637</v>
+        <v>125450818</v>
       </c>
       <c r="B37" t="n">
-        <v>78972</v>
+        <v>98341</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533545</v>
+        <v>533494</v>
       </c>
       <c r="R37" t="n">
-        <v>6885577</v>
+        <v>6885624</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4324,45 +4324,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125456221</v>
+        <v>125448393</v>
       </c>
       <c r="B38" t="n">
-        <v>78972</v>
+        <v>97219</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533478</v>
+        <v>533568</v>
       </c>
       <c r="R38" t="n">
-        <v>6884944</v>
+        <v>6885736</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4421,10 +4421,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125450387</v>
+        <v>125456538</v>
       </c>
       <c r="B39" t="n">
-        <v>78972</v>
+        <v>57652</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4432,34 +4432,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533528</v>
+        <v>533543</v>
       </c>
       <c r="R39" t="n">
-        <v>6885627</v>
+        <v>6885069</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4492,6 +4497,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4518,10 +4528,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125456538</v>
+        <v>125456221</v>
       </c>
       <c r="B40" t="n">
-        <v>57651</v>
+        <v>78973</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4529,39 +4539,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533543</v>
+        <v>533478</v>
       </c>
       <c r="R40" t="n">
-        <v>6885069</v>
+        <v>6884944</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4594,11 +4599,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4625,32 +4625,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125448393</v>
+        <v>125450387</v>
       </c>
       <c r="B41" t="n">
-        <v>97217</v>
+        <v>78973</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533568</v>
+        <v>533528</v>
       </c>
       <c r="R41" t="n">
-        <v>6885736</v>
+        <v>6885627</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4725,7 +4725,7 @@
         <v>125451578</v>
       </c>
       <c r="B42" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4823,10 +4823,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125456823</v>
+        <v>125449555</v>
       </c>
       <c r="B43" t="n">
-        <v>57651</v>
+        <v>80076</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4834,39 +4834,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533580</v>
+        <v>533527</v>
       </c>
       <c r="R43" t="n">
-        <v>6885391</v>
+        <v>6885657</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4899,11 +4894,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4930,10 +4920,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125456232</v>
+        <v>125456823</v>
       </c>
       <c r="B44" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4961,7 +4951,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4970,10 +4960,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533493</v>
+        <v>533580</v>
       </c>
       <c r="R44" t="n">
-        <v>6884951</v>
+        <v>6885391</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5010,7 +5000,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack på tall.  Mest äldre spår men öven något färskt</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5037,10 +5027,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125449555</v>
+        <v>125456232</v>
       </c>
       <c r="B45" t="n">
-        <v>80075</v>
+        <v>57652</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5048,34 +5038,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533527</v>
+        <v>533493</v>
       </c>
       <c r="R45" t="n">
-        <v>6885657</v>
+        <v>6884951</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5108,6 +5103,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Mest äldre spår men öven något färskt</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5137,7 +5137,7 @@
         <v>125456035</v>
       </c>
       <c r="B46" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>125456732</v>
       </c>
       <c r="B47" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5333,38 +5333,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125451954</v>
+        <v>125451692</v>
       </c>
       <c r="B48" t="n">
-        <v>56834</v>
+        <v>98341</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>22</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5373,10 +5372,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533479</v>
+        <v>533471</v>
       </c>
       <c r="R48" t="n">
-        <v>6885506</v>
+        <v>6885526</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5435,49 +5434,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125451692</v>
+        <v>125457380</v>
       </c>
       <c r="B49" t="n">
-        <v>98339</v>
+        <v>91530</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>533471</v>
+        <v>533577</v>
       </c>
       <c r="R49" t="n">
-        <v>6885526</v>
+        <v>6885438</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5536,54 +5540,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125457380</v>
+        <v>125451683</v>
       </c>
       <c r="B50" t="n">
-        <v>91528</v>
+        <v>80105</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>533577</v>
+        <v>533471</v>
       </c>
       <c r="R50" t="n">
-        <v>6885438</v>
+        <v>6885526</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5645,7 +5640,7 @@
         <v>125450555</v>
       </c>
       <c r="B51" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5739,45 +5734,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125451683</v>
+        <v>125451954</v>
       </c>
       <c r="B52" t="n">
-        <v>80104</v>
+        <v>56835</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>533471</v>
+        <v>533479</v>
       </c>
       <c r="R52" t="n">
-        <v>6885526</v>
+        <v>6885506</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5836,32 +5836,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125459017</v>
+        <v>125451445</v>
       </c>
       <c r="B53" t="n">
-        <v>91902</v>
+        <v>80105</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>898</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5871,10 +5871,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533634</v>
+        <v>533474</v>
       </c>
       <c r="R53" t="n">
-        <v>6885654</v>
+        <v>6885569</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5936,7 +5936,7 @@
         <v>125453495</v>
       </c>
       <c r="B54" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6040,42 +6040,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125452337</v>
+        <v>125448879</v>
       </c>
       <c r="B55" t="n">
-        <v>78972</v>
+        <v>98341</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6084,10 +6079,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>533485</v>
+        <v>533558</v>
       </c>
       <c r="R55" t="n">
-        <v>6885472</v>
+        <v>6885696</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6146,32 +6141,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125451445</v>
+        <v>125459017</v>
       </c>
       <c r="B56" t="n">
-        <v>80104</v>
+        <v>91904</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>898</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6181,10 +6176,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>533474</v>
+        <v>533634</v>
       </c>
       <c r="R56" t="n">
-        <v>6885569</v>
+        <v>6885654</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6243,37 +6238,42 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125448879</v>
+        <v>125452337</v>
       </c>
       <c r="B57" t="n">
-        <v>98339</v>
+        <v>78973</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>533558</v>
+        <v>533485</v>
       </c>
       <c r="R57" t="n">
-        <v>6885696</v>
+        <v>6885472</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6347,7 +6347,7 @@
         <v>125456355</v>
       </c>
       <c r="B58" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>125457312</v>
       </c>
       <c r="B59" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>125455687</v>
       </c>
       <c r="B60" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>125452374</v>
       </c>
       <c r="B61" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>125448352</v>
       </c>
       <c r="B62" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>125456968</v>
       </c>
       <c r="B63" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>125450152</v>
       </c>
       <c r="B64" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>125451409</v>
       </c>
       <c r="B65" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7134,45 +7134,50 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125449765</v>
+        <v>125448834</v>
       </c>
       <c r="B66" t="n">
-        <v>78972</v>
+        <v>58021</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>533527</v>
+        <v>533571</v>
       </c>
       <c r="R66" t="n">
-        <v>6885657</v>
+        <v>6885716</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7231,10 +7236,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125448531</v>
+        <v>125450235</v>
       </c>
       <c r="B67" t="n">
-        <v>78972</v>
+        <v>57652</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7242,34 +7247,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>533571</v>
+        <v>533551</v>
       </c>
       <c r="R67" t="n">
-        <v>6885716</v>
+        <v>6885632</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7302,6 +7312,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7328,45 +7343,49 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125451247</v>
+        <v>125452794</v>
       </c>
       <c r="B68" t="n">
-        <v>78972</v>
+        <v>98341</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533498</v>
+        <v>533476</v>
       </c>
       <c r="R68" t="n">
-        <v>6885552</v>
+        <v>6885492</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7425,10 +7444,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125451627</v>
+        <v>125449765</v>
       </c>
       <c r="B69" t="n">
-        <v>80075</v>
+        <v>78973</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7436,21 +7455,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7460,10 +7479,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533471</v>
+        <v>533527</v>
       </c>
       <c r="R69" t="n">
-        <v>6885526</v>
+        <v>6885657</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7522,10 +7541,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125454471</v>
+        <v>125448531</v>
       </c>
       <c r="B70" t="n">
-        <v>80075</v>
+        <v>78973</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7533,21 +7552,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7557,10 +7576,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533467</v>
+        <v>533571</v>
       </c>
       <c r="R70" t="n">
-        <v>6885270</v>
+        <v>6885716</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7619,10 +7638,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125450235</v>
+        <v>125454471</v>
       </c>
       <c r="B71" t="n">
-        <v>57651</v>
+        <v>80076</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7630,39 +7649,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>533551</v>
+        <v>533467</v>
       </c>
       <c r="R71" t="n">
-        <v>6885632</v>
+        <v>6885270</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7695,11 +7709,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7726,50 +7735,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125448834</v>
+        <v>125451627</v>
       </c>
       <c r="B72" t="n">
-        <v>58020</v>
+        <v>80076</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>533571</v>
+        <v>533471</v>
       </c>
       <c r="R72" t="n">
-        <v>6885716</v>
+        <v>6885526</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7828,49 +7832,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125452794</v>
+        <v>125451247</v>
       </c>
       <c r="B73" t="n">
-        <v>98339</v>
+        <v>78973</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>533476</v>
+        <v>533498</v>
       </c>
       <c r="R73" t="n">
-        <v>6885492</v>
+        <v>6885552</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7932,7 +7932,7 @@
         <v>125452693</v>
       </c>
       <c r="B74" t="n">
-        <v>56227</v>
+        <v>56228</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>125456893</v>
       </c>
       <c r="B75" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8142,10 +8142,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125456406</v>
+        <v>125450898</v>
       </c>
       <c r="B76" t="n">
-        <v>57648</v>
+        <v>80076</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8153,39 +8153,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>533520</v>
+        <v>533518</v>
       </c>
       <c r="R76" t="n">
-        <v>6885018</v>
+        <v>6885534</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8244,10 +8244,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125450898</v>
+        <v>125456406</v>
       </c>
       <c r="B77" t="n">
-        <v>80075</v>
+        <v>57649</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8255,39 +8255,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>533518</v>
+        <v>533520</v>
       </c>
       <c r="R77" t="n">
-        <v>6885534</v>
+        <v>6885018</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8349,7 +8349,7 @@
         <v>125453817</v>
       </c>
       <c r="B78" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8443,10 +8443,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125455827</v>
+        <v>125456371</v>
       </c>
       <c r="B79" t="n">
-        <v>91232</v>
+        <v>78973</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8454,21 +8454,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>533479</v>
+        <v>533602</v>
       </c>
       <c r="R79" t="n">
-        <v>6884999</v>
+        <v>6885362</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8540,45 +8540,50 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125454123</v>
+        <v>125459043</v>
       </c>
       <c r="B80" t="n">
-        <v>97217</v>
+        <v>57652</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>533490</v>
+        <v>533634</v>
       </c>
       <c r="R80" t="n">
-        <v>6885291</v>
+        <v>6885654</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8611,6 +8616,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8640,7 +8650,7 @@
         <v>125458100</v>
       </c>
       <c r="B81" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8738,45 +8748,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125456371</v>
+        <v>125454123</v>
       </c>
       <c r="B82" t="n">
-        <v>78972</v>
+        <v>97219</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533602</v>
+        <v>533490</v>
       </c>
       <c r="R82" t="n">
-        <v>6885362</v>
+        <v>6885291</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8835,10 +8845,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125459043</v>
+        <v>125455827</v>
       </c>
       <c r="B83" t="n">
-        <v>57651</v>
+        <v>91234</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8846,39 +8856,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>533634</v>
+        <v>533479</v>
       </c>
       <c r="R83" t="n">
-        <v>6885654</v>
+        <v>6884999</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8911,11 +8916,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8945,7 +8945,7 @@
         <v>125456250</v>
       </c>
       <c r="B84" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>125458140</v>
       </c>
       <c r="B85" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>125449196</v>
       </c>
       <c r="B86" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>125450671</v>
       </c>
       <c r="B87" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9352,45 +9352,49 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125457466</v>
+        <v>125450718</v>
       </c>
       <c r="B88" t="n">
-        <v>91232</v>
+        <v>98341</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>533602</v>
+        <v>533537</v>
       </c>
       <c r="R88" t="n">
-        <v>6885362</v>
+        <v>6885571</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9449,45 +9453,49 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125449549</v>
+        <v>125450452</v>
       </c>
       <c r="B89" t="n">
-        <v>80075</v>
+        <v>98341</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>533559</v>
+        <v>533508</v>
       </c>
       <c r="R89" t="n">
-        <v>6885649</v>
+        <v>6885633</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9546,10 +9554,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125457133</v>
+        <v>125457466</v>
       </c>
       <c r="B90" t="n">
-        <v>78972</v>
+        <v>91234</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9557,21 +9565,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9581,10 +9589,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>533574</v>
+        <v>533602</v>
       </c>
       <c r="R90" t="n">
-        <v>6885404</v>
+        <v>6885362</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9646,7 +9654,7 @@
         <v>125458930</v>
       </c>
       <c r="B91" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9740,10 +9748,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125450505</v>
+        <v>125457133</v>
       </c>
       <c r="B92" t="n">
-        <v>80075</v>
+        <v>78973</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9751,39 +9759,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>533526</v>
+        <v>533574</v>
       </c>
       <c r="R92" t="n">
-        <v>6885605</v>
+        <v>6885404</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9842,10 +9845,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125450188</v>
+        <v>125450505</v>
       </c>
       <c r="B93" t="n">
-        <v>57651</v>
+        <v>80076</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9853,27 +9856,27 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -9882,10 +9885,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>533539</v>
+        <v>533526</v>
       </c>
       <c r="R93" t="n">
-        <v>6885634</v>
+        <v>6885605</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9918,11 +9921,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9949,54 +9947,49 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125452660</v>
+        <v>125456788</v>
       </c>
       <c r="B94" t="n">
-        <v>57651</v>
+        <v>98341</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>130</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Kölabäcken, Hls</t>
+          <t>Lillkölsberget, Hls</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>533535</v>
+        <v>533556</v>
       </c>
       <c r="R94" t="n">
-        <v>6885468</v>
+        <v>6885155</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10055,49 +10048,50 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125456788</v>
+        <v>125450188</v>
       </c>
       <c r="B95" t="n">
-        <v>98339</v>
+        <v>57652</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>130</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lillkölsberget, Hls</t>
+          <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>533556</v>
+        <v>533539</v>
       </c>
       <c r="R95" t="n">
-        <v>6885155</v>
+        <v>6885634</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10130,6 +10124,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10156,37 +10155,42 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125450718</v>
+        <v>125452660</v>
       </c>
       <c r="B96" t="n">
-        <v>98339</v>
+        <v>57652</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -10195,10 +10199,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>533537</v>
+        <v>533535</v>
       </c>
       <c r="R96" t="n">
-        <v>6885571</v>
+        <v>6885468</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10257,49 +10261,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125450452</v>
+        <v>125449549</v>
       </c>
       <c r="B97" t="n">
-        <v>98339</v>
+        <v>80076</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Kölabäcken, Hls</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>533508</v>
+        <v>533559</v>
       </c>
       <c r="R97" t="n">
-        <v>6885633</v>
+        <v>6885649</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10361,7 +10361,7 @@
         <v>125455828</v>
       </c>
       <c r="B98" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
